--- a/Excel_Introduction_and_Data_Formating/Excel_Data_Analytics_Practice.xlsx
+++ b/Excel_Introduction_and_Data_Formating/Excel_Data_Analytics_Practice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e01621777f20dcb/Desktop/Excel_For_Data_Analytics/Excel_Introduction_and_Data_Formating/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2650" documentId="8_{5BFF8888-E61D-45DF-9242-3D43603A95FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF20AC83-9EE6-4CB5-B94A-95FDDEB8F235}"/>
+  <xr:revisionPtr revIDLastSave="2839" documentId="8_{5BFF8888-E61D-45DF-9242-3D43603A95FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9AA602D-0567-4A0F-87BA-3F22A6C16545}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="13" activeTab="15" xr2:uid="{E6744EAD-35E1-4258-81F8-3CB7F274373C}"/>
+    <workbookView minimized="1" xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" firstSheet="16" activeTab="18" xr2:uid="{E6744EAD-35E1-4258-81F8-3CB7F274373C}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel Interface" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,9 @@
     <sheet name="Vlookup" sheetId="16" r:id="rId14"/>
     <sheet name="LOOKUP" sheetId="18" r:id="rId15"/>
     <sheet name="XLOOKUP" sheetId="17" r:id="rId16"/>
+    <sheet name="Index and Match Function" sheetId="19" r:id="rId17"/>
+    <sheet name="Data Validation" sheetId="20" r:id="rId18"/>
+    <sheet name="Paste Special" sheetId="21" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,8 +51,35 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={3AB69CAA-AE09-4487-A013-2D20A073A2CA}</author>
+    <author>tc={4A6D0816-4D41-4AB2-A9D6-1E38783FDE95}</author>
+  </authors>
+  <commentList>
+    <comment ref="R4" authorId="0" shapeId="0" xr:uid="{3AB69CAA-AE09-4487-A013-2D20A073A2CA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please checck the value</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="1" shapeId="0" xr:uid="{4A6D0816-4D41-4AB2-A9D6-1E38783FDE95}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please checck the value</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -71,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="448">
   <si>
     <t>1.edit in data  (F2)/double click</t>
   </si>
@@ -1385,6 +1415,36 @@
   </si>
   <si>
     <t>Wildcard data present in sequence</t>
+  </si>
+  <si>
+    <t>Positions from Match function</t>
+  </si>
+  <si>
+    <t>Column numbers</t>
+  </si>
+  <si>
+    <t>Row numbers</t>
+  </si>
+  <si>
+    <t>Values from Index function - 1D</t>
+  </si>
+  <si>
+    <t>Values from Index function - 2D</t>
+  </si>
+  <si>
+    <t>Index + Match Functions</t>
+  </si>
+  <si>
+    <t>DATA VALIDATION G2:J6</t>
+  </si>
+  <si>
+    <t>South-west</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>DATA VALIDATION - using paste special</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1457,7 @@
     <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="167" formatCode="dddd"/>
   </numFmts>
-  <fonts count="112" x14ac:knownFonts="1">
+  <fonts count="124" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2212,8 +2272,94 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Amasis MT Pro Medium"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Amasis MT Pro Medium"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Amasis MT Pro Medium"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Amasis MT Pro Medium"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Amasis MT Pro Medium"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Amasis MT Pro Medium"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Amasis MT Pro Medium"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="45">
+  <fills count="48">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2478,8 +2624,26 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor rgb="FFFBE4D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor rgb="FFB4C6E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="49">
+  <borders count="65">
     <border>
       <left/>
       <right/>
@@ -3095,15 +3259,219 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color theme="3" tint="0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="493">
+  <cellXfs count="551">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4233,246 +4601,401 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="39" borderId="40" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="24" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="117" fillId="24" borderId="51" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="39" borderId="40" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="40" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="115" fillId="45" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="45" borderId="40" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="115" fillId="45" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="40" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="45" borderId="40" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="45" borderId="40" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="46" borderId="40" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="47" borderId="40" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="115" fillId="0" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="115" fillId="0" borderId="40" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="50" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="8" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="24" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="24" borderId="51" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="24" borderId="51" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="24" borderId="55" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="56" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="24" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="24" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="24" borderId="53" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="59" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="61" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="62" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="64" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="28" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="28" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="27" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="27" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="28" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="22" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="22" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="8" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="33" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="16" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="8" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="9" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="9" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="9" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="31" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="31" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="28" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="28" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="28" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="27" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="27" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="28" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="22" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="22" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="8" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="33" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="16" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="8" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="9" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="9" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="9" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="31" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="31" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="95" fillId="35" borderId="43" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4515,12 +5038,29 @@
     <xf numFmtId="0" fontId="104" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="120" fillId="2" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="2" borderId="32" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="2" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="54" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{5DD338C1-82ED-4982-9BB5-3EF66968FF01}"/>
     <cellStyle name="Normal 2 2" xfId="4" xr:uid="{511AF93F-5767-4AA6-B1ED-4F988213519B}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{2325A7D6-EA30-4F87-9F44-BE1E3356D852}"/>
+    <cellStyle name="Normal 3 2" xfId="6" xr:uid="{ED522051-0225-4473-9518-F3E7B0C53EBF}"/>
+    <cellStyle name="Normal 4" xfId="5" xr:uid="{8BD345DC-0D02-476B-B0AB-1D49AAEB3C56}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="27">
@@ -5587,6 +6127,146 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5800</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>96190</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>6160</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>96550</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9AB586C-E202-45CC-9C02-77FEF928A72F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1326600" y="293040"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="31" name="Ink 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01B45ACC-065C-BBB4-47F8-8C0FEC82A2A4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1317600" y="284040"/>
+              <a:ext cx="18000" cy="18000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5800</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>96190</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>6160</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>96550</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8517FF53-23AE-42A8-AD01-0C204E480CC4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1326600" y="293040"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="31" name="Ink 30">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01B45ACC-065C-BBB4-47F8-8C0FEC82A2A4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1317600" y="284040"/>
+              <a:ext cx="18000" cy="18000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
@@ -5783,8 +6463,66 @@
 </inkml:ink>
 </file>
 
+<file path=xl/ink/ink8.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-30T17:33:17.700"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 23387,'0'0'3121</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink9.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-30T17:45:31.041"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#5B2D90"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 23387,'0'0'3121</inkml:trace>
+</inkml:ink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="DR. NISHTHA JAIN" id="{08673384-2B29-4805-AFBC-FD46B9A55678}" userId="116f6aa4af3aa8b1" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6122,6 +6860,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="R4" dT="2026-08-07T14:27:43.43" personId="{08673384-2B29-4805-AFBC-FD46B9A55678}" id="{3AB69CAA-AE09-4487-A013-2D20A073A2CA}">
+    <text>Please checck the value</text>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2026-08-07T14:27:43.43" personId="{08673384-2B29-4805-AFBC-FD46B9A55678}" id="{4A6D0816-4D41-4AB2-A9D6-1E38783FDE95}">
+    <text>Please checck the value</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A60D101-F3F4-44C7-92C7-5B064D8BC768}">
   <dimension ref="A1:N22"/>
@@ -6136,77 +6885,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="401" t="s">
+      <c r="A1" s="452" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="402"/>
-      <c r="C1" s="402"/>
-      <c r="D1" s="402"/>
-      <c r="E1" s="402"/>
-      <c r="F1" s="402"/>
+      <c r="B1" s="453"/>
+      <c r="C1" s="453"/>
+      <c r="D1" s="453"/>
+      <c r="E1" s="453"/>
+      <c r="F1" s="453"/>
     </row>
     <row r="2" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="402"/>
-      <c r="B2" s="402"/>
-      <c r="C2" s="402"/>
-      <c r="D2" s="402"/>
-      <c r="E2" s="402"/>
-      <c r="F2" s="402"/>
+      <c r="A2" s="453"/>
+      <c r="B2" s="453"/>
+      <c r="C2" s="453"/>
+      <c r="D2" s="453"/>
+      <c r="E2" s="453"/>
+      <c r="F2" s="453"/>
     </row>
     <row r="3" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="402"/>
-      <c r="B3" s="402"/>
-      <c r="C3" s="402"/>
-      <c r="D3" s="402"/>
-      <c r="E3" s="402"/>
-      <c r="F3" s="402"/>
-      <c r="G3" s="403" t="s">
+      <c r="A3" s="453"/>
+      <c r="B3" s="453"/>
+      <c r="C3" s="453"/>
+      <c r="D3" s="453"/>
+      <c r="E3" s="453"/>
+      <c r="F3" s="453"/>
+      <c r="G3" s="454" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="403"/>
-      <c r="I3" s="403"/>
-      <c r="J3" s="403"/>
-      <c r="K3" s="403"/>
+      <c r="H3" s="454"/>
+      <c r="I3" s="454"/>
+      <c r="J3" s="454"/>
+      <c r="K3" s="454"/>
     </row>
     <row r="4" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G4" s="403" t="s">
+      <c r="G4" s="454" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="403"/>
-      <c r="I4" s="403"/>
-      <c r="J4" s="403"/>
-      <c r="K4" s="403"/>
+      <c r="H4" s="454"/>
+      <c r="I4" s="454"/>
+      <c r="J4" s="454"/>
+      <c r="K4" s="454"/>
     </row>
     <row r="5" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G5" s="403" t="s">
+      <c r="G5" s="454" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="403"/>
-      <c r="I5" s="403"/>
-      <c r="J5" s="403"/>
-      <c r="K5" s="403"/>
+      <c r="H5" s="454"/>
+      <c r="I5" s="454"/>
+      <c r="J5" s="454"/>
+      <c r="K5" s="454"/>
     </row>
     <row r="6" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G6" s="403" t="s">
+      <c r="G6" s="454" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="403"/>
-      <c r="I6" s="403"/>
-      <c r="J6" s="403"/>
-      <c r="K6" s="403"/>
+      <c r="H6" s="454"/>
+      <c r="I6" s="454"/>
+      <c r="J6" s="454"/>
+      <c r="K6" s="454"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C7" s="8"/>
       <c r="E7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="403" t="s">
+      <c r="G7" s="454" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="403"/>
-      <c r="I7" s="403"/>
-      <c r="J7" s="403"/>
-      <c r="K7" s="403"/>
+      <c r="H7" s="454"/>
+      <c r="I7" s="454"/>
+      <c r="J7" s="454"/>
+      <c r="K7" s="454"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -6527,18 +7276,18 @@
         <f>IF(D3&gt;=180,"Excellent","Good")</f>
         <v>Excellent</v>
       </c>
-      <c r="F3" s="448" t="s">
+      <c r="F3" s="500" t="s">
         <v>305</v>
       </c>
       <c r="G3" s="123"/>
-      <c r="H3" s="451" t="s">
+      <c r="H3" s="503" t="s">
         <v>306</v>
       </c>
       <c r="I3" s="178" t="str" cm="1">
         <f t="array" ref="I3">_xlfn.IFS(D3&lt;130,"Poor",D3&gt;=180,"Good")</f>
         <v>Good</v>
       </c>
-      <c r="J3" s="454" t="s">
+      <c r="J3" s="506" t="s">
         <v>307</v>
       </c>
       <c r="K3" s="139"/>
@@ -6558,14 +7307,14 @@
         <f>IF(D4&gt;=180,"Excellent","Good")</f>
         <v>Excellent</v>
       </c>
-      <c r="F4" s="449"/>
+      <c r="F4" s="501"/>
       <c r="G4" s="123"/>
-      <c r="H4" s="452"/>
+      <c r="H4" s="504"/>
       <c r="I4" s="178" t="str" cm="1">
         <f t="array" ref="I4">_xlfn.IFS(D4&lt;130,"Poor",D4&gt;=180,"Good")</f>
         <v>Good</v>
       </c>
-      <c r="J4" s="455"/>
+      <c r="J4" s="507"/>
       <c r="K4" s="139"/>
       <c r="L4" s="140"/>
     </row>
@@ -6583,14 +7332,14 @@
         <f t="shared" ref="E5:E34" si="0">IF(D5&gt;=180,"Excellent","Good")</f>
         <v>Good</v>
       </c>
-      <c r="F5" s="449"/>
+      <c r="F5" s="501"/>
       <c r="G5" s="123"/>
-      <c r="H5" s="453"/>
+      <c r="H5" s="505"/>
       <c r="I5" s="178" t="str" cm="1">
         <f t="array" ref="I5">_xlfn.IFS(D5&lt;150,"Poor",D5&gt;=150,"Good")</f>
         <v>Poor</v>
       </c>
-      <c r="J5" s="455"/>
+      <c r="J5" s="507"/>
       <c r="K5" s="141"/>
       <c r="L5" s="181" t="s">
         <v>309</v>
@@ -6610,11 +7359,11 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F6" s="449"/>
+      <c r="F6" s="501"/>
       <c r="G6" s="122"/>
       <c r="H6" s="120"/>
       <c r="I6" s="120"/>
-      <c r="J6" s="455"/>
+      <c r="J6" s="507"/>
       <c r="K6" s="141"/>
       <c r="L6" s="117" t="s">
         <v>310</v>
@@ -6634,16 +7383,16 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F7" s="449"/>
+      <c r="F7" s="501"/>
       <c r="G7" s="123"/>
-      <c r="H7" s="457" t="s">
+      <c r="H7" s="509" t="s">
         <v>312</v>
       </c>
       <c r="I7" s="178" t="str" cm="1">
         <f t="array" ref="I7">_xlfn.IFS(D6&lt;100,"very poor",D6&lt;=150,"average",D6&gt;=150,"Goog")</f>
         <v>average</v>
       </c>
-      <c r="J7" s="455"/>
+      <c r="J7" s="507"/>
       <c r="K7" s="141"/>
       <c r="L7" s="120"/>
     </row>
@@ -6661,14 +7410,14 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F8" s="449"/>
+      <c r="F8" s="501"/>
       <c r="G8" s="123"/>
-      <c r="H8" s="458"/>
+      <c r="H8" s="510"/>
       <c r="I8" s="178" t="str" cm="1">
         <f t="array" ref="I8">_xlfn.IFS(D7&lt;100,"very poor",D7&lt;=150,"average",D7&gt;=150,"Goog")</f>
         <v>average</v>
       </c>
-      <c r="J8" s="455"/>
+      <c r="J8" s="507"/>
       <c r="K8" s="139"/>
       <c r="L8" s="139"/>
     </row>
@@ -6686,14 +7435,14 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F9" s="449"/>
+      <c r="F9" s="501"/>
       <c r="G9" s="123"/>
-      <c r="H9" s="459"/>
+      <c r="H9" s="511"/>
       <c r="I9" s="178" t="str" cm="1">
         <f t="array" ref="I9">_xlfn.IFS(D8&lt;100,"very poor",D8&lt;=150,"average",D8&gt;=150,"Good")</f>
         <v>Good</v>
       </c>
-      <c r="J9" s="455"/>
+      <c r="J9" s="507"/>
       <c r="K9" s="139"/>
       <c r="L9" s="139"/>
     </row>
@@ -6711,11 +7460,11 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F10" s="449"/>
+      <c r="F10" s="501"/>
       <c r="G10" s="122"/>
       <c r="H10" s="115"/>
       <c r="I10" s="142"/>
-      <c r="J10" s="455"/>
+      <c r="J10" s="507"/>
       <c r="K10" s="139"/>
       <c r="L10" s="139"/>
     </row>
@@ -6733,16 +7482,16 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F11" s="449"/>
+      <c r="F11" s="501"/>
       <c r="G11" s="123"/>
-      <c r="H11" s="460" t="s">
+      <c r="H11" s="512" t="s">
         <v>317</v>
       </c>
       <c r="I11" s="180" t="str" cm="1">
         <f t="array" ref="I11">_xlfn.IFS(D10&lt;100,"very poor",D10&lt;=100,"poor",D10&lt;=150,"Good",D10&gt;=200,"excellent")</f>
         <v>very poor</v>
       </c>
-      <c r="J11" s="455"/>
+      <c r="J11" s="507"/>
       <c r="K11" s="139"/>
       <c r="L11" s="139"/>
     </row>
@@ -6760,14 +7509,14 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F12" s="449"/>
+      <c r="F12" s="501"/>
       <c r="G12" s="123"/>
-      <c r="H12" s="461"/>
+      <c r="H12" s="513"/>
       <c r="I12" s="180" t="str" cm="1">
         <f t="array" ref="I12">_xlfn.IFS(D11&lt;100,"very poor",D11&lt;=100,"poor",D11&lt;=150,"Good",D11&gt;=200,"excellent")</f>
         <v>Good</v>
       </c>
-      <c r="J12" s="455"/>
+      <c r="J12" s="507"/>
       <c r="K12" s="139"/>
       <c r="L12" s="179"/>
     </row>
@@ -6785,14 +7534,14 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F13" s="449"/>
+      <c r="F13" s="501"/>
       <c r="G13" s="123"/>
-      <c r="H13" s="462"/>
+      <c r="H13" s="514"/>
       <c r="I13" s="180" t="str" cm="1">
         <f t="array" ref="I13">_xlfn.IFS(D12&lt;100,"very poor",D12&lt;=100,"poor",D12&lt;=150,"Good",D12&gt;=200,"excellent")</f>
         <v>excellent</v>
       </c>
-      <c r="J13" s="456"/>
+      <c r="J13" s="508"/>
       <c r="K13" s="139"/>
       <c r="L13" s="139"/>
     </row>
@@ -6810,12 +7559,12 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F14" s="449"/>
+      <c r="F14" s="501"/>
       <c r="G14" s="123"/>
-      <c r="H14" s="463" t="s">
+      <c r="H14" s="515" t="s">
         <v>281</v>
       </c>
-      <c r="I14" s="464"/>
+      <c r="I14" s="516"/>
       <c r="J14" s="122"/>
       <c r="K14" s="139"/>
       <c r="L14" s="139"/>
@@ -6834,7 +7583,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F15" s="449"/>
+      <c r="F15" s="501"/>
       <c r="G15" s="122"/>
       <c r="H15" s="122"/>
       <c r="I15" s="122"/>
@@ -6856,7 +7605,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F16" s="449"/>
+      <c r="F16" s="501"/>
       <c r="G16" s="122"/>
       <c r="H16" s="122"/>
       <c r="I16" s="122"/>
@@ -6878,7 +7627,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F17" s="449"/>
+      <c r="F17" s="501"/>
       <c r="G17" s="122"/>
       <c r="H17" s="122"/>
       <c r="I17" s="122"/>
@@ -6900,7 +7649,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F18" s="449"/>
+      <c r="F18" s="501"/>
       <c r="G18" s="122"/>
       <c r="H18" s="184"/>
       <c r="I18" s="122"/>
@@ -6922,7 +7671,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F19" s="449"/>
+      <c r="F19" s="501"/>
       <c r="G19" s="182"/>
       <c r="H19" s="185"/>
       <c r="I19" s="183" t="s">
@@ -6946,7 +7695,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F20" s="449"/>
+      <c r="F20" s="501"/>
       <c r="G20" s="182"/>
       <c r="H20" s="185"/>
       <c r="I20" s="183"/>
@@ -6968,7 +7717,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F21" s="450"/>
+      <c r="F21" s="502"/>
       <c r="G21" s="122"/>
       <c r="H21" s="186" t="s">
         <v>121</v>
@@ -7004,7 +7753,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F22" s="448" t="s">
+      <c r="F22" s="500" t="s">
         <v>305</v>
       </c>
       <c r="G22" s="122"/>
@@ -7038,7 +7787,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F23" s="449"/>
+      <c r="F23" s="501"/>
       <c r="G23" s="122"/>
       <c r="H23" s="189" t="s">
         <v>127</v>
@@ -7068,7 +7817,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F24" s="449"/>
+      <c r="F24" s="501"/>
       <c r="G24" s="122"/>
       <c r="H24" s="189" t="s">
         <v>129</v>
@@ -7098,7 +7847,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F25" s="449"/>
+      <c r="F25" s="501"/>
       <c r="G25" s="122"/>
       <c r="H25" s="189" t="s">
         <v>130</v>
@@ -7128,7 +7877,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F26" s="449"/>
+      <c r="F26" s="501"/>
       <c r="G26" s="122"/>
       <c r="H26" s="189" t="s">
         <v>131</v>
@@ -7158,7 +7907,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F27" s="449"/>
+      <c r="F27" s="501"/>
       <c r="G27" s="122"/>
       <c r="H27" s="189" t="s">
         <v>133</v>
@@ -7188,7 +7937,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F28" s="449"/>
+      <c r="F28" s="501"/>
       <c r="G28" s="122"/>
       <c r="H28" s="189" t="s">
         <v>129</v>
@@ -7218,7 +7967,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F29" s="449"/>
+      <c r="F29" s="501"/>
       <c r="G29" s="122"/>
       <c r="H29" s="189" t="s">
         <v>135</v>
@@ -7248,7 +7997,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F30" s="449"/>
+      <c r="F30" s="501"/>
       <c r="G30" s="122"/>
       <c r="H30" s="189" t="s">
         <v>136</v>
@@ -7278,7 +8027,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F31" s="449"/>
+      <c r="F31" s="501"/>
       <c r="G31" s="122"/>
       <c r="H31" s="189" t="s">
         <v>137</v>
@@ -7308,7 +8057,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F32" s="449"/>
+      <c r="F32" s="501"/>
       <c r="G32" s="122"/>
       <c r="H32" s="189" t="s">
         <v>138</v>
@@ -7338,7 +8087,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F33" s="449"/>
+      <c r="F33" s="501"/>
       <c r="G33" s="122"/>
       <c r="H33" s="189" t="s">
         <v>139</v>
@@ -7368,7 +8117,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F34" s="449"/>
+      <c r="F34" s="501"/>
       <c r="G34" s="122"/>
       <c r="H34" s="189" t="s">
         <v>140</v>
@@ -7398,7 +8147,7 @@
         <f>IF(D35&gt;=180,"Excellent","Good")</f>
         <v>Good</v>
       </c>
-      <c r="F35" s="450"/>
+      <c r="F35" s="502"/>
       <c r="G35" s="122"/>
       <c r="H35" s="189" t="s">
         <v>141</v>
@@ -7665,11 +8414,11 @@
       <c r="F6" s="243">
         <v>90</v>
       </c>
-      <c r="I6" s="468" t="s">
+      <c r="I6" s="520" t="s">
         <v>389</v>
       </c>
-      <c r="J6" s="468"/>
-      <c r="K6" s="468"/>
+      <c r="J6" s="520"/>
+      <c r="K6" s="520"/>
       <c r="L6" s="251" t="b">
         <v>1</v>
       </c>
@@ -7699,9 +8448,9 @@
       <c r="F7" s="86">
         <v>40</v>
       </c>
-      <c r="I7" s="468"/>
-      <c r="J7" s="468"/>
-      <c r="K7" s="468"/>
+      <c r="I7" s="520"/>
+      <c r="J7" s="520"/>
+      <c r="K7" s="520"/>
       <c r="L7" s="251" t="b">
         <v>0</v>
       </c>
@@ -7731,9 +8480,9 @@
       <c r="F8" s="86">
         <v>80</v>
       </c>
-      <c r="I8" s="468"/>
-      <c r="J8" s="468"/>
-      <c r="K8" s="468"/>
+      <c r="I8" s="520"/>
+      <c r="J8" s="520"/>
+      <c r="K8" s="520"/>
       <c r="L8" s="251" t="b">
         <v>1</v>
       </c>
@@ -7763,9 +8512,9 @@
       <c r="F9" s="86">
         <v>100</v>
       </c>
-      <c r="I9" s="468"/>
-      <c r="J9" s="468"/>
-      <c r="K9" s="468"/>
+      <c r="I9" s="520"/>
+      <c r="J9" s="520"/>
+      <c r="K9" s="520"/>
       <c r="L9" s="251" t="b">
         <v>0</v>
       </c>
@@ -7819,11 +8568,11 @@
       <c r="F11" s="86">
         <v>35</v>
       </c>
-      <c r="I11" s="469" t="s">
+      <c r="I11" s="521" t="s">
         <v>390</v>
       </c>
-      <c r="J11" s="469"/>
-      <c r="K11" s="469"/>
+      <c r="J11" s="521"/>
+      <c r="K11" s="521"/>
       <c r="L11" s="257" t="b">
         <v>1</v>
       </c>
@@ -7853,9 +8602,9 @@
       <c r="F12" s="86">
         <v>90</v>
       </c>
-      <c r="I12" s="469"/>
-      <c r="J12" s="469"/>
-      <c r="K12" s="469"/>
+      <c r="I12" s="521"/>
+      <c r="J12" s="521"/>
+      <c r="K12" s="521"/>
       <c r="L12" s="257" t="b">
         <v>0</v>
       </c>
@@ -7885,9 +8634,9 @@
       <c r="F13" s="86">
         <v>25</v>
       </c>
-      <c r="I13" s="469"/>
-      <c r="J13" s="469"/>
-      <c r="K13" s="469"/>
+      <c r="I13" s="521"/>
+      <c r="J13" s="521"/>
+      <c r="K13" s="521"/>
       <c r="L13" s="257" t="b">
         <v>1</v>
       </c>
@@ -7917,9 +8666,9 @@
       <c r="F14" s="86">
         <v>85</v>
       </c>
-      <c r="I14" s="469"/>
-      <c r="J14" s="469"/>
-      <c r="K14" s="469"/>
+      <c r="I14" s="521"/>
+      <c r="J14" s="521"/>
+      <c r="K14" s="521"/>
       <c r="L14" s="257" t="b">
         <v>0</v>
       </c>
@@ -7973,11 +8722,11 @@
       <c r="F16" s="86">
         <v>60</v>
       </c>
-      <c r="I16" s="470" t="s">
+      <c r="I16" s="522" t="s">
         <v>391</v>
       </c>
-      <c r="J16" s="470"/>
-      <c r="K16" s="470"/>
+      <c r="J16" s="522"/>
+      <c r="K16" s="522"/>
       <c r="L16" s="261" t="b">
         <v>1</v>
       </c>
@@ -7997,9 +8746,9 @@
       <c r="D17" s="86"/>
       <c r="E17" s="86"/>
       <c r="F17" s="244"/>
-      <c r="I17" s="470"/>
-      <c r="J17" s="470"/>
-      <c r="K17" s="470"/>
+      <c r="I17" s="522"/>
+      <c r="J17" s="522"/>
+      <c r="K17" s="522"/>
       <c r="L17" s="261" t="b">
         <v>1</v>
       </c>
@@ -8014,9 +8763,9 @@
       </c>
     </row>
     <row r="18" spans="2:15" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="I18" s="470"/>
-      <c r="J18" s="470"/>
-      <c r="K18" s="470"/>
+      <c r="I18" s="522"/>
+      <c r="J18" s="522"/>
+      <c r="K18" s="522"/>
       <c r="L18" s="261" t="b">
         <v>0</v>
       </c>
@@ -8031,9 +8780,9 @@
       </c>
     </row>
     <row r="19" spans="2:15" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="I19" s="470"/>
-      <c r="J19" s="470"/>
-      <c r="K19" s="470"/>
+      <c r="I19" s="522"/>
+      <c r="J19" s="522"/>
+      <c r="K19" s="522"/>
       <c r="L19" s="261" t="b">
         <v>0</v>
       </c>
@@ -8048,7 +8797,7 @@
       </c>
     </row>
     <row r="20" spans="2:15" ht="55.8" x14ac:dyDescent="0.3">
-      <c r="B20" s="465" t="s">
+      <c r="B20" s="517" t="s">
         <v>380</v>
       </c>
       <c r="C20" s="247" t="s">
@@ -8058,7 +8807,7 @@
         <f>OR(D3&gt;70,E3&gt;70,F3&gt;70)</f>
         <v>1</v>
       </c>
-      <c r="E20" s="466" t="s">
+      <c r="E20" s="518" t="s">
         <v>382</v>
       </c>
       <c r="F20" s="249" t="b">
@@ -8072,9 +8821,9 @@
         <f>AND(D5&gt;70,E5&gt;70,F5&gt;70)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="470"/>
-      <c r="J20" s="470"/>
-      <c r="K20" s="470"/>
+      <c r="I20" s="522"/>
+      <c r="J20" s="522"/>
+      <c r="K20" s="522"/>
       <c r="L20" s="263" t="s">
         <v>392</v>
       </c>
@@ -8085,7 +8834,7 @@
       <c r="O20" s="262"/>
     </row>
     <row r="21" spans="2:15" ht="18" x14ac:dyDescent="0.3">
-      <c r="B21" s="465"/>
+      <c r="B21" s="517"/>
       <c r="C21" s="246" t="s">
         <v>384</v>
       </c>
@@ -8093,7 +8842,7 @@
         <f>OR(D4&gt;70,E4&gt;70,F4&gt;70)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="467"/>
+      <c r="E21" s="519"/>
       <c r="F21" s="249" t="b">
         <f>AND(D10&gt;70,E10&gt;70,F10&gt;70)</f>
         <v>1</v>
@@ -8282,7 +9031,7 @@
       <c r="F7" s="216">
         <v>35</v>
       </c>
-      <c r="G7" s="472" t="s">
+      <c r="G7" s="524" t="s">
         <v>360</v>
       </c>
       <c r="H7" s="217" t="b">
@@ -8317,7 +9066,7 @@
       <c r="F8" s="216">
         <v>40</v>
       </c>
-      <c r="G8" s="472"/>
+      <c r="G8" s="524"/>
       <c r="H8" s="217" t="b">
         <f>OR(D5&gt;=50,E5&gt;=50,F5&gt;=50)</f>
         <v>1</v>
@@ -8350,7 +9099,7 @@
       <c r="F9" s="216">
         <v>80</v>
       </c>
-      <c r="G9" s="472"/>
+      <c r="G9" s="524"/>
       <c r="H9" s="217" t="b">
         <f>OR(D6&gt;=50,E6&gt;=50,F6&gt;=50)</f>
         <v>0</v>
@@ -8405,7 +9154,7 @@
       <c r="F11" s="221">
         <v>75</v>
       </c>
-      <c r="G11" s="473" t="s">
+      <c r="G11" s="525" t="s">
         <v>361</v>
       </c>
       <c r="H11" s="224" t="b">
@@ -8440,7 +9189,7 @@
       <c r="F12" s="221">
         <v>35</v>
       </c>
-      <c r="G12" s="474"/>
+      <c r="G12" s="526"/>
       <c r="H12" s="224" t="b">
         <f t="shared" ref="H12:H13" si="1">AND(D8&gt;=50,E8&gt;=50,F8&gt;=50)</f>
         <v>0</v>
@@ -8473,7 +9222,7 @@
       <c r="F13" s="227">
         <v>90</v>
       </c>
-      <c r="G13" s="475"/>
+      <c r="G13" s="527"/>
       <c r="H13" s="224" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -8528,7 +9277,7 @@
       <c r="F15" s="227">
         <v>85</v>
       </c>
-      <c r="G15" s="473" t="s">
+      <c r="G15" s="525" t="s">
         <v>362</v>
       </c>
       <c r="H15" s="231" t="b">
@@ -8563,7 +9312,7 @@
       <c r="F16" s="227">
         <v>50</v>
       </c>
-      <c r="G16" s="474"/>
+      <c r="G16" s="526"/>
       <c r="H16" s="231" t="b">
         <f t="shared" ref="H16:H17" si="4">_xlfn.XOR(D11&gt;=50,E11&gt;=50,F11&gt;=50)</f>
         <v>1</v>
@@ -8596,7 +9345,7 @@
       <c r="F17" s="227">
         <v>60</v>
       </c>
-      <c r="G17" s="475"/>
+      <c r="G17" s="527"/>
       <c r="H17" s="231" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -8628,14 +9377,14 @@
       <c r="K18" s="210"/>
     </row>
     <row r="20" spans="2:11" ht="51.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="476" t="s">
+      <c r="B20" s="528" t="s">
         <v>364</v>
       </c>
       <c r="C20" s="234" t="b">
         <f>ISBLANK(G10)</f>
         <v>1</v>
       </c>
-      <c r="D20" s="476" t="s">
+      <c r="D20" s="528" t="s">
         <v>365</v>
       </c>
       <c r="E20" s="234" t="b">
@@ -8657,12 +9406,12 @@
       </c>
     </row>
     <row r="21" spans="2:11" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="477"/>
+      <c r="B21" s="529"/>
       <c r="C21" s="234" t="b">
         <f>ISBLANK(G11)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="477"/>
+      <c r="D21" s="529"/>
       <c r="E21" s="234" t="b">
         <f>IFERROR(H8, 0)</f>
         <v>1</v>
@@ -8685,14 +9434,14 @@
       </c>
     </row>
     <row r="22" spans="2:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B22" s="476" t="s">
+      <c r="B22" s="528" t="s">
         <v>366</v>
       </c>
       <c r="C22" s="234" t="b">
         <f>ISERROR(G10)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="476" t="s">
+      <c r="D22" s="528" t="s">
         <v>367</v>
       </c>
       <c r="E22" s="234" t="b">
@@ -8701,19 +9450,19 @@
       </c>
       <c r="G22" s="210"/>
       <c r="H22" s="210"/>
-      <c r="I22" s="471" t="s">
+      <c r="I22" s="523" t="s">
         <v>373</v>
       </c>
-      <c r="J22" s="471"/>
-      <c r="K22" s="471"/>
+      <c r="J22" s="523"/>
+      <c r="K22" s="523"/>
     </row>
     <row r="23" spans="2:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B23" s="477"/>
+      <c r="B23" s="529"/>
       <c r="C23" s="234" t="b">
         <f>ISERROR(G11)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="477"/>
+      <c r="D23" s="529"/>
       <c r="E23" s="234" t="b">
         <f>_xlfn.IFNA(H12, 0)</f>
         <v>0</v>
@@ -8992,12 +9741,12 @@
         <f>HLOOKUP(B11,$C$5:$P$7,3,FALSE)</f>
         <v>45663</v>
       </c>
-      <c r="F11" s="478" t="s">
+      <c r="F11" s="530" t="s">
         <v>408</v>
       </c>
-      <c r="G11" s="399"/>
-      <c r="H11" s="399"/>
-      <c r="I11" s="399"/>
+      <c r="G11" s="499"/>
+      <c r="H11" s="499"/>
+      <c r="I11" s="499"/>
     </row>
     <row r="12" spans="2:16" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B12" s="278" t="s">
@@ -9011,10 +9760,10 @@
         <f t="shared" ref="D12:D18" si="0">HLOOKUP(B12,$C$5:$P$7,3,FALSE)</f>
         <v>45666</v>
       </c>
-      <c r="F12" s="399"/>
-      <c r="G12" s="399"/>
-      <c r="H12" s="399"/>
-      <c r="I12" s="399"/>
+      <c r="F12" s="499"/>
+      <c r="G12" s="499"/>
+      <c r="H12" s="499"/>
+      <c r="I12" s="499"/>
     </row>
     <row r="13" spans="2:16" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B13" s="278" t="s">
@@ -9028,10 +9777,10 @@
         <f t="shared" si="0"/>
         <v>45676</v>
       </c>
-      <c r="F13" s="399"/>
-      <c r="G13" s="399"/>
-      <c r="H13" s="399"/>
-      <c r="I13" s="399"/>
+      <c r="F13" s="499"/>
+      <c r="G13" s="499"/>
+      <c r="H13" s="499"/>
+      <c r="I13" s="499"/>
     </row>
     <row r="14" spans="2:16" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B14" s="278" t="s">
@@ -9045,10 +9794,10 @@
         <f t="shared" si="0"/>
         <v>45658</v>
       </c>
-      <c r="F14" s="399"/>
-      <c r="G14" s="399"/>
-      <c r="H14" s="399"/>
-      <c r="I14" s="399"/>
+      <c r="F14" s="499"/>
+      <c r="G14" s="499"/>
+      <c r="H14" s="499"/>
+      <c r="I14" s="499"/>
     </row>
     <row r="15" spans="2:16" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B15" s="281" t="s">
@@ -9062,10 +9811,10 @@
         <f t="shared" si="0"/>
         <v>45677</v>
       </c>
-      <c r="F15" s="399"/>
-      <c r="G15" s="399"/>
-      <c r="H15" s="399"/>
-      <c r="I15" s="399"/>
+      <c r="F15" s="499"/>
+      <c r="G15" s="499"/>
+      <c r="H15" s="499"/>
+      <c r="I15" s="499"/>
     </row>
     <row r="16" spans="2:16" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B16" s="281" t="s">
@@ -9079,10 +9828,10 @@
         <f t="shared" si="0"/>
         <v>45667</v>
       </c>
-      <c r="F16" s="399"/>
-      <c r="G16" s="399"/>
-      <c r="H16" s="399"/>
-      <c r="I16" s="399"/>
+      <c r="F16" s="499"/>
+      <c r="G16" s="499"/>
+      <c r="H16" s="499"/>
+      <c r="I16" s="499"/>
     </row>
     <row r="17" spans="2:9" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B17" s="281" t="s">
@@ -9096,10 +9845,10 @@
         <f t="shared" si="0"/>
         <v>45674</v>
       </c>
-      <c r="F17" s="399"/>
-      <c r="G17" s="399"/>
-      <c r="H17" s="399"/>
-      <c r="I17" s="399"/>
+      <c r="F17" s="499"/>
+      <c r="G17" s="499"/>
+      <c r="H17" s="499"/>
+      <c r="I17" s="499"/>
     </row>
     <row r="18" spans="2:9" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B18" s="281" t="s">
@@ -9656,14 +10405,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="399" t="s">
+      <c r="F1" s="499" t="s">
         <v>429</v>
       </c>
-      <c r="G1" s="399"/>
+      <c r="G1" s="499"/>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="F2" s="399"/>
-      <c r="G2" s="399"/>
+      <c r="F2" s="499"/>
+      <c r="G2" s="499"/>
     </row>
     <row r="3" spans="2:8" ht="18" x14ac:dyDescent="0.3">
       <c r="B3" s="367" t="s">
@@ -10669,11 +11418,11 @@
       <c r="U58" s="372" t="s">
         <v>405</v>
       </c>
-      <c r="V58" s="400" t="s">
+      <c r="V58" s="531" t="s">
         <v>435</v>
       </c>
-      <c r="W58" s="400"/>
-      <c r="X58" s="400"/>
+      <c r="W58" s="531"/>
+      <c r="X58" s="531"/>
     </row>
     <row r="59" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H59" s="393"/>
@@ -10695,9 +11444,9 @@
       <c r="S59" s="374"/>
       <c r="T59" s="374"/>
       <c r="U59" s="374"/>
-      <c r="V59" s="400"/>
-      <c r="W59" s="400"/>
-      <c r="X59" s="400"/>
+      <c r="V59" s="531"/>
+      <c r="W59" s="531"/>
+      <c r="X59" s="531"/>
     </row>
     <row r="60" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H60" s="393"/>
@@ -10716,9 +11465,9 @@
       <c r="S60" s="374"/>
       <c r="T60" s="374"/>
       <c r="U60" s="374"/>
-      <c r="V60" s="400"/>
-      <c r="W60" s="400"/>
-      <c r="X60" s="400"/>
+      <c r="V60" s="531"/>
+      <c r="W60" s="531"/>
+      <c r="X60" s="531"/>
     </row>
     <row r="61" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H61" s="393"/>
@@ -10737,9 +11486,9 @@
       <c r="S61" s="381"/>
       <c r="T61" s="381"/>
       <c r="U61" s="381"/>
-      <c r="V61" s="400"/>
-      <c r="W61" s="400"/>
-      <c r="X61" s="400"/>
+      <c r="V61" s="531"/>
+      <c r="W61" s="531"/>
+      <c r="X61" s="531"/>
     </row>
     <row r="62" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="393"/>
@@ -10758,9 +11507,9 @@
       <c r="S62" s="381"/>
       <c r="T62" s="381"/>
       <c r="U62" s="381"/>
-      <c r="V62" s="400"/>
-      <c r="W62" s="400"/>
-      <c r="X62" s="400"/>
+      <c r="V62" s="531"/>
+      <c r="W62" s="531"/>
+      <c r="X62" s="531"/>
     </row>
     <row r="63" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H63" s="382"/>
@@ -10777,9 +11526,9 @@
       <c r="S63" s="382"/>
       <c r="T63" s="382"/>
       <c r="U63" s="382"/>
-      <c r="V63" s="400"/>
-      <c r="W63" s="400"/>
-      <c r="X63" s="400"/>
+      <c r="V63" s="531"/>
+      <c r="W63" s="531"/>
+      <c r="X63" s="531"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10817,7 +11566,7 @@
       <c r="A1" s="305"/>
     </row>
     <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="A2" s="484">
+      <c r="A2" s="537">
         <v>1</v>
       </c>
       <c r="B2" s="307" t="s">
@@ -10834,7 +11583,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="484"/>
+      <c r="A3" s="537"/>
       <c r="B3" s="309">
         <v>36533</v>
       </c>
@@ -10849,7 +11598,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="484"/>
+      <c r="A4" s="537"/>
       <c r="B4" s="309">
         <v>36540</v>
       </c>
@@ -10865,7 +11614,7 @@
       <c r="F4" s="305"/>
     </row>
     <row r="5" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="484"/>
+      <c r="A5" s="537"/>
       <c r="B5" s="309">
         <v>36526</v>
       </c>
@@ -10881,7 +11630,7 @@
       <c r="F5" s="305"/>
     </row>
     <row r="6" spans="1:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="A6" s="484"/>
+      <c r="A6" s="537"/>
       <c r="B6" s="309">
         <v>36536</v>
       </c>
@@ -10906,12 +11655,12 @@
       <c r="I6" s="324" t="s">
         <v>403</v>
       </c>
-      <c r="J6" s="485" t="s">
+      <c r="J6" s="538" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="484"/>
+      <c r="A7" s="537"/>
       <c r="B7" s="309">
         <v>36528</v>
       </c>
@@ -10936,10 +11685,10 @@
         <f>_xlfn.XLOOKUP(G7,$D$3:$D$19,$E$3:$E$19)</f>
         <v>2000</v>
       </c>
-      <c r="J7" s="486"/>
+      <c r="J7" s="539"/>
     </row>
     <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A8" s="484"/>
+      <c r="A8" s="537"/>
       <c r="B8" s="309">
         <v>36544</v>
       </c>
@@ -10966,10 +11715,10 @@
         <f>_xlfn.XLOOKUP(G8,D2:D19,E2:E19,,,-1)</f>
         <v>28000</v>
       </c>
-      <c r="J8" s="486"/>
+      <c r="J8" s="539"/>
     </row>
     <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A9" s="484"/>
+      <c r="A9" s="537"/>
       <c r="B9" s="309">
         <v>36538</v>
       </c>
@@ -10991,13 +11740,13 @@
         <v>South</v>
       </c>
       <c r="I9" s="327">
-        <f t="shared" ref="I9:I15" si="0">_xlfn.XLOOKUP(G9,$D$3:$D$19,$E$3:$E$19)</f>
+        <f t="shared" ref="I9" si="0">_xlfn.XLOOKUP(G9,$D$3:$D$19,$E$3:$E$19)</f>
         <v>30000</v>
       </c>
-      <c r="J9" s="486"/>
+      <c r="J9" s="539"/>
     </row>
     <row r="10" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="484"/>
+      <c r="A10" s="537"/>
       <c r="B10" s="309">
         <v>36532</v>
       </c>
@@ -11022,10 +11771,10 @@
         <f t="shared" ref="I10" si="2">_xlfn.XLOOKUP(G10,D4:D21,E4:E21,,,-1)</f>
         <v>38000</v>
       </c>
-      <c r="J10" s="486"/>
+      <c r="J10" s="539"/>
     </row>
     <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A11" s="484"/>
+      <c r="A11" s="537"/>
       <c r="B11" s="309">
         <v>36531</v>
       </c>
@@ -11049,13 +11798,13 @@
         <v>South</v>
       </c>
       <c r="I11" s="327">
-        <f t="shared" ref="I11:I15" si="4">_xlfn.XLOOKUP(G11,$D$3:$D$19,$E$3:$E$19)</f>
+        <f t="shared" ref="I11" si="4">_xlfn.XLOOKUP(G11,$D$3:$D$19,$E$3:$E$19)</f>
         <v>20000</v>
       </c>
-      <c r="J11" s="486"/>
+      <c r="J11" s="539"/>
     </row>
     <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A12" s="484"/>
+      <c r="A12" s="537"/>
       <c r="B12" s="309">
         <v>36538</v>
       </c>
@@ -11080,10 +11829,10 @@
         <f t="shared" ref="I12" si="6">_xlfn.XLOOKUP(G12,D6:D23,E6:E23,,,-1)</f>
         <v>25000</v>
       </c>
-      <c r="J12" s="486"/>
+      <c r="J12" s="539"/>
     </row>
     <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A13" s="484"/>
+      <c r="A13" s="537"/>
       <c r="B13" s="309">
         <v>36542</v>
       </c>
@@ -11107,13 +11856,13 @@
         <v>East</v>
       </c>
       <c r="I13" s="327">
-        <f t="shared" ref="I13:I15" si="7">_xlfn.XLOOKUP(G13,$D$3:$D$19,$E$3:$E$19)</f>
+        <f t="shared" ref="I13" si="7">_xlfn.XLOOKUP(G13,$D$3:$D$19,$E$3:$E$19)</f>
         <v>10000</v>
       </c>
-      <c r="J13" s="486"/>
+      <c r="J13" s="539"/>
     </row>
     <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="484"/>
+      <c r="A14" s="537"/>
       <c r="B14" s="313">
         <v>36535</v>
       </c>
@@ -11137,10 +11886,10 @@
         <f t="shared" ref="I14" si="9">_xlfn.XLOOKUP(G14,D8:D25,E8:E25,,,-1)</f>
         <v>42000</v>
       </c>
-      <c r="J14" s="486"/>
+      <c r="J14" s="539"/>
     </row>
     <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A15" s="484"/>
+      <c r="A15" s="537"/>
       <c r="B15" s="316">
         <v>36545</v>
       </c>
@@ -11164,10 +11913,10 @@
         <f t="shared" ref="I15" si="11">_xlfn.XLOOKUP(G15,$D$3:$D$19,$E$3:$E$19)</f>
         <v>20000</v>
       </c>
-      <c r="J15" s="487"/>
+      <c r="J15" s="540"/>
     </row>
     <row r="16" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="484"/>
+      <c r="A16" s="537"/>
       <c r="B16" s="316">
         <v>36529</v>
       </c>
@@ -11182,7 +11931,7 @@
       </c>
     </row>
     <row r="17" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="484"/>
+      <c r="A17" s="537"/>
       <c r="B17" s="316">
         <v>36531</v>
       </c>
@@ -11197,7 +11946,7 @@
       </c>
     </row>
     <row r="18" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="484"/>
+      <c r="A18" s="537"/>
       <c r="B18" s="316">
         <v>36535</v>
       </c>
@@ -11212,7 +11961,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="484"/>
+      <c r="A19" s="537"/>
       <c r="B19" s="316">
         <v>36531</v>
       </c>
@@ -11466,25 +12215,25 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="36" x14ac:dyDescent="0.3">
-      <c r="A25" s="484">
+      <c r="A25" s="537">
         <v>2</v>
       </c>
-      <c r="B25" s="484"/>
-      <c r="C25" s="484"/>
-      <c r="D25" s="484"/>
-      <c r="E25" s="484"/>
-      <c r="F25" s="484"/>
-      <c r="G25" s="484"/>
-      <c r="H25" s="484"/>
-      <c r="I25" s="484"/>
-      <c r="J25" s="484"/>
-      <c r="K25" s="484"/>
-      <c r="L25" s="484"/>
-      <c r="M25" s="484"/>
-      <c r="N25" s="484"/>
-      <c r="O25" s="484"/>
-      <c r="P25" s="484"/>
-      <c r="Q25" s="484"/>
+      <c r="B25" s="537"/>
+      <c r="C25" s="537"/>
+      <c r="D25" s="537"/>
+      <c r="E25" s="537"/>
+      <c r="F25" s="537"/>
+      <c r="G25" s="537"/>
+      <c r="H25" s="537"/>
+      <c r="I25" s="537"/>
+      <c r="J25" s="537"/>
+      <c r="K25" s="537"/>
+      <c r="L25" s="537"/>
+      <c r="M25" s="537"/>
+      <c r="N25" s="537"/>
+      <c r="O25" s="537"/>
+      <c r="P25" s="537"/>
+      <c r="Q25" s="537"/>
       <c r="R25" s="305"/>
       <c r="S25" s="305"/>
     </row>
@@ -11499,7 +12248,7 @@
       <c r="D27" s="338" t="s">
         <v>403</v>
       </c>
-      <c r="E27" s="488" t="s">
+      <c r="E27" s="541" t="s">
         <v>412</v>
       </c>
     </row>
@@ -11516,7 +12265,7 @@
         <f>_xlfn.XLOOKUP(B28,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
         <v>2000</v>
       </c>
-      <c r="E28" s="488"/>
+      <c r="E28" s="541"/>
     </row>
     <row r="29" spans="1:19" ht="36" x14ac:dyDescent="0.3">
       <c r="A29" s="320" t="s">
@@ -11533,7 +12282,7 @@
         <f>_xlfn.XLOOKUP(B29,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
         <v>2000</v>
       </c>
-      <c r="E29" s="488"/>
+      <c r="E29" s="541"/>
     </row>
     <row r="30" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A30" s="305"/>
@@ -11545,10 +12294,10 @@
         <v>South</v>
       </c>
       <c r="D30" s="341">
-        <f t="shared" ref="D30:D37" si="13">_xlfn.XLOOKUP(B30,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
+        <f t="shared" ref="D30" si="13">_xlfn.XLOOKUP(B30,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
         <v>30000</v>
       </c>
-      <c r="E30" s="488"/>
+      <c r="E30" s="541"/>
     </row>
     <row r="31" spans="1:19" ht="36" x14ac:dyDescent="0.3">
       <c r="A31" s="320" t="s">
@@ -11562,10 +12311,10 @@
         <v>West</v>
       </c>
       <c r="D31" s="341">
-        <f t="shared" ref="D31:D37" si="15">_xlfn.XLOOKUP(B31,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
+        <f t="shared" ref="D31" si="15">_xlfn.XLOOKUP(B31,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
         <v>30000</v>
       </c>
-      <c r="E31" s="488"/>
+      <c r="E31" s="541"/>
     </row>
     <row r="32" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A32" s="305"/>
@@ -11577,10 +12326,10 @@
         <v>South</v>
       </c>
       <c r="D32" s="341">
-        <f t="shared" ref="D32:D37" si="16">_xlfn.XLOOKUP(B32,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
+        <f t="shared" ref="D32" si="16">_xlfn.XLOOKUP(B32,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
         <v>20000</v>
       </c>
-      <c r="E32" s="488"/>
+      <c r="E32" s="541"/>
     </row>
     <row r="33" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A33" s="305"/>
@@ -11592,10 +12341,10 @@
         <v>West</v>
       </c>
       <c r="D33" s="341">
-        <f t="shared" ref="D33:D37" si="18">_xlfn.XLOOKUP(B33,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
+        <f t="shared" ref="D33" si="18">_xlfn.XLOOKUP(B33,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
         <v>16000</v>
       </c>
-      <c r="E33" s="488"/>
+      <c r="E33" s="541"/>
     </row>
     <row r="34" spans="1:10" ht="36" x14ac:dyDescent="0.3">
       <c r="A34" s="305"/>
@@ -11607,10 +12356,10 @@
         <v>Not present in the data</v>
       </c>
       <c r="D34" s="341" t="str">
-        <f t="shared" ref="D34:D37" si="19">_xlfn.XLOOKUP(B34,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
+        <f t="shared" ref="D34" si="19">_xlfn.XLOOKUP(B34,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
         <v>Not found in data</v>
       </c>
-      <c r="E34" s="488"/>
+      <c r="E34" s="541"/>
     </row>
     <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A35" s="305"/>
@@ -11622,10 +12371,10 @@
         <v>Not Present in data</v>
       </c>
       <c r="D35" s="341" t="str">
-        <f t="shared" ref="D35:D37" si="20">_xlfn.XLOOKUP(B35,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
+        <f t="shared" ref="D35" si="20">_xlfn.XLOOKUP(B35,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
         <v>Not found in data</v>
       </c>
-      <c r="E35" s="488"/>
+      <c r="E35" s="541"/>
     </row>
     <row r="36" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A36" s="305"/>
@@ -11637,10 +12386,10 @@
         <v>North</v>
       </c>
       <c r="D36" s="341">
-        <f t="shared" ref="D36:D37" si="21">_xlfn.XLOOKUP(B36,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
+        <f t="shared" ref="D36" si="21">_xlfn.XLOOKUP(B36,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
         <v>20000</v>
       </c>
-      <c r="E36" s="488"/>
+      <c r="E36" s="541"/>
     </row>
     <row r="37" spans="1:10" ht="36" x14ac:dyDescent="0.3">
       <c r="A37" s="320" t="s">
@@ -11657,10 +12406,10 @@
         <f t="shared" ref="D37" si="23">_xlfn.XLOOKUP(B37,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
         <v>20000</v>
       </c>
-      <c r="E37" s="488"/>
+      <c r="E37" s="541"/>
     </row>
     <row r="42" spans="1:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="A42" s="482">
+      <c r="A42" s="535">
         <v>3</v>
       </c>
       <c r="B42" s="343" t="s">
@@ -11677,7 +12426,7 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A43" s="482"/>
+      <c r="A43" s="535"/>
       <c r="B43" s="345" t="s">
         <v>139</v>
       </c>
@@ -11692,7 +12441,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A44" s="482"/>
+      <c r="A44" s="535"/>
       <c r="B44" s="345" t="s">
         <v>139</v>
       </c>
@@ -11707,7 +12456,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A45" s="482"/>
+      <c r="A45" s="535"/>
       <c r="B45" s="345" t="s">
         <v>399</v>
       </c>
@@ -11722,7 +12471,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="A46" s="482"/>
+      <c r="A46" s="535"/>
       <c r="B46" s="345" t="s">
         <v>399</v>
       </c>
@@ -11745,12 +12494,12 @@
       <c r="I46" s="350" t="s">
         <v>396</v>
       </c>
-      <c r="J46" s="489" t="s">
+      <c r="J46" s="542" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A47" s="482"/>
+      <c r="A47" s="535"/>
       <c r="B47" s="346" t="s">
         <v>415</v>
       </c>
@@ -11775,10 +12524,10 @@
         <f>_xlfn.XLOOKUP(G47,B43:B58,D43:D58,"Not present in data")</f>
         <v>East</v>
       </c>
-      <c r="J47" s="490"/>
+      <c r="J47" s="543"/>
     </row>
     <row r="48" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A48" s="482"/>
+      <c r="A48" s="535"/>
       <c r="B48" s="346" t="s">
         <v>416</v>
       </c>
@@ -11796,17 +12545,17 @@
         <v>72</v>
       </c>
       <c r="H48" s="340">
-        <f t="shared" ref="H48:H52" si="24">_xlfn.XLOOKUP(G48,$B$42:$B$58,$C$42:$C$58,"Not Found in data",2)</f>
+        <f t="shared" ref="H48" si="24">_xlfn.XLOOKUP(G48,$B$42:$B$58,$C$42:$C$58,"Not Found in data",2)</f>
         <v>36542</v>
       </c>
       <c r="I48" s="340" t="str">
         <f>_xlfn.XLOOKUP(G48,$B$43:$B$58,$D$43:$D$58,"Not found in data")</f>
         <v>East</v>
       </c>
-      <c r="J48" s="490"/>
+      <c r="J48" s="543"/>
     </row>
     <row r="49" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="482"/>
+      <c r="A49" s="535"/>
       <c r="B49" s="345" t="s">
         <v>405</v>
       </c>
@@ -11833,10 +12582,10 @@
         <f>_xlfn.XLOOKUP("*"&amp;G49&amp;"*",B45:B60,D45:D60,"Not present in data",2)</f>
         <v>North</v>
       </c>
-      <c r="J49" s="490"/>
+      <c r="J49" s="543"/>
     </row>
     <row r="50" spans="1:11" ht="38.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="482"/>
+      <c r="A50" s="535"/>
       <c r="B50" s="345" t="s">
         <v>405</v>
       </c>
@@ -11863,10 +12612,10 @@
         <f>_xlfn.XLOOKUP("*"&amp;G50&amp;"*",B46:B61,D46:D61,"Not present in data",2,-1)</f>
         <v>East</v>
       </c>
-      <c r="J50" s="490"/>
+      <c r="J50" s="543"/>
     </row>
     <row r="51" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="482"/>
+      <c r="A51" s="535"/>
       <c r="B51" s="345" t="s">
         <v>397</v>
       </c>
@@ -11893,10 +12642,10 @@
         <f>_xlfn.XLOOKUP("*"&amp;G51&amp;"*",B47:B62,D47:D62,"Not present in data",2)</f>
         <v>North</v>
       </c>
-      <c r="J51" s="490"/>
+      <c r="J51" s="543"/>
     </row>
     <row r="52" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="482"/>
+      <c r="A52" s="535"/>
       <c r="B52" s="345" t="s">
         <v>406</v>
       </c>
@@ -11923,10 +12672,10 @@
         <f>_xlfn.XLOOKUP("*"&amp;G52&amp;"*",B48:B63,D48:D63,"Not present in data",2,-1)</f>
         <v>West</v>
       </c>
-      <c r="J52" s="491"/>
+      <c r="J52" s="544"/>
     </row>
     <row r="53" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="A53" s="482"/>
+      <c r="A53" s="535"/>
       <c r="B53" s="345" t="s">
         <v>72</v>
       </c>
@@ -11941,7 +12690,7 @@
       </c>
     </row>
     <row r="54" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="A54" s="482"/>
+      <c r="A54" s="535"/>
       <c r="B54" s="345" t="s">
         <v>72</v>
       </c>
@@ -11956,7 +12705,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="21" x14ac:dyDescent="0.3">
-      <c r="A55" s="482"/>
+      <c r="A55" s="535"/>
       <c r="B55" s="346" t="s">
         <v>401</v>
       </c>
@@ -11982,12 +12731,12 @@
       <c r="J55" s="350" t="s">
         <v>403</v>
       </c>
-      <c r="K55" s="492" t="s">
+      <c r="K55" s="545" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="482"/>
+      <c r="A56" s="535"/>
       <c r="B56" s="346" t="s">
         <v>417</v>
       </c>
@@ -12014,10 +12763,10 @@
       <c r="J56" s="355">
         <v>4000</v>
       </c>
-      <c r="K56" s="492"/>
+      <c r="K56" s="545"/>
     </row>
     <row r="57" spans="1:11" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="482"/>
+      <c r="A57" s="535"/>
       <c r="B57" s="348" t="s">
         <v>398</v>
       </c>
@@ -12044,10 +12793,10 @@
       <c r="J57" s="355">
         <v>8000</v>
       </c>
-      <c r="K57" s="492"/>
+      <c r="K57" s="545"/>
     </row>
     <row r="58" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="482"/>
+      <c r="A58" s="535"/>
       <c r="B58" s="349" t="s">
         <v>402</v>
       </c>
@@ -12076,7 +12825,7 @@
       <c r="J58" s="355">
         <v>16000</v>
       </c>
-      <c r="K58" s="492"/>
+      <c r="K58" s="545"/>
     </row>
     <row r="59" spans="1:11" ht="38.4" x14ac:dyDescent="0.3">
       <c r="F59" s="352" t="s">
@@ -12095,7 +12844,7 @@
       <c r="J59" s="355">
         <v>18000</v>
       </c>
-      <c r="K59" s="492"/>
+      <c r="K59" s="545"/>
     </row>
     <row r="60" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
       <c r="F60" s="352" t="s">
@@ -12114,7 +12863,7 @@
       <c r="J60" s="355">
         <v>20000</v>
       </c>
-      <c r="K60" s="492"/>
+      <c r="K60" s="545"/>
     </row>
     <row r="61" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
       <c r="F61" s="352" t="s">
@@ -12133,16 +12882,16 @@
       <c r="J61" s="355">
         <v>42000</v>
       </c>
-      <c r="K61" s="492"/>
+      <c r="K61" s="545"/>
     </row>
     <row r="67" spans="1:10" ht="21" x14ac:dyDescent="0.3">
       <c r="A67" s="305"/>
       <c r="B67" s="305"/>
-      <c r="C67" s="479" t="s">
+      <c r="C67" s="532" t="s">
         <v>422</v>
       </c>
-      <c r="D67" s="480"/>
-      <c r="E67" s="481"/>
+      <c r="D67" s="533"/>
+      <c r="E67" s="534"/>
       <c r="G67" s="362" t="s">
         <v>425</v>
       </c>
@@ -12152,7 +12901,7 @@
       <c r="I67" s="363" t="s">
         <v>122</v>
       </c>
-      <c r="J67" s="483" t="s">
+      <c r="J67" s="536" t="s">
         <v>427</v>
       </c>
     </row>
@@ -12181,10 +12930,10 @@
         <f t="array" ref="I68">_xlfn.XLOOKUP(G68,$B$68:$B$82,_xlfn.XLOOKUP(H68,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>40000</v>
       </c>
-      <c r="J68" s="483"/>
+      <c r="J68" s="536"/>
     </row>
     <row r="69" spans="1:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="A69" s="482">
+      <c r="A69" s="535">
         <v>4</v>
       </c>
       <c r="B69" s="345" t="s">
@@ -12210,10 +12959,10 @@
         <f t="array" ref="I69">_xlfn.XLOOKUP(G69,$B$68:$B$82,_xlfn.XLOOKUP(H69,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>57000</v>
       </c>
-      <c r="J69" s="483"/>
+      <c r="J69" s="536"/>
     </row>
     <row r="70" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A70" s="482"/>
+      <c r="A70" s="535"/>
       <c r="B70" s="345" t="s">
         <v>139</v>
       </c>
@@ -12237,10 +12986,10 @@
         <f t="array" ref="I70">_xlfn.XLOOKUP(G70,$B$68:$B$82,_xlfn.XLOOKUP(H70,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>8000</v>
       </c>
-      <c r="J70" s="483"/>
+      <c r="J70" s="536"/>
     </row>
     <row r="71" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A71" s="482"/>
+      <c r="A71" s="535"/>
       <c r="B71" s="346" t="s">
         <v>399</v>
       </c>
@@ -12264,10 +13013,10 @@
         <f t="array" ref="I71">_xlfn.XLOOKUP(G71,$B$68:$B$82,_xlfn.XLOOKUP(H71,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>78000</v>
       </c>
-      <c r="J71" s="483"/>
+      <c r="J71" s="536"/>
     </row>
     <row r="72" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A72" s="482"/>
+      <c r="A72" s="535"/>
       <c r="B72" s="346" t="s">
         <v>399</v>
       </c>
@@ -12291,10 +13040,10 @@
         <f t="array" ref="I72">_xlfn.XLOOKUP(G72,$B$68:$B$82,_xlfn.XLOOKUP(H72,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>35000</v>
       </c>
-      <c r="J72" s="483"/>
+      <c r="J72" s="536"/>
     </row>
     <row r="73" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A73" s="482"/>
+      <c r="A73" s="535"/>
       <c r="B73" s="345" t="s">
         <v>423</v>
       </c>
@@ -12318,10 +13067,10 @@
         <f t="array" ref="I73">_xlfn.XLOOKUP(G73,$B$68:$B$82,_xlfn.XLOOKUP(H73,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>42000</v>
       </c>
-      <c r="J73" s="483"/>
+      <c r="J73" s="536"/>
     </row>
     <row r="74" spans="1:10" ht="36" x14ac:dyDescent="0.3">
-      <c r="A74" s="482"/>
+      <c r="A74" s="535"/>
       <c r="B74" s="345" t="s">
         <v>424</v>
       </c>
@@ -12345,10 +13094,10 @@
         <f t="array" ref="I74">_xlfn.XLOOKUP(G74,$B$68:$B$82,_xlfn.XLOOKUP(H74,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>80000</v>
       </c>
-      <c r="J74" s="483"/>
+      <c r="J74" s="536"/>
     </row>
     <row r="75" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A75" s="482"/>
+      <c r="A75" s="535"/>
       <c r="B75" s="346" t="s">
         <v>405</v>
       </c>
@@ -12366,7 +13115,7 @@
       <c r="H75" s="360"/>
     </row>
     <row r="76" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A76" s="482"/>
+      <c r="A76" s="535"/>
       <c r="B76" s="346" t="s">
         <v>405</v>
       </c>
@@ -12384,7 +13133,7 @@
       <c r="H76" s="360"/>
     </row>
     <row r="77" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A77" s="482"/>
+      <c r="A77" s="535"/>
       <c r="B77" s="345" t="s">
         <v>397</v>
       </c>
@@ -12402,7 +13151,7 @@
       <c r="H77" s="360"/>
     </row>
     <row r="78" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A78" s="482"/>
+      <c r="A78" s="535"/>
       <c r="B78" s="346" t="s">
         <v>406</v>
       </c>
@@ -12420,7 +13169,7 @@
       <c r="H78" s="360"/>
     </row>
     <row r="79" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A79" s="482"/>
+      <c r="A79" s="535"/>
       <c r="B79" s="346" t="s">
         <v>72</v>
       </c>
@@ -12438,7 +13187,7 @@
       <c r="H79" s="360"/>
     </row>
     <row r="80" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A80" s="482"/>
+      <c r="A80" s="535"/>
       <c r="B80" s="346" t="s">
         <v>72</v>
       </c>
@@ -12456,7 +13205,7 @@
       <c r="H80" s="360"/>
     </row>
     <row r="81" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A81" s="482"/>
+      <c r="A81" s="535"/>
       <c r="B81" s="345" t="s">
         <v>401</v>
       </c>
@@ -12474,7 +13223,7 @@
       <c r="H81" s="360"/>
     </row>
     <row r="82" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A82" s="482"/>
+      <c r="A82" s="535"/>
       <c r="B82" s="345" t="s">
         <v>398</v>
       </c>
@@ -12518,6 +13267,2127 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD521CD-765E-40B8-9285-A8DBFA6D8FA1}">
+  <dimension ref="B2:M18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="42.77734375" customWidth="1"/>
+    <col min="8" max="8" width="15.77734375" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="21.21875" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="B2" s="406" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="406" t="s">
+        <v>396</v>
+      </c>
+      <c r="D2" s="406" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="406" t="s">
+        <v>403</v>
+      </c>
+      <c r="G2" s="400" t="s">
+        <v>404</v>
+      </c>
+      <c r="H2" s="408" t="s">
+        <v>397</v>
+      </c>
+      <c r="I2" s="408" t="s">
+        <v>401</v>
+      </c>
+      <c r="J2" s="408" t="s">
+        <v>405</v>
+      </c>
+      <c r="K2" s="408" t="s">
+        <v>402</v>
+      </c>
+      <c r="L2" s="408" t="s">
+        <v>72</v>
+      </c>
+      <c r="M2" s="409"/>
+    </row>
+    <row r="3" spans="2:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="B3" s="410">
+        <v>36533</v>
+      </c>
+      <c r="C3" s="410" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="411" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="412">
+        <v>2000</v>
+      </c>
+      <c r="G3" s="413"/>
+      <c r="H3" s="413"/>
+      <c r="I3" s="413"/>
+      <c r="J3" s="413"/>
+      <c r="K3" s="413"/>
+      <c r="L3" s="413"/>
+      <c r="M3" s="409"/>
+    </row>
+    <row r="4" spans="2:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="B4" s="410">
+        <v>36531</v>
+      </c>
+      <c r="C4" s="410" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="414" t="s">
+        <v>397</v>
+      </c>
+      <c r="E4" s="412">
+        <v>4000</v>
+      </c>
+      <c r="G4" s="400" t="s">
+        <v>438</v>
+      </c>
+      <c r="H4" s="413">
+        <f>MATCH(H2,D3:D16,0)</f>
+        <v>2</v>
+      </c>
+      <c r="I4" s="413">
+        <f>MATCH(I2,D3:D16,1)</f>
+        <v>7</v>
+      </c>
+      <c r="J4" s="413">
+        <f>MATCH(J2,D3:D16,0)</f>
+        <v>10</v>
+      </c>
+      <c r="K4" s="413">
+        <f>MATCH(J2,D3:D16,0)</f>
+        <v>10</v>
+      </c>
+      <c r="L4" s="413">
+        <f>MATCH(L2,D3:D16,1)</f>
+        <v>3</v>
+      </c>
+      <c r="M4" s="409"/>
+    </row>
+    <row r="5" spans="2:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="B5" s="410">
+        <v>36542</v>
+      </c>
+      <c r="C5" s="410" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="414" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="412">
+        <v>6000</v>
+      </c>
+      <c r="G5" s="415"/>
+      <c r="H5" s="415"/>
+      <c r="I5" s="415"/>
+      <c r="J5" s="415"/>
+      <c r="K5" s="415"/>
+      <c r="L5" s="415"/>
+      <c r="M5" s="409"/>
+    </row>
+    <row r="6" spans="2:13" ht="21" x14ac:dyDescent="0.3">
+      <c r="B6" s="410">
+        <v>36531</v>
+      </c>
+      <c r="C6" s="410" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="416" t="s">
+        <v>398</v>
+      </c>
+      <c r="E6" s="412">
+        <v>10000</v>
+      </c>
+      <c r="G6" s="415"/>
+      <c r="H6" s="415"/>
+      <c r="I6" s="415"/>
+      <c r="J6" s="415"/>
+      <c r="K6" s="415"/>
+      <c r="L6" s="415"/>
+      <c r="M6" s="409"/>
+    </row>
+    <row r="7" spans="2:13" ht="21" x14ac:dyDescent="0.3">
+      <c r="B7" s="410">
+        <v>36526</v>
+      </c>
+      <c r="C7" s="410" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="414" t="s">
+        <v>399</v>
+      </c>
+      <c r="E7" s="412">
+        <v>14000</v>
+      </c>
+      <c r="G7" s="417" t="s">
+        <v>439</v>
+      </c>
+      <c r="H7" s="418">
+        <v>2</v>
+      </c>
+      <c r="I7" s="418">
+        <v>4</v>
+      </c>
+      <c r="J7" s="418">
+        <v>1</v>
+      </c>
+      <c r="K7" s="418">
+        <v>3</v>
+      </c>
+      <c r="L7" s="415"/>
+      <c r="M7" s="409"/>
+    </row>
+    <row r="8" spans="2:13" ht="21" x14ac:dyDescent="0.3">
+      <c r="B8" s="410">
+        <v>36528</v>
+      </c>
+      <c r="C8" s="410" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="411" t="s">
+        <v>400</v>
+      </c>
+      <c r="E8" s="412">
+        <v>16000</v>
+      </c>
+      <c r="G8" s="417" t="s">
+        <v>440</v>
+      </c>
+      <c r="H8" s="418">
+        <v>3</v>
+      </c>
+      <c r="I8" s="418">
+        <v>9</v>
+      </c>
+      <c r="J8" s="418">
+        <v>6</v>
+      </c>
+      <c r="K8" s="418">
+        <v>5</v>
+      </c>
+      <c r="L8" s="415"/>
+      <c r="M8" s="409"/>
+    </row>
+    <row r="9" spans="2:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="B9" s="410">
+        <v>36545</v>
+      </c>
+      <c r="C9" s="411" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="414" t="s">
+        <v>401</v>
+      </c>
+      <c r="E9" s="412">
+        <v>20000</v>
+      </c>
+      <c r="G9" s="413"/>
+      <c r="H9" s="413"/>
+      <c r="I9" s="413"/>
+      <c r="J9" s="413"/>
+      <c r="K9" s="413"/>
+      <c r="L9" s="415"/>
+      <c r="M9" s="409"/>
+    </row>
+    <row r="10" spans="2:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="B10" s="410">
+        <v>36535</v>
+      </c>
+      <c r="C10" s="410" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="414" t="s">
+        <v>402</v>
+      </c>
+      <c r="E10" s="412">
+        <v>25000</v>
+      </c>
+      <c r="G10" s="400" t="s">
+        <v>441</v>
+      </c>
+      <c r="H10" s="419" cm="1">
+        <f t="array" ref="H10">INDEX(B2:B16,H7)</f>
+        <v>36533</v>
+      </c>
+      <c r="I10" s="419" cm="1">
+        <f t="array" ref="I10">INDEX(B2:B16,I7)</f>
+        <v>36542</v>
+      </c>
+      <c r="J10" s="419" t="str" cm="1">
+        <f t="array" ref="J10">INDEX(B2:B16,J7)</f>
+        <v>Date</v>
+      </c>
+      <c r="K10" s="419" cm="1">
+        <f t="array" ref="K10">INDEX(E2:E16,K7)</f>
+        <v>4000</v>
+      </c>
+      <c r="L10" s="415"/>
+      <c r="M10" s="409"/>
+    </row>
+    <row r="11" spans="2:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="B11" s="410">
+        <v>36540</v>
+      </c>
+      <c r="C11" s="410" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="411" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="412">
+        <v>28000</v>
+      </c>
+      <c r="G11" s="400" t="s">
+        <v>441</v>
+      </c>
+      <c r="H11" s="413" t="str" cm="1">
+        <f t="array" ref="H11">INDEX($C$3:$C$16,H8)</f>
+        <v>West</v>
+      </c>
+      <c r="I11" s="413" t="str" cm="1">
+        <f t="array" ref="I11">INDEX($C$3:$C$16,I8)</f>
+        <v>South</v>
+      </c>
+      <c r="J11" s="413" t="str" cm="1">
+        <f t="array" ref="J11">INDEX($C$3:$C$16,J8)</f>
+        <v>North</v>
+      </c>
+      <c r="K11" s="413" t="str" cm="1">
+        <f t="array" ref="K11">INDEX($C$3:$C$16,K8)</f>
+        <v>North</v>
+      </c>
+      <c r="L11" s="415"/>
+      <c r="M11" s="409"/>
+    </row>
+    <row r="12" spans="2:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="B12" s="410">
+        <v>36538</v>
+      </c>
+      <c r="C12" s="410" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="414" t="s">
+        <v>405</v>
+      </c>
+      <c r="E12" s="412">
+        <v>30000</v>
+      </c>
+      <c r="G12" s="400" t="s">
+        <v>442</v>
+      </c>
+      <c r="H12" s="413" t="str" cm="1">
+        <f t="array" ref="H12">INDEX(B3:E16,H8,H7)</f>
+        <v>West</v>
+      </c>
+      <c r="I12" s="420" cm="1">
+        <f t="array" ref="I12">INDEX($B$3:$E$16,I8,I7)</f>
+        <v>28000</v>
+      </c>
+      <c r="J12" s="420" cm="1">
+        <f t="array" ref="J12">INDEX($B$3:$E$16,J8,J7)</f>
+        <v>36528</v>
+      </c>
+      <c r="K12" s="420" t="str" cm="1">
+        <f t="array" ref="K12">INDEX($B$3:$E$16,K8,K7)</f>
+        <v>Beard trimmer</v>
+      </c>
+      <c r="L12" s="415"/>
+      <c r="M12" s="409"/>
+    </row>
+    <row r="13" spans="2:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="B13" s="410">
+        <v>36538</v>
+      </c>
+      <c r="C13" s="410" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="411" t="s">
+        <v>406</v>
+      </c>
+      <c r="E13" s="412">
+        <v>20000</v>
+      </c>
+      <c r="G13" s="407"/>
+      <c r="H13" s="407"/>
+      <c r="I13" s="407"/>
+      <c r="J13" s="407"/>
+      <c r="K13" s="407"/>
+      <c r="L13" s="407"/>
+      <c r="M13" s="409"/>
+    </row>
+    <row r="14" spans="2:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="B14" s="410">
+        <v>36536</v>
+      </c>
+      <c r="C14" s="410" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="411" t="s">
+        <v>399</v>
+      </c>
+      <c r="E14" s="412">
+        <v>36000</v>
+      </c>
+      <c r="G14" s="407"/>
+      <c r="H14" s="407"/>
+      <c r="I14" s="407"/>
+      <c r="J14" s="407"/>
+      <c r="K14" s="407"/>
+      <c r="L14" s="407"/>
+      <c r="M14" s="409"/>
+    </row>
+    <row r="15" spans="2:13" ht="21" x14ac:dyDescent="0.3">
+      <c r="B15" s="410">
+        <v>36532</v>
+      </c>
+      <c r="C15" s="410" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="411" t="s">
+        <v>405</v>
+      </c>
+      <c r="E15" s="412">
+        <v>38000</v>
+      </c>
+      <c r="G15" s="421" t="str">
+        <f>INDEX(C3:C16,MATCH(H2,D3:D15,0))</f>
+        <v>East</v>
+      </c>
+      <c r="H15" s="546" t="s">
+        <v>443</v>
+      </c>
+      <c r="I15" s="407"/>
+      <c r="J15" s="407"/>
+      <c r="K15" s="407"/>
+      <c r="L15" s="407"/>
+      <c r="M15" s="409"/>
+    </row>
+    <row r="16" spans="2:13" ht="21" x14ac:dyDescent="0.3">
+      <c r="B16" s="410">
+        <v>36547</v>
+      </c>
+      <c r="C16" s="411" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="414" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="412">
+        <v>40000</v>
+      </c>
+      <c r="G16" s="421" t="str">
+        <f>INDEX(C3:C16,MATCH(D6,D3:D16,0))</f>
+        <v>East</v>
+      </c>
+      <c r="H16" s="547"/>
+      <c r="I16" s="407"/>
+      <c r="J16" s="407"/>
+      <c r="K16" s="407"/>
+      <c r="L16" s="407"/>
+      <c r="M16" s="409"/>
+    </row>
+    <row r="17" spans="7:13" ht="21" x14ac:dyDescent="0.3">
+      <c r="G17" s="421" t="str">
+        <f>INDEX($C$3:$C$16, MATCH(J2, $D$3:$D$16, 0))</f>
+        <v>South</v>
+      </c>
+      <c r="H17" s="547"/>
+      <c r="I17" s="422"/>
+      <c r="J17" s="422"/>
+      <c r="K17" s="422"/>
+      <c r="L17" s="422"/>
+      <c r="M17" s="399"/>
+    </row>
+    <row r="18" spans="7:13" ht="21" x14ac:dyDescent="0.3">
+      <c r="G18" s="421" t="str">
+        <f>INDEX($C$3:$C$16, MATCH(K2, $D$3:$D$16, 0))</f>
+        <v>North</v>
+      </c>
+      <c r="H18" s="548"/>
+      <c r="I18" s="422"/>
+      <c r="J18" s="422"/>
+      <c r="K18" s="422"/>
+      <c r="L18" s="422"/>
+      <c r="M18" s="399"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H15:H18"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2" xr:uid="{0186CE42-ADC9-4858-A35D-F9D6871D32FA}">
+      <formula1>$D$3:$D$16</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C7DC0A-C9A3-4F87-8446-63CCC93A49EA}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.109375" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="424" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="424" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="424" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="425" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="437"/>
+      <c r="F1" s="441"/>
+      <c r="G1" s="444"/>
+      <c r="H1" s="442" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1" s="402"/>
+      <c r="J1" s="549" t="s">
+        <v>444</v>
+      </c>
+      <c r="K1" s="403"/>
+      <c r="L1" s="403"/>
+      <c r="M1" s="403"/>
+    </row>
+    <row r="2" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="426" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="427">
+        <v>5000</v>
+      </c>
+      <c r="C2" s="428">
+        <v>45359</v>
+      </c>
+      <c r="D2" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" s="438">
+        <v>60</v>
+      </c>
+      <c r="G2" s="443"/>
+      <c r="H2" s="423"/>
+      <c r="I2" s="402"/>
+      <c r="J2" s="549"/>
+      <c r="K2" s="403"/>
+      <c r="L2" s="403"/>
+      <c r="M2" s="403"/>
+    </row>
+    <row r="3" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="426" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="427">
+        <v>6000</v>
+      </c>
+      <c r="C3" s="428">
+        <v>45297</v>
+      </c>
+      <c r="D3" s="429" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="438">
+        <v>90</v>
+      </c>
+      <c r="G3" s="436"/>
+      <c r="H3" s="423" t="s">
+        <v>445</v>
+      </c>
+      <c r="I3" s="402" t="s">
+        <v>128</v>
+      </c>
+      <c r="J3" s="549"/>
+      <c r="K3" s="403"/>
+      <c r="L3" s="403"/>
+      <c r="M3" s="403"/>
+    </row>
+    <row r="4" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="426" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="427">
+        <v>7000</v>
+      </c>
+      <c r="C4" s="428">
+        <v>45308</v>
+      </c>
+      <c r="D4" s="429" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="439">
+        <v>50</v>
+      </c>
+      <c r="G4" s="436"/>
+      <c r="H4" s="423"/>
+      <c r="I4" s="402"/>
+      <c r="J4" s="549"/>
+      <c r="K4" s="403"/>
+      <c r="L4" s="403"/>
+      <c r="M4" s="403"/>
+    </row>
+    <row r="5" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="426" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="427">
+        <v>8000</v>
+      </c>
+      <c r="C5" s="428">
+        <v>45392</v>
+      </c>
+      <c r="D5" s="429" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="440"/>
+      <c r="G5" s="445"/>
+      <c r="H5" s="423" t="s">
+        <v>446</v>
+      </c>
+      <c r="I5" s="402"/>
+      <c r="J5" s="549"/>
+      <c r="K5" s="403"/>
+      <c r="L5" s="403"/>
+      <c r="M5" s="403"/>
+    </row>
+    <row r="6" spans="1:13" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="426" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="427">
+        <v>9000</v>
+      </c>
+      <c r="C6" s="428">
+        <v>45297</v>
+      </c>
+      <c r="D6" s="429" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="446"/>
+    </row>
+    <row r="7" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="426" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="427">
+        <v>10000</v>
+      </c>
+      <c r="C7" s="428">
+        <v>45292</v>
+      </c>
+      <c r="D7" s="429" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="426" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="427">
+        <v>10000</v>
+      </c>
+      <c r="C8" s="428">
+        <v>45313</v>
+      </c>
+      <c r="D8" s="429" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="426" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="427">
+        <v>15000</v>
+      </c>
+      <c r="C9" s="428">
+        <v>45415</v>
+      </c>
+      <c r="D9" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="402"/>
+      <c r="G9" s="402"/>
+      <c r="H9" s="402"/>
+      <c r="I9" s="402"/>
+      <c r="J9" s="550" t="s">
+        <v>447</v>
+      </c>
+      <c r="K9" s="404"/>
+      <c r="L9" s="405"/>
+      <c r="M9" s="401"/>
+    </row>
+    <row r="10" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="426" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="427">
+        <v>18000</v>
+      </c>
+      <c r="C10" s="428">
+        <v>45310</v>
+      </c>
+      <c r="D10" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" s="402"/>
+      <c r="G10" s="402"/>
+      <c r="H10" s="402"/>
+      <c r="I10" s="402"/>
+      <c r="J10" s="550"/>
+      <c r="K10" s="404"/>
+      <c r="L10" s="405"/>
+      <c r="M10" s="401"/>
+    </row>
+    <row r="11" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="426" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="427">
+        <v>25000</v>
+      </c>
+      <c r="C11" s="428">
+        <v>45493</v>
+      </c>
+      <c r="D11" s="429" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" s="402"/>
+      <c r="G11" s="402"/>
+      <c r="H11" s="402"/>
+      <c r="I11" s="402"/>
+      <c r="J11" s="550"/>
+      <c r="K11" s="404"/>
+      <c r="L11" s="405"/>
+      <c r="M11" s="401"/>
+    </row>
+    <row r="12" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="426" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="427">
+        <v>25000</v>
+      </c>
+      <c r="C12" s="428">
+        <v>45301</v>
+      </c>
+      <c r="D12" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="402"/>
+      <c r="G12" s="402"/>
+      <c r="H12" s="402"/>
+      <c r="I12" s="402"/>
+      <c r="J12" s="550"/>
+      <c r="K12" s="401"/>
+      <c r="L12" s="401"/>
+      <c r="M12" s="401"/>
+    </row>
+    <row r="13" spans="1:13" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="426" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="427">
+        <v>30000</v>
+      </c>
+      <c r="C13" s="428">
+        <v>45519</v>
+      </c>
+      <c r="D13" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13" s="402"/>
+      <c r="G13" s="402"/>
+      <c r="H13" s="402"/>
+      <c r="I13" s="402"/>
+      <c r="J13" s="550"/>
+      <c r="K13" s="401"/>
+      <c r="L13" s="401"/>
+      <c r="M13" s="401"/>
+    </row>
+    <row r="14" spans="1:13" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="426" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="427">
+        <v>30000</v>
+      </c>
+      <c r="C14" s="428">
+        <v>45304</v>
+      </c>
+      <c r="D14" s="429" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="426" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="427">
+        <v>35000</v>
+      </c>
+      <c r="C15" s="428">
+        <v>45548</v>
+      </c>
+      <c r="D15" s="429" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="426" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="427">
+        <v>36000</v>
+      </c>
+      <c r="C16" s="428">
+        <v>45302</v>
+      </c>
+      <c r="D16" s="429" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="426" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="427">
+        <v>40000</v>
+      </c>
+      <c r="C17" s="428">
+        <v>45455</v>
+      </c>
+      <c r="D17" s="429" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="426" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="427">
+        <v>45000</v>
+      </c>
+      <c r="C18" s="428">
+        <v>45298</v>
+      </c>
+      <c r="D18" s="429" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="426" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" s="427">
+        <v>50000</v>
+      </c>
+      <c r="C19" s="428">
+        <v>45313</v>
+      </c>
+      <c r="D19" s="429" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="426" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="427">
+        <v>70000</v>
+      </c>
+      <c r="C20" s="430">
+        <v>45600</v>
+      </c>
+      <c r="D20" s="431" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="432" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="433">
+        <v>80000</v>
+      </c>
+      <c r="C21" s="434">
+        <v>45296</v>
+      </c>
+      <c r="D21" s="435" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="J1:J5"/>
+    <mergeCell ref="J9:J13"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation type="list" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="INCORRECT VALUE !" error="Select a region ONLY from the in-cell dropdown !" promptTitle="Use the dropdown" prompt="Please select a region from the in-cell dropdown !" sqref="H1:I5" xr:uid="{C85AC986-E5A7-45E4-A3EC-B088639F02F0}">
+      <formula1>$E$3:$E$22</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="INCORRECT VALUE !" error="Whole nos. only from 50 to100 ALLOWED !!!" promptTitle="WHOLE Numbers ONLY !!" prompt="Please enter whole nos. only from 50 to100..." sqref="F5 F1:F4 G1 G3:G5 G2" xr:uid="{0414136D-974B-4658-9715-7CDBC61DA2A3}">
+      <formula1>50</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{1357AECD-DD91-457B-95D9-E3BD469AC1CE}">
+      <formula1>50</formula1>
+      <formula2>1000</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A6D3575-B74F-40B4-A367-865D27AC6BB2}">
+  <dimension ref="A1:AH46"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="424" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="424" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="424" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="425" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="426" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="427">
+        <v>5000</v>
+      </c>
+      <c r="C2" s="428">
+        <v>45359</v>
+      </c>
+      <c r="D2" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" s="447" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="447" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="447" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" s="447" t="s">
+        <v>124</v>
+      </c>
+      <c r="N2" s="424" t="s">
+        <v>121</v>
+      </c>
+      <c r="O2" s="426" t="s">
+        <v>125</v>
+      </c>
+      <c r="P2" s="426" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q2" s="426" t="s">
+        <v>129</v>
+      </c>
+      <c r="R2" s="426" t="s">
+        <v>130</v>
+      </c>
+      <c r="S2" s="426" t="s">
+        <v>131</v>
+      </c>
+      <c r="T2" s="426" t="s">
+        <v>133</v>
+      </c>
+      <c r="U2" s="426" t="s">
+        <v>129</v>
+      </c>
+      <c r="V2" s="426" t="s">
+        <v>135</v>
+      </c>
+      <c r="W2" s="426" t="s">
+        <v>136</v>
+      </c>
+      <c r="X2" s="426" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y2" s="426" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z2" s="426" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA2" s="426" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB2" s="426" t="s">
+        <v>135</v>
+      </c>
+      <c r="AC2" s="426" t="s">
+        <v>142</v>
+      </c>
+      <c r="AD2" s="426" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE2" s="426" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF2" s="426" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG2" s="426" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH2" s="432" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="426" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="427">
+        <v>6000</v>
+      </c>
+      <c r="C3" s="428">
+        <v>45297</v>
+      </c>
+      <c r="D3" s="429" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="448" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="449">
+        <v>5000</v>
+      </c>
+      <c r="H3" s="450">
+        <v>45359</v>
+      </c>
+      <c r="I3" s="451" t="s">
+        <v>126</v>
+      </c>
+      <c r="N3" s="424" t="s">
+        <v>122</v>
+      </c>
+      <c r="O3" s="427">
+        <v>5000</v>
+      </c>
+      <c r="P3" s="427">
+        <v>6000</v>
+      </c>
+      <c r="Q3" s="427">
+        <v>7000</v>
+      </c>
+      <c r="R3" s="427">
+        <v>8000</v>
+      </c>
+      <c r="S3" s="427">
+        <v>9000</v>
+      </c>
+      <c r="T3" s="427">
+        <v>10000</v>
+      </c>
+      <c r="U3" s="427">
+        <v>10000</v>
+      </c>
+      <c r="V3" s="427">
+        <v>15000</v>
+      </c>
+      <c r="W3" s="427">
+        <v>18000</v>
+      </c>
+      <c r="X3" s="427">
+        <v>25000</v>
+      </c>
+      <c r="Y3" s="427">
+        <v>25000</v>
+      </c>
+      <c r="Z3" s="427">
+        <v>30000</v>
+      </c>
+      <c r="AA3" s="427">
+        <v>30000</v>
+      </c>
+      <c r="AB3" s="427">
+        <v>35000</v>
+      </c>
+      <c r="AC3" s="427">
+        <v>36000</v>
+      </c>
+      <c r="AD3" s="427">
+        <v>40000</v>
+      </c>
+      <c r="AE3" s="427">
+        <v>45000</v>
+      </c>
+      <c r="AF3" s="427">
+        <v>50000</v>
+      </c>
+      <c r="AG3" s="427">
+        <v>70000</v>
+      </c>
+      <c r="AH3" s="433">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="426" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="427">
+        <v>7000</v>
+      </c>
+      <c r="C4" s="428">
+        <v>45308</v>
+      </c>
+      <c r="D4" s="429" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="448" t="s">
+        <v>127</v>
+      </c>
+      <c r="G4" s="449">
+        <v>6000</v>
+      </c>
+      <c r="H4" s="450">
+        <v>45297</v>
+      </c>
+      <c r="I4" s="451" t="s">
+        <v>128</v>
+      </c>
+      <c r="N4" s="424" t="s">
+        <v>123</v>
+      </c>
+      <c r="O4" s="428">
+        <v>45359</v>
+      </c>
+      <c r="P4" s="428">
+        <v>45297</v>
+      </c>
+      <c r="Q4" s="428">
+        <v>45308</v>
+      </c>
+      <c r="R4" s="428">
+        <v>45392</v>
+      </c>
+      <c r="S4" s="428">
+        <v>45297</v>
+      </c>
+      <c r="T4" s="428">
+        <v>45292</v>
+      </c>
+      <c r="U4" s="428">
+        <v>45313</v>
+      </c>
+      <c r="V4" s="428">
+        <v>45415</v>
+      </c>
+      <c r="W4" s="428">
+        <v>45310</v>
+      </c>
+      <c r="X4" s="428">
+        <v>45493</v>
+      </c>
+      <c r="Y4" s="428">
+        <v>45301</v>
+      </c>
+      <c r="Z4" s="428">
+        <v>45519</v>
+      </c>
+      <c r="AA4" s="428">
+        <v>45304</v>
+      </c>
+      <c r="AB4" s="428">
+        <v>45548</v>
+      </c>
+      <c r="AC4" s="428">
+        <v>45302</v>
+      </c>
+      <c r="AD4" s="428">
+        <v>45455</v>
+      </c>
+      <c r="AE4" s="428">
+        <v>45298</v>
+      </c>
+      <c r="AF4" s="428">
+        <v>45313</v>
+      </c>
+      <c r="AG4" s="430">
+        <v>45600</v>
+      </c>
+      <c r="AH4" s="434">
+        <v>45296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="426" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="427">
+        <v>8000</v>
+      </c>
+      <c r="C5" s="428">
+        <v>45392</v>
+      </c>
+      <c r="D5" s="429" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="448" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="449">
+        <v>7000</v>
+      </c>
+      <c r="H5" s="450">
+        <v>45308</v>
+      </c>
+      <c r="I5" s="451" t="s">
+        <v>128</v>
+      </c>
+      <c r="N5" s="425" t="s">
+        <v>124</v>
+      </c>
+      <c r="O5" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="P5" s="429" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q5" s="429" t="s">
+        <v>128</v>
+      </c>
+      <c r="R5" s="429" t="s">
+        <v>128</v>
+      </c>
+      <c r="S5" s="429" t="s">
+        <v>132</v>
+      </c>
+      <c r="T5" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="U5" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="V5" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="W5" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="X5" s="429" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y5" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z5" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA5" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB5" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC5" s="429" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD5" s="429" t="s">
+        <v>132</v>
+      </c>
+      <c r="AE5" s="429" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF5" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="AG5" s="431" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH5" s="435" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="426" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="427">
+        <v>9000</v>
+      </c>
+      <c r="C6" s="428">
+        <v>45297</v>
+      </c>
+      <c r="D6" s="429" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6" s="448" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="449">
+        <v>8000</v>
+      </c>
+      <c r="H6" s="450">
+        <v>45392</v>
+      </c>
+      <c r="I6" s="451" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="426" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="427">
+        <v>10000</v>
+      </c>
+      <c r="C7" s="428">
+        <v>45292</v>
+      </c>
+      <c r="D7" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="448" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" s="449">
+        <v>9000</v>
+      </c>
+      <c r="H7" s="450">
+        <v>45297</v>
+      </c>
+      <c r="I7" s="451" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="426" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="427">
+        <v>10000</v>
+      </c>
+      <c r="C8" s="428">
+        <v>45313</v>
+      </c>
+      <c r="D8" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="448" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" s="449">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="450">
+        <v>45292</v>
+      </c>
+      <c r="I8" s="451" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="426" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="427">
+        <v>15000</v>
+      </c>
+      <c r="C9" s="428">
+        <v>45415</v>
+      </c>
+      <c r="D9" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="448" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="449">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="450">
+        <v>45313</v>
+      </c>
+      <c r="I9" s="451" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="426" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="427">
+        <v>18000</v>
+      </c>
+      <c r="C10" s="428">
+        <v>45310</v>
+      </c>
+      <c r="D10" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" s="448" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10" s="449">
+        <v>15000</v>
+      </c>
+      <c r="H10" s="450">
+        <v>45415</v>
+      </c>
+      <c r="I10" s="451" t="s">
+        <v>134</v>
+      </c>
+      <c r="K10" t="s">
+        <v>121</v>
+      </c>
+      <c r="L10" t="s">
+        <v>122</v>
+      </c>
+      <c r="M10" t="s">
+        <v>123</v>
+      </c>
+      <c r="N10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="426" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="427">
+        <v>25000</v>
+      </c>
+      <c r="C11" s="428">
+        <v>45493</v>
+      </c>
+      <c r="D11" s="429" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" s="448" t="s">
+        <v>136</v>
+      </c>
+      <c r="G11" s="449">
+        <v>18000</v>
+      </c>
+      <c r="H11" s="450">
+        <v>45310</v>
+      </c>
+      <c r="I11" s="451" t="s">
+        <v>134</v>
+      </c>
+      <c r="K11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L11">
+        <v>5000</v>
+      </c>
+      <c r="M11">
+        <v>45359</v>
+      </c>
+      <c r="N11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="426" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="427">
+        <v>25000</v>
+      </c>
+      <c r="C12" s="428">
+        <v>45301</v>
+      </c>
+      <c r="D12" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="448" t="s">
+        <v>136</v>
+      </c>
+      <c r="G12" s="449">
+        <v>25000</v>
+      </c>
+      <c r="H12" s="450">
+        <v>45493</v>
+      </c>
+      <c r="I12" s="451" t="s">
+        <v>132</v>
+      </c>
+      <c r="K12" t="s">
+        <v>127</v>
+      </c>
+      <c r="L12">
+        <v>6000</v>
+      </c>
+      <c r="M12">
+        <v>45297</v>
+      </c>
+      <c r="N12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="426" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="427">
+        <v>30000</v>
+      </c>
+      <c r="C13" s="428">
+        <v>45519</v>
+      </c>
+      <c r="D13" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13" s="448" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" s="449">
+        <v>25000</v>
+      </c>
+      <c r="H13" s="450">
+        <v>45301</v>
+      </c>
+      <c r="I13" s="451" t="s">
+        <v>134</v>
+      </c>
+      <c r="K13" t="s">
+        <v>129</v>
+      </c>
+      <c r="L13">
+        <v>7000</v>
+      </c>
+      <c r="M13">
+        <v>45308</v>
+      </c>
+      <c r="N13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="426" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="427">
+        <v>30000</v>
+      </c>
+      <c r="C14" s="428">
+        <v>45304</v>
+      </c>
+      <c r="D14" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="448" t="s">
+        <v>139</v>
+      </c>
+      <c r="G14" s="449">
+        <v>30000</v>
+      </c>
+      <c r="H14" s="450">
+        <v>45519</v>
+      </c>
+      <c r="I14" s="451" t="s">
+        <v>126</v>
+      </c>
+      <c r="K14" t="s">
+        <v>130</v>
+      </c>
+      <c r="L14">
+        <v>8000</v>
+      </c>
+      <c r="M14">
+        <v>45392</v>
+      </c>
+      <c r="N14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="426" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="427">
+        <v>35000</v>
+      </c>
+      <c r="C15" s="428">
+        <v>45548</v>
+      </c>
+      <c r="D15" s="429" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="448" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" s="449">
+        <v>30000</v>
+      </c>
+      <c r="H15" s="450">
+        <v>45304</v>
+      </c>
+      <c r="I15" s="451" t="s">
+        <v>126</v>
+      </c>
+      <c r="K15" t="s">
+        <v>131</v>
+      </c>
+      <c r="L15">
+        <v>9000</v>
+      </c>
+      <c r="M15">
+        <v>45297</v>
+      </c>
+      <c r="N15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="426" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="427">
+        <v>36000</v>
+      </c>
+      <c r="C16" s="428">
+        <v>45302</v>
+      </c>
+      <c r="D16" s="429" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="448" t="s">
+        <v>135</v>
+      </c>
+      <c r="G16" s="449">
+        <v>35000</v>
+      </c>
+      <c r="H16" s="450">
+        <v>45548</v>
+      </c>
+      <c r="I16" s="451" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" t="s">
+        <v>133</v>
+      </c>
+      <c r="L16">
+        <v>10000</v>
+      </c>
+      <c r="M16">
+        <v>45292</v>
+      </c>
+      <c r="N16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="426" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="427">
+        <v>40000</v>
+      </c>
+      <c r="C17" s="428">
+        <v>45455</v>
+      </c>
+      <c r="D17" s="429" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" s="448" t="s">
+        <v>142</v>
+      </c>
+      <c r="G17" s="449">
+        <v>36000</v>
+      </c>
+      <c r="H17" s="450">
+        <v>45302</v>
+      </c>
+      <c r="I17" s="451" t="s">
+        <v>132</v>
+      </c>
+      <c r="K17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L17">
+        <v>10000</v>
+      </c>
+      <c r="M17">
+        <v>45313</v>
+      </c>
+      <c r="N17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="426" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="427">
+        <v>45000</v>
+      </c>
+      <c r="C18" s="428">
+        <v>45298</v>
+      </c>
+      <c r="D18" s="429" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18" s="448" t="s">
+        <v>143</v>
+      </c>
+      <c r="G18" s="449">
+        <v>40000</v>
+      </c>
+      <c r="H18" s="450">
+        <v>45455</v>
+      </c>
+      <c r="I18" s="451" t="s">
+        <v>132</v>
+      </c>
+      <c r="K18" t="s">
+        <v>135</v>
+      </c>
+      <c r="L18">
+        <v>15000</v>
+      </c>
+      <c r="M18">
+        <v>45415</v>
+      </c>
+      <c r="N18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="426" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" s="427">
+        <v>50000</v>
+      </c>
+      <c r="C19" s="428">
+        <v>45313</v>
+      </c>
+      <c r="D19" s="429" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="448" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="449">
+        <v>45000</v>
+      </c>
+      <c r="H19" s="450">
+        <v>45298</v>
+      </c>
+      <c r="I19" s="451" t="s">
+        <v>128</v>
+      </c>
+      <c r="K19" t="s">
+        <v>136</v>
+      </c>
+      <c r="L19">
+        <v>18000</v>
+      </c>
+      <c r="M19">
+        <v>45310</v>
+      </c>
+      <c r="N19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="426" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="427">
+        <v>70000</v>
+      </c>
+      <c r="C20" s="430">
+        <v>45600</v>
+      </c>
+      <c r="D20" s="431" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="448" t="s">
+        <v>131</v>
+      </c>
+      <c r="G20" s="449">
+        <v>50000</v>
+      </c>
+      <c r="H20" s="450">
+        <v>45313</v>
+      </c>
+      <c r="I20" s="451" t="s">
+        <v>134</v>
+      </c>
+      <c r="K20" t="s">
+        <v>136</v>
+      </c>
+      <c r="L20">
+        <v>25000</v>
+      </c>
+      <c r="M20">
+        <v>45493</v>
+      </c>
+      <c r="N20" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="432" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="433">
+        <v>80000</v>
+      </c>
+      <c r="C21" s="434">
+        <v>45296</v>
+      </c>
+      <c r="D21" s="435" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="448" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="449">
+        <v>70000</v>
+      </c>
+      <c r="H21" s="450">
+        <v>45600</v>
+      </c>
+      <c r="I21" s="451" t="s">
+        <v>132</v>
+      </c>
+      <c r="K21" t="s">
+        <v>138</v>
+      </c>
+      <c r="L21">
+        <v>25000</v>
+      </c>
+      <c r="M21">
+        <v>45301</v>
+      </c>
+      <c r="N21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="F22" s="448" t="s">
+        <v>138</v>
+      </c>
+      <c r="G22" s="449">
+        <v>80000</v>
+      </c>
+      <c r="H22" s="450">
+        <v>45296</v>
+      </c>
+      <c r="I22" s="451" t="s">
+        <v>132</v>
+      </c>
+      <c r="K22" t="s">
+        <v>139</v>
+      </c>
+      <c r="L22">
+        <v>30000</v>
+      </c>
+      <c r="M22">
+        <v>45519</v>
+      </c>
+      <c r="N22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K23" t="s">
+        <v>140</v>
+      </c>
+      <c r="L23">
+        <v>30000</v>
+      </c>
+      <c r="M23">
+        <v>45304</v>
+      </c>
+      <c r="N23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K24" t="s">
+        <v>135</v>
+      </c>
+      <c r="L24">
+        <v>35000</v>
+      </c>
+      <c r="M24">
+        <v>45548</v>
+      </c>
+      <c r="N24" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K25" t="s">
+        <v>142</v>
+      </c>
+      <c r="L25">
+        <v>36000</v>
+      </c>
+      <c r="M25">
+        <v>45302</v>
+      </c>
+      <c r="N25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E26" s="424"/>
+      <c r="F26" s="424"/>
+      <c r="G26" s="424"/>
+      <c r="H26" s="425"/>
+      <c r="K26" t="s">
+        <v>143</v>
+      </c>
+      <c r="L26">
+        <v>40000</v>
+      </c>
+      <c r="M26">
+        <v>45455</v>
+      </c>
+      <c r="N26" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E27" s="426"/>
+      <c r="F27" s="427"/>
+      <c r="G27" s="428"/>
+      <c r="H27" s="429"/>
+      <c r="K27" t="s">
+        <v>125</v>
+      </c>
+      <c r="L27">
+        <v>45000</v>
+      </c>
+      <c r="M27">
+        <v>45298</v>
+      </c>
+      <c r="N27" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E28" s="426"/>
+      <c r="F28" s="427"/>
+      <c r="G28" s="428"/>
+      <c r="H28" s="429"/>
+      <c r="K28" t="s">
+        <v>131</v>
+      </c>
+      <c r="L28">
+        <v>50000</v>
+      </c>
+      <c r="M28">
+        <v>45313</v>
+      </c>
+      <c r="N28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E29" s="426"/>
+      <c r="F29" s="427"/>
+      <c r="G29" s="428"/>
+      <c r="H29" s="429"/>
+      <c r="K29" t="s">
+        <v>136</v>
+      </c>
+      <c r="L29">
+        <v>70000</v>
+      </c>
+      <c r="M29">
+        <v>45600</v>
+      </c>
+      <c r="N29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E30" s="426"/>
+      <c r="F30" s="427"/>
+      <c r="G30" s="428"/>
+      <c r="H30" s="429"/>
+      <c r="K30" t="s">
+        <v>138</v>
+      </c>
+      <c r="L30">
+        <v>80000</v>
+      </c>
+      <c r="M30">
+        <v>45296</v>
+      </c>
+      <c r="N30" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E31" s="426"/>
+      <c r="F31" s="427"/>
+      <c r="G31" s="428"/>
+      <c r="H31" s="429"/>
+    </row>
+    <row r="32" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E32" s="426"/>
+      <c r="F32" s="427"/>
+      <c r="G32" s="428"/>
+      <c r="H32" s="429"/>
+    </row>
+    <row r="33" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E33" s="426"/>
+      <c r="F33" s="427"/>
+      <c r="G33" s="428"/>
+      <c r="H33" s="429"/>
+    </row>
+    <row r="34" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E34" s="426"/>
+      <c r="F34" s="427"/>
+      <c r="G34" s="428"/>
+      <c r="H34" s="429"/>
+    </row>
+    <row r="35" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E35" s="426"/>
+      <c r="F35" s="427"/>
+      <c r="G35" s="428"/>
+      <c r="H35" s="429"/>
+    </row>
+    <row r="36" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E36" s="426"/>
+      <c r="F36" s="427"/>
+      <c r="G36" s="428"/>
+      <c r="H36" s="429"/>
+    </row>
+    <row r="37" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E37" s="426"/>
+      <c r="F37" s="427"/>
+      <c r="G37" s="428"/>
+      <c r="H37" s="429"/>
+    </row>
+    <row r="38" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E38" s="426"/>
+      <c r="F38" s="427"/>
+      <c r="G38" s="428"/>
+      <c r="H38" s="429"/>
+    </row>
+    <row r="39" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E39" s="426"/>
+      <c r="F39" s="427"/>
+      <c r="G39" s="428"/>
+      <c r="H39" s="429"/>
+    </row>
+    <row r="40" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E40" s="426"/>
+      <c r="F40" s="427"/>
+      <c r="G40" s="428"/>
+      <c r="H40" s="429"/>
+    </row>
+    <row r="41" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E41" s="426"/>
+      <c r="F41" s="427"/>
+      <c r="G41" s="428"/>
+      <c r="H41" s="429"/>
+    </row>
+    <row r="42" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E42" s="426"/>
+      <c r="F42" s="427"/>
+      <c r="G42" s="428"/>
+      <c r="H42" s="429"/>
+    </row>
+    <row r="43" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E43" s="426"/>
+      <c r="F43" s="427"/>
+      <c r="G43" s="428"/>
+      <c r="H43" s="429"/>
+    </row>
+    <row r="44" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E44" s="426"/>
+      <c r="F44" s="427"/>
+      <c r="G44" s="428"/>
+      <c r="H44" s="429"/>
+    </row>
+    <row r="45" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E45" s="426"/>
+      <c r="F45" s="427"/>
+      <c r="G45" s="430"/>
+      <c r="H45" s="431"/>
+    </row>
+    <row r="46" spans="5:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="E46" s="432"/>
+      <c r="F46" s="433"/>
+      <c r="G46" s="434"/>
+      <c r="H46" s="435"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4BF2667-FA00-42BA-A9F8-94619B32ED44}">
   <dimension ref="A1:R23"/>
@@ -12534,16 +15404,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="404" t="s">
+      <c r="A1" s="455" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="403"/>
-      <c r="C1" s="403"/>
+      <c r="B1" s="454"/>
+      <c r="C1" s="454"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="403"/>
-      <c r="B2" s="403"/>
-      <c r="C2" s="403"/>
+      <c r="A2" s="454"/>
+      <c r="B2" s="454"/>
+      <c r="C2" s="454"/>
     </row>
     <row r="3" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="D3" s="29"/>
@@ -12567,11 +15437,11 @@
       <c r="R4" s="5"/>
     </row>
     <row r="5" spans="1:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="C5" s="405" t="s">
+      <c r="C5" s="456" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="405"/>
-      <c r="E5" s="405"/>
+      <c r="D5" s="456"/>
+      <c r="E5" s="456"/>
       <c r="I5" s="30"/>
       <c r="J5" s="30"/>
       <c r="K5" s="30"/>
@@ -12590,13 +15460,13 @@
       <c r="E6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="408" t="s">
+      <c r="H6" s="459" t="s">
         <v>75</v>
       </c>
-      <c r="I6" s="409"/>
-      <c r="J6" s="409"/>
-      <c r="K6" s="409"/>
-      <c r="L6" s="409"/>
+      <c r="I6" s="460"/>
+      <c r="J6" s="460"/>
+      <c r="K6" s="460"/>
+      <c r="L6" s="460"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
@@ -12815,12 +15685,12 @@
       </c>
     </row>
     <row r="17" spans="3:12" ht="15" x14ac:dyDescent="0.35">
-      <c r="C17" s="406" t="s">
+      <c r="C17" s="457" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="407"/>
-      <c r="E17" s="407"/>
-      <c r="F17" s="407"/>
+      <c r="D17" s="458"/>
+      <c r="E17" s="458"/>
+      <c r="F17" s="458"/>
       <c r="H17" s="22">
         <v>109</v>
       </c>
@@ -13020,17 +15890,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="410" t="s">
+      <c r="A1" s="461" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="411"/>
-      <c r="C1" s="411"/>
-      <c r="D1" s="411"/>
-      <c r="E1" s="411"/>
-      <c r="F1" s="411"/>
-      <c r="G1" s="411"/>
-      <c r="H1" s="411"/>
-      <c r="I1" s="411"/>
+      <c r="B1" s="462"/>
+      <c r="C1" s="462"/>
+      <c r="D1" s="462"/>
+      <c r="E1" s="462"/>
+      <c r="F1" s="462"/>
+      <c r="G1" s="462"/>
+      <c r="H1" s="462"/>
+      <c r="I1" s="462"/>
     </row>
     <row r="2" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="31">
@@ -13384,7 +16254,7 @@
       <c r="C3" s="33">
         <v>46221</v>
       </c>
-      <c r="D3" s="415" t="s">
+      <c r="D3" s="466" t="s">
         <v>120</v>
       </c>
     </row>
@@ -13392,30 +16262,30 @@
       <c r="C4" s="33">
         <v>46220</v>
       </c>
-      <c r="D4" s="415"/>
+      <c r="D4" s="466"/>
     </row>
     <row r="5" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="40"/>
       <c r="C5" s="33">
         <v>46219</v>
       </c>
-      <c r="D5" s="415"/>
+      <c r="D5" s="466"/>
       <c r="E5" s="35">
         <v>600</v>
       </c>
-      <c r="F5" s="414" t="s">
+      <c r="F5" s="465" t="s">
         <v>120</v>
       </c>
       <c r="G5" s="39">
         <v>0.1</v>
       </c>
-      <c r="H5" s="412" t="s">
+      <c r="H5" s="463" t="s">
         <v>119</v>
       </c>
       <c r="I5" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="J5" s="413" t="s">
+      <c r="J5" s="464" t="s">
         <v>119</v>
       </c>
     </row>
@@ -13424,175 +16294,175 @@
       <c r="C6" s="33">
         <v>46218</v>
       </c>
-      <c r="D6" s="415"/>
+      <c r="D6" s="466"/>
       <c r="E6" s="35">
         <v>432</v>
       </c>
-      <c r="F6" s="414"/>
+      <c r="F6" s="465"/>
       <c r="G6" s="38">
         <v>0.3</v>
       </c>
-      <c r="H6" s="412"/>
+      <c r="H6" s="463"/>
       <c r="I6" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="J6" s="413"/>
+      <c r="J6" s="464"/>
     </row>
     <row r="7" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="40"/>
       <c r="C7" s="33">
         <v>46217</v>
       </c>
-      <c r="D7" s="415"/>
+      <c r="D7" s="466"/>
       <c r="E7" s="35">
         <v>400</v>
       </c>
-      <c r="F7" s="414"/>
+      <c r="F7" s="465"/>
       <c r="G7" s="38">
         <v>0.34</v>
       </c>
-      <c r="H7" s="412"/>
+      <c r="H7" s="463"/>
       <c r="I7" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="J7" s="413"/>
+      <c r="J7" s="464"/>
     </row>
     <row r="8" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="40"/>
       <c r="C8" s="33">
         <v>46216</v>
       </c>
-      <c r="D8" s="415"/>
+      <c r="D8" s="466"/>
       <c r="E8" s="35">
         <v>360</v>
       </c>
-      <c r="F8" s="414"/>
+      <c r="F8" s="465"/>
       <c r="G8" s="38">
         <v>0.43</v>
       </c>
-      <c r="H8" s="412"/>
+      <c r="H8" s="463"/>
       <c r="I8" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="J8" s="413"/>
+      <c r="J8" s="464"/>
     </row>
     <row r="9" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="40"/>
       <c r="C9" s="33">
         <v>46215</v>
       </c>
-      <c r="D9" s="415"/>
+      <c r="D9" s="466"/>
       <c r="E9" s="35">
         <v>350</v>
       </c>
-      <c r="F9" s="414"/>
+      <c r="F9" s="465"/>
       <c r="G9" s="38">
         <v>0.45</v>
       </c>
-      <c r="H9" s="412"/>
+      <c r="H9" s="463"/>
       <c r="I9" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="J9" s="413"/>
+      <c r="J9" s="464"/>
     </row>
     <row r="10" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="40"/>
       <c r="C10" s="33">
         <v>46214</v>
       </c>
-      <c r="D10" s="415"/>
+      <c r="D10" s="466"/>
       <c r="E10" s="35">
         <v>300</v>
       </c>
-      <c r="F10" s="414"/>
+      <c r="F10" s="465"/>
       <c r="G10" s="38">
         <v>0.5</v>
       </c>
-      <c r="H10" s="412"/>
+      <c r="H10" s="463"/>
     </row>
     <row r="11" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="40"/>
       <c r="C11" s="33">
         <v>46213</v>
       </c>
-      <c r="D11" s="415"/>
+      <c r="D11" s="466"/>
       <c r="E11" s="35">
         <v>300</v>
       </c>
-      <c r="F11" s="414"/>
+      <c r="F11" s="465"/>
       <c r="G11" s="38">
         <v>0.6</v>
       </c>
-      <c r="H11" s="412"/>
+      <c r="H11" s="463"/>
     </row>
     <row r="12" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="40"/>
       <c r="C12" s="33">
         <v>46212</v>
       </c>
-      <c r="D12" s="415"/>
+      <c r="D12" s="466"/>
       <c r="E12" s="35">
         <v>230</v>
       </c>
-      <c r="F12" s="414"/>
+      <c r="F12" s="465"/>
       <c r="G12" s="38">
         <v>0.9</v>
       </c>
-      <c r="H12" s="412"/>
+      <c r="H12" s="463"/>
     </row>
     <row r="13" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="40"/>
       <c r="C13" s="33">
         <v>46211</v>
       </c>
-      <c r="D13" s="415"/>
+      <c r="D13" s="466"/>
       <c r="E13" s="35">
         <v>150</v>
       </c>
-      <c r="F13" s="414"/>
+      <c r="F13" s="465"/>
     </row>
     <row r="14" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="40"/>
       <c r="C14" s="33">
         <v>46210</v>
       </c>
-      <c r="D14" s="415"/>
+      <c r="D14" s="466"/>
       <c r="E14" s="35">
         <v>100</v>
       </c>
-      <c r="F14" s="414"/>
+      <c r="F14" s="465"/>
     </row>
     <row r="15" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="40"/>
       <c r="C15" s="33">
         <v>46209</v>
       </c>
-      <c r="D15" s="415"/>
+      <c r="D15" s="466"/>
     </row>
     <row r="16" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="40"/>
       <c r="C16" s="33">
         <v>46208</v>
       </c>
-      <c r="D16" s="415"/>
+      <c r="D16" s="466"/>
     </row>
     <row r="17" spans="3:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C17" s="33">
         <v>46207</v>
       </c>
-      <c r="D17" s="415"/>
+      <c r="D17" s="466"/>
     </row>
     <row r="18" spans="3:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C18" s="33">
         <v>46206</v>
       </c>
-      <c r="D18" s="415"/>
+      <c r="D18" s="466"/>
     </row>
     <row r="19" spans="3:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="33">
         <v>46205</v>
       </c>
-      <c r="D19" s="415"/>
+      <c r="D19" s="466"/>
     </row>
     <row r="20" spans="3:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C20" s="33">
@@ -13678,7 +16548,7 @@
         <f>SUM(C4:C10)</f>
         <v>55000</v>
       </c>
-      <c r="J5" s="416" t="s">
+      <c r="J5" s="467" t="s">
         <v>147</v>
       </c>
     </row>
@@ -13699,7 +16569,7 @@
         <f>C4+C5+C6+C7+C8+C9+C10</f>
         <v>55000</v>
       </c>
-      <c r="J6" s="417"/>
+      <c r="J6" s="468"/>
     </row>
     <row r="7" spans="2:10" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="57" t="s">
@@ -14054,7 +16924,7 @@
       <c r="D29" s="79" t="s">
         <v>157</v>
       </c>
-      <c r="E29" s="418" t="s">
+      <c r="E29" s="469" t="s">
         <v>159</v>
       </c>
     </row>
@@ -14069,7 +16939,7 @@
       <c r="D30" s="80" t="s">
         <v>158</v>
       </c>
-      <c r="E30" s="418"/>
+      <c r="E30" s="469"/>
       <c r="I30" s="81" t="s">
         <v>163</v>
       </c>
@@ -14085,7 +16955,7 @@
       <c r="D31" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="E31" s="418"/>
+      <c r="E31" s="469"/>
       <c r="I31" s="81" t="s">
         <v>164</v>
       </c>
@@ -14101,7 +16971,7 @@
       <c r="D32" s="79" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="418"/>
+      <c r="E32" s="469"/>
       <c r="I32" s="81" t="s">
         <v>165</v>
       </c>
@@ -14117,7 +16987,7 @@
       <c r="D33" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="E33" s="418"/>
+      <c r="E33" s="469"/>
       <c r="I33" s="82" t="s">
         <v>166</v>
       </c>
@@ -15728,18 +18598,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="D1" s="419" t="s">
+      <c r="D1" s="470" t="s">
         <v>340</v>
       </c>
-      <c r="E1" s="419"/>
-      <c r="F1" s="419"/>
-      <c r="G1" s="419"/>
-      <c r="H1" s="419"/>
-      <c r="I1" s="419"/>
-      <c r="J1" s="419"/>
-      <c r="K1" s="419"/>
-      <c r="L1" s="419"/>
-      <c r="M1" s="419"/>
+      <c r="E1" s="470"/>
+      <c r="F1" s="470"/>
+      <c r="G1" s="470"/>
+      <c r="H1" s="470"/>
+      <c r="I1" s="470"/>
+      <c r="J1" s="470"/>
+      <c r="K1" s="470"/>
+      <c r="L1" s="470"/>
+      <c r="M1" s="470"/>
     </row>
     <row r="2" spans="2:13" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="42" t="s">
@@ -16340,11 +19210,11 @@
       </c>
       <c r="G4" s="156">
         <f ca="1">TODAY()</f>
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="H4" s="155">
         <f ca="1">NOW()</f>
-        <v>46259.918957407404</v>
+        <v>46266.485833217594</v>
       </c>
       <c r="I4" s="156">
         <f>DATE(C2,C3,C4)</f>
@@ -16518,13 +19388,13 @@
         <f>F11+H11</f>
         <v>45242</v>
       </c>
-      <c r="K11" s="399" t="s">
+      <c r="K11" s="499" t="s">
         <v>348</v>
       </c>
-      <c r="L11" s="399"/>
-      <c r="M11" s="399"/>
-      <c r="N11" s="399"/>
-      <c r="O11" s="399"/>
+      <c r="L11" s="499"/>
+      <c r="M11" s="499"/>
+      <c r="N11" s="499"/>
+      <c r="O11" s="499"/>
     </row>
     <row r="12" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="116" t="s">
@@ -16548,13 +19418,13 @@
         <f>F12+H12</f>
         <v>44913</v>
       </c>
-      <c r="K12" s="399" t="s">
+      <c r="K12" s="499" t="s">
         <v>349</v>
       </c>
-      <c r="L12" s="399"/>
-      <c r="M12" s="399"/>
-      <c r="N12" s="399"/>
-      <c r="O12" s="399"/>
+      <c r="L12" s="499"/>
+      <c r="M12" s="499"/>
+      <c r="N12" s="499"/>
+      <c r="O12" s="499"/>
     </row>
     <row r="13" spans="2:18" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="116" t="s">
@@ -16578,13 +19448,13 @@
         <f>F13+H13</f>
         <v>42293</v>
       </c>
-      <c r="K13" s="399" t="s">
+      <c r="K13" s="499" t="s">
         <v>350</v>
       </c>
-      <c r="L13" s="399"/>
-      <c r="M13" s="399"/>
-      <c r="N13" s="399"/>
-      <c r="O13" s="399"/>
+      <c r="L13" s="499"/>
+      <c r="M13" s="499"/>
+      <c r="N13" s="499"/>
+      <c r="O13" s="499"/>
     </row>
     <row r="14" spans="2:18" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="116" t="s">
@@ -16608,13 +19478,13 @@
         <f>E14+H14</f>
         <v>45770</v>
       </c>
-      <c r="K14" s="399" t="s">
+      <c r="K14" s="499" t="s">
         <v>353</v>
       </c>
-      <c r="L14" s="399"/>
-      <c r="M14" s="399"/>
-      <c r="N14" s="399"/>
-      <c r="O14" s="399"/>
+      <c r="L14" s="499"/>
+      <c r="M14" s="499"/>
+      <c r="N14" s="499"/>
+      <c r="O14" s="499"/>
     </row>
     <row r="15" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="116" t="s">
@@ -16627,11 +19497,11 @@
       <c r="G15" s="122"/>
       <c r="H15" s="122"/>
       <c r="I15" s="122"/>
-      <c r="K15" s="399"/>
-      <c r="L15" s="399"/>
-      <c r="M15" s="399"/>
-      <c r="N15" s="399"/>
-      <c r="O15" s="399"/>
+      <c r="K15" s="499"/>
+      <c r="L15" s="499"/>
+      <c r="M15" s="499"/>
+      <c r="N15" s="499"/>
+      <c r="O15" s="499"/>
     </row>
     <row r="16" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="116" t="s">
@@ -16644,32 +19514,32 @@
       <c r="G16" s="122"/>
       <c r="H16" s="122"/>
       <c r="I16" s="122"/>
-      <c r="K16" s="399"/>
-      <c r="L16" s="399"/>
-      <c r="M16" s="399"/>
-      <c r="N16" s="399"/>
-      <c r="O16" s="399"/>
+      <c r="K16" s="499"/>
+      <c r="L16" s="499"/>
+      <c r="M16" s="499"/>
+      <c r="N16" s="499"/>
+      <c r="O16" s="499"/>
     </row>
     <row r="17" spans="2:15" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="116" t="s">
         <v>262</v>
       </c>
       <c r="C17" s="122"/>
-      <c r="D17" s="446" t="s">
+      <c r="D17" s="497" t="s">
         <v>347</v>
       </c>
-      <c r="E17" s="447"/>
+      <c r="E17" s="498"/>
       <c r="F17" s="122"/>
       <c r="G17" s="122"/>
       <c r="H17" s="163" t="s">
         <v>352</v>
       </c>
       <c r="I17" s="122"/>
-      <c r="K17" s="399"/>
-      <c r="L17" s="399"/>
-      <c r="M17" s="399"/>
-      <c r="N17" s="399"/>
-      <c r="O17" s="399"/>
+      <c r="K17" s="499"/>
+      <c r="L17" s="499"/>
+      <c r="M17" s="499"/>
+      <c r="N17" s="499"/>
+      <c r="O17" s="499"/>
     </row>
     <row r="18" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="116" t="s">
@@ -16682,11 +19552,11 @@
       <c r="G18" s="115"/>
       <c r="H18" s="115"/>
       <c r="I18" s="115"/>
-      <c r="K18" s="445"/>
-      <c r="L18" s="445"/>
-      <c r="M18" s="445"/>
-      <c r="N18" s="445"/>
-      <c r="O18" s="445"/>
+      <c r="K18" s="496"/>
+      <c r="L18" s="496"/>
+      <c r="M18" s="496"/>
+      <c r="N18" s="496"/>
+      <c r="O18" s="496"/>
     </row>
     <row r="19" spans="2:15" ht="33" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="122"/>
@@ -16709,7 +19579,7 @@
     <row r="20" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="122"/>
       <c r="C20" s="123"/>
-      <c r="D20" s="423" t="s">
+      <c r="D20" s="474" t="s">
         <v>267</v>
       </c>
       <c r="E20" s="124">
@@ -16725,14 +19595,14 @@
       <c r="H20" s="162">
         <v>44988</v>
       </c>
-      <c r="I20" s="423" t="s">
+      <c r="I20" s="474" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
-      <c r="D21" s="424"/>
+      <c r="D21" s="475"/>
       <c r="E21" s="124">
         <v>45512</v>
       </c>
@@ -16746,12 +19616,12 @@
       <c r="H21" s="162">
         <v>45665</v>
       </c>
-      <c r="I21" s="424"/>
+      <c r="I21" s="475"/>
     </row>
     <row r="22" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="122"/>
       <c r="C22" s="123"/>
-      <c r="D22" s="424"/>
+      <c r="D22" s="475"/>
       <c r="E22" s="124">
         <v>42252</v>
       </c>
@@ -16765,12 +19635,12 @@
       <c r="H22" s="162">
         <v>42099</v>
       </c>
-      <c r="I22" s="424"/>
+      <c r="I22" s="475"/>
     </row>
     <row r="23" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="122"/>
       <c r="C23" s="123"/>
-      <c r="D23" s="425"/>
+      <c r="D23" s="476"/>
       <c r="E23" s="124">
         <v>45770</v>
       </c>
@@ -16784,7 +19654,7 @@
       <c r="H23" s="162">
         <v>45405</v>
       </c>
-      <c r="I23" s="425"/>
+      <c r="I23" s="476"/>
     </row>
     <row r="24" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="122"/>
@@ -16798,10 +19668,10 @@
     </row>
     <row r="25" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="123"/>
-      <c r="C25" s="420" t="s">
+      <c r="C25" s="471" t="s">
         <v>269</v>
       </c>
-      <c r="D25" s="423" t="s">
+      <c r="D25" s="474" t="s">
         <v>270</v>
       </c>
       <c r="E25" s="156">
@@ -16815,8 +19685,8 @@
     </row>
     <row r="26" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="123"/>
-      <c r="C26" s="421"/>
-      <c r="D26" s="424"/>
+      <c r="C26" s="472"/>
+      <c r="D26" s="475"/>
       <c r="E26" s="156">
         <f>EOMONTH(G21,G12)</f>
         <v>45838</v>
@@ -16830,8 +19700,8 @@
     </row>
     <row r="27" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="123"/>
-      <c r="C27" s="421"/>
-      <c r="D27" s="424"/>
+      <c r="C27" s="472"/>
+      <c r="D27" s="475"/>
       <c r="E27" s="156">
         <f>EOMONTH(G22,G13)</f>
         <v>41973</v>
@@ -16843,8 +19713,8 @@
     </row>
     <row r="28" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="123"/>
-      <c r="C28" s="422"/>
-      <c r="D28" s="425"/>
+      <c r="C28" s="473"/>
+      <c r="D28" s="476"/>
       <c r="E28" s="156">
         <f>EOMONTH(G23,G14)</f>
         <v>45046</v>
@@ -16866,10 +19736,10 @@
     </row>
     <row r="30" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="123"/>
-      <c r="C30" s="420" t="s">
+      <c r="C30" s="471" t="s">
         <v>271</v>
       </c>
-      <c r="D30" s="423" t="s">
+      <c r="D30" s="474" t="s">
         <v>257</v>
       </c>
       <c r="E30" s="164">
@@ -16887,8 +19757,8 @@
     </row>
     <row r="31" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="123"/>
-      <c r="C31" s="421"/>
-      <c r="D31" s="424"/>
+      <c r="C31" s="472"/>
+      <c r="D31" s="475"/>
       <c r="E31" s="164">
         <f t="shared" ref="E31:E33" si="1">WEEKDAY(F31,2)</f>
         <v>3</v>
@@ -16904,8 +19774,8 @@
     </row>
     <row r="32" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="123"/>
-      <c r="C32" s="421"/>
-      <c r="D32" s="424"/>
+      <c r="C32" s="472"/>
+      <c r="D32" s="475"/>
       <c r="E32" s="164">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -16921,8 +19791,8 @@
     </row>
     <row r="33" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="123"/>
-      <c r="C33" s="422"/>
-      <c r="D33" s="425"/>
+      <c r="C33" s="473"/>
+      <c r="D33" s="476"/>
       <c r="E33" s="164">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -16948,10 +19818,10 @@
     </row>
     <row r="35" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="123"/>
-      <c r="C35" s="420" t="s">
+      <c r="C35" s="471" t="s">
         <v>272</v>
       </c>
-      <c r="D35" s="423" t="s">
+      <c r="D35" s="474" t="s">
         <v>258</v>
       </c>
       <c r="E35" s="164">
@@ -16967,8 +19837,8 @@
     </row>
     <row r="36" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="123"/>
-      <c r="C36" s="421"/>
-      <c r="D36" s="424"/>
+      <c r="C36" s="472"/>
+      <c r="D36" s="475"/>
       <c r="E36" s="164">
         <f t="shared" ref="E36:E38" si="2">WEEKNUM(F36,11)</f>
         <v>2</v>
@@ -16982,8 +19852,8 @@
     </row>
     <row r="37" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="123"/>
-      <c r="C37" s="421"/>
-      <c r="D37" s="424"/>
+      <c r="C37" s="472"/>
+      <c r="D37" s="475"/>
       <c r="E37" s="164">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -16997,8 +19867,8 @@
     </row>
     <row r="38" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="123"/>
-      <c r="C38" s="422"/>
-      <c r="D38" s="425"/>
+      <c r="C38" s="473"/>
+      <c r="D38" s="476"/>
       <c r="E38" s="164">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -17043,7 +19913,7 @@
     <row r="41" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="122"/>
       <c r="C41" s="123"/>
-      <c r="D41" s="423" t="s">
+      <c r="D41" s="474" t="s">
         <v>255</v>
       </c>
       <c r="E41" s="164">
@@ -17068,7 +19938,7 @@
     <row r="42" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="122"/>
       <c r="C42" s="123"/>
-      <c r="D42" s="424"/>
+      <c r="D42" s="475"/>
       <c r="E42" s="164">
         <f>DATEDIF(F42,G42,"M")</f>
         <v>28</v>
@@ -17091,7 +19961,7 @@
     <row r="43" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="122"/>
       <c r="C43" s="123"/>
-      <c r="D43" s="424"/>
+      <c r="D43" s="475"/>
       <c r="E43" s="164">
         <f>DATEDIF(F43,G43,"M")</f>
         <v>10</v>
@@ -17114,7 +19984,7 @@
     <row r="44" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="122"/>
       <c r="C44" s="123"/>
-      <c r="D44" s="425"/>
+      <c r="D44" s="476"/>
       <c r="E44" s="164">
         <f>DATEDIF(F44,G44,"M")</f>
         <v>44</v>
@@ -17157,7 +20027,7 @@
         <f>DATEDIF($D$47,$I$47,"Y")</f>
         <v>20</v>
       </c>
-      <c r="G46" s="423" t="s">
+      <c r="G46" s="474" t="s">
         <v>278</v>
       </c>
       <c r="H46" s="115"/>
@@ -17176,7 +20046,7 @@
         <f>DATEDIF($D$47,$I$47,"M")</f>
         <v>244</v>
       </c>
-      <c r="G47" s="424"/>
+      <c r="G47" s="475"/>
       <c r="H47" s="119" t="s">
         <v>279</v>
       </c>
@@ -17195,7 +20065,7 @@
         <f>DATEDIF($D$47,$I$47,"D")</f>
         <v>7434</v>
       </c>
-      <c r="G48" s="425"/>
+      <c r="G48" s="476"/>
       <c r="H48" s="122"/>
       <c r="I48" s="122"/>
     </row>
@@ -17220,16 +20090,16 @@
       <c r="I50" s="115"/>
     </row>
     <row r="51" spans="2:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="436" t="s">
+      <c r="B51" s="487" t="s">
         <v>280</v>
       </c>
-      <c r="C51" s="437"/>
-      <c r="D51" s="437"/>
-      <c r="E51" s="437"/>
-      <c r="F51" s="437"/>
-      <c r="G51" s="437"/>
-      <c r="H51" s="438"/>
-      <c r="I51" s="439" t="s">
+      <c r="C51" s="488"/>
+      <c r="D51" s="488"/>
+      <c r="E51" s="488"/>
+      <c r="F51" s="488"/>
+      <c r="G51" s="488"/>
+      <c r="H51" s="489"/>
+      <c r="I51" s="490" t="s">
         <v>281</v>
       </c>
     </row>
@@ -17255,7 +20125,7 @@
       <c r="H52" s="124">
         <v>43862</v>
       </c>
-      <c r="I52" s="440"/>
+      <c r="I52" s="491"/>
     </row>
     <row r="53" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="128" t="s">
@@ -17279,7 +20149,7 @@
       <c r="H53" s="124">
         <v>44208</v>
       </c>
-      <c r="I53" s="440"/>
+      <c r="I53" s="491"/>
     </row>
     <row r="54" spans="2:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="128" t="s">
@@ -17303,7 +20173,7 @@
       <c r="H54" s="118" t="s">
         <v>285</v>
       </c>
-      <c r="I54" s="440"/>
+      <c r="I54" s="491"/>
     </row>
     <row r="55" spans="2:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="129" t="s">
@@ -17333,7 +20203,7 @@
         <f>DATEDIF(H52,H53,"YD")</f>
         <v>346</v>
       </c>
-      <c r="I55" s="441"/>
+      <c r="I55" s="492"/>
     </row>
     <row r="56" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="115"/>
@@ -17403,7 +20273,7 @@
         <f>NETWORKDAYS(E59,F59,D66:D68)</f>
         <v>257</v>
       </c>
-      <c r="I59" s="426" t="s">
+      <c r="I59" s="477" t="s">
         <v>262</v>
       </c>
     </row>
@@ -17429,7 +20299,7 @@
         <f>NETWORKDAYS(E60,F60,D69:D71)</f>
         <v>259</v>
       </c>
-      <c r="I60" s="427"/>
+      <c r="I60" s="478"/>
     </row>
     <row r="61" spans="2:9" ht="49.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="130" t="s">
@@ -17453,7 +20323,7 @@
         <f>NETWORKDAYS.INTL(E61,F61,1,D72:D74)</f>
         <v>259</v>
       </c>
-      <c r="I61" s="428" t="s">
+      <c r="I61" s="479" t="s">
         <v>354</v>
       </c>
     </row>
@@ -17479,7 +20349,7 @@
         <f>NETWORKDAYS.INTL(E62,F62,1,G69:G71)</f>
         <v>258</v>
       </c>
-      <c r="I62" s="429"/>
+      <c r="I62" s="480"/>
     </row>
     <row r="63" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="122"/>
@@ -17513,7 +20383,7 @@
     </row>
     <row r="66" spans="2:9" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="135"/>
-      <c r="C66" s="442" t="s">
+      <c r="C66" s="493" t="s">
         <v>298</v>
       </c>
       <c r="D66" s="134">
@@ -17522,7 +20392,7 @@
       <c r="E66" s="136" t="s">
         <v>295</v>
       </c>
-      <c r="F66" s="430" t="s">
+      <c r="F66" s="481" t="s">
         <v>296</v>
       </c>
       <c r="G66" s="137">
@@ -17531,56 +20401,56 @@
       <c r="H66" s="138" t="s">
         <v>297</v>
       </c>
-      <c r="I66" s="433" t="s">
+      <c r="I66" s="484" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="135"/>
-      <c r="C67" s="443"/>
+      <c r="C67" s="494"/>
       <c r="D67" s="124">
         <v>45153</v>
       </c>
       <c r="E67" s="125" t="s">
         <v>299</v>
       </c>
-      <c r="F67" s="431"/>
+      <c r="F67" s="482"/>
       <c r="G67" s="137">
         <v>42189</v>
       </c>
       <c r="H67" s="138" t="s">
         <v>299</v>
       </c>
-      <c r="I67" s="434"/>
+      <c r="I67" s="485"/>
     </row>
     <row r="68" spans="2:9" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="135"/>
-      <c r="C68" s="443"/>
+      <c r="C68" s="494"/>
       <c r="D68" s="134">
         <v>45201</v>
       </c>
       <c r="E68" s="136" t="s">
         <v>300</v>
       </c>
-      <c r="F68" s="431"/>
+      <c r="F68" s="482"/>
       <c r="G68" s="137">
         <v>42248</v>
       </c>
       <c r="H68" s="138" t="s">
         <v>301</v>
       </c>
-      <c r="I68" s="435"/>
+      <c r="I68" s="486"/>
     </row>
     <row r="69" spans="2:9" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B69" s="122"/>
-      <c r="C69" s="443"/>
+      <c r="C69" s="494"/>
       <c r="D69" s="134">
         <v>45317</v>
       </c>
       <c r="E69" s="136" t="s">
         <v>295</v>
       </c>
-      <c r="F69" s="431"/>
+      <c r="F69" s="482"/>
       <c r="G69" s="137">
         <v>45705</v>
       </c>
@@ -17591,14 +20461,14 @@
     </row>
     <row r="70" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B70" s="122"/>
-      <c r="C70" s="443"/>
+      <c r="C70" s="494"/>
       <c r="D70" s="124">
         <v>45519</v>
       </c>
       <c r="E70" s="125" t="s">
         <v>299</v>
       </c>
-      <c r="F70" s="431"/>
+      <c r="F70" s="482"/>
       <c r="G70" s="137">
         <v>45842</v>
       </c>
@@ -17609,14 +20479,14 @@
     </row>
     <row r="71" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="122"/>
-      <c r="C71" s="443"/>
+      <c r="C71" s="494"/>
       <c r="D71" s="134">
         <v>45567</v>
       </c>
       <c r="E71" s="136" t="s">
         <v>300</v>
       </c>
-      <c r="F71" s="431"/>
+      <c r="F71" s="482"/>
       <c r="G71" s="137">
         <v>45901</v>
       </c>
@@ -17627,42 +20497,42 @@
     </row>
     <row r="72" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B72" s="122"/>
-      <c r="C72" s="443"/>
+      <c r="C72" s="494"/>
       <c r="D72" s="134">
         <v>42030</v>
       </c>
       <c r="E72" s="136" t="s">
         <v>295</v>
       </c>
-      <c r="F72" s="431"/>
+      <c r="F72" s="482"/>
       <c r="G72" s="122"/>
       <c r="H72" s="122"/>
       <c r="I72" s="122"/>
     </row>
     <row r="73" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B73" s="122"/>
-      <c r="C73" s="443"/>
+      <c r="C73" s="494"/>
       <c r="D73" s="124">
         <v>42231</v>
       </c>
       <c r="E73" s="125" t="s">
         <v>299</v>
       </c>
-      <c r="F73" s="431"/>
+      <c r="F73" s="482"/>
       <c r="G73" s="122"/>
       <c r="H73" s="122"/>
       <c r="I73" s="122"/>
     </row>
     <row r="74" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="122"/>
-      <c r="C74" s="444"/>
+      <c r="C74" s="495"/>
       <c r="D74" s="134">
         <v>42279</v>
       </c>
       <c r="E74" s="136" t="s">
         <v>300</v>
       </c>
-      <c r="F74" s="432"/>
+      <c r="F74" s="483"/>
       <c r="G74" s="122"/>
       <c r="H74" s="122"/>
       <c r="I74" s="122"/>

--- a/Excel_Introduction_and_Data_Formating/Excel_Data_Analytics_Practice.xlsx
+++ b/Excel_Introduction_and_Data_Formating/Excel_Data_Analytics_Practice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e01621777f20dcb/Desktop/Excel_For_Data_Analytics/Excel_Introduction_and_Data_Formating/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2839" documentId="8_{5BFF8888-E61D-45DF-9242-3D43603A95FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9AA602D-0567-4A0F-87BA-3F22A6C16545}"/>
+  <xr:revisionPtr revIDLastSave="3113" documentId="8_{5BFF8888-E61D-45DF-9242-3D43603A95FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F60648BB-CC72-4BDC-A5F3-02FEA46C244C}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" firstSheet="16" activeTab="18" xr2:uid="{E6744EAD-35E1-4258-81F8-3CB7F274373C}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="23" activeTab="24" xr2:uid="{E6744EAD-35E1-4258-81F8-3CB7F274373C}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel Interface" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,19 @@
     <sheet name="Index and Match Function" sheetId="19" r:id="rId17"/>
     <sheet name="Data Validation" sheetId="20" r:id="rId18"/>
     <sheet name="Paste Special" sheetId="21" r:id="rId19"/>
+    <sheet name="Conditional Formatting" sheetId="22" r:id="rId20"/>
+    <sheet name="Scenario manager" sheetId="23" r:id="rId21"/>
+    <sheet name="Scenario Summary" sheetId="28" r:id="rId22"/>
+    <sheet name="Goal seek-1" sheetId="25" r:id="rId23"/>
+    <sheet name="Goal seek-2" sheetId="24" r:id="rId24"/>
+    <sheet name="Data Table" sheetId="29" r:id="rId25"/>
   </sheets>
+  <definedNames>
+    <definedName name="CPU">'Scenario manager'!$C$9</definedName>
+    <definedName name="Motherboards">'Scenario manager'!$C$4</definedName>
+    <definedName name="RAM">'Scenario manager'!$C$5</definedName>
+    <definedName name="Speakers">'Scenario manager'!$C$6</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -101,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="507">
   <si>
     <t>1.edit in data  (F2)/double click</t>
   </si>
@@ -1445,6 +1457,183 @@
   </si>
   <si>
     <t>DATA VALIDATION - using paste special</t>
+  </si>
+  <si>
+    <t>Cost Price</t>
+  </si>
+  <si>
+    <t>Cost Price2</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>Magazines</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>Pencils</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>Pens</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>Colors</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Highlighters</t>
+  </si>
+  <si>
+    <t>Scales/Rulers</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>Novels</t>
+  </si>
+  <si>
+    <t>Laptop Production</t>
+  </si>
+  <si>
+    <t>Parts</t>
+  </si>
+  <si>
+    <t>Costing</t>
+  </si>
+  <si>
+    <t>Motherboards</t>
+  </si>
+  <si>
+    <t>RAM Modules</t>
+  </si>
+  <si>
+    <t>Speakers</t>
+  </si>
+  <si>
+    <t>Cooling fans</t>
+  </si>
+  <si>
+    <t>Batteries and Adapters</t>
+  </si>
+  <si>
+    <t>CPU</t>
+  </si>
+  <si>
+    <t>Toouchpad</t>
+  </si>
+  <si>
+    <t>Display screen</t>
+  </si>
+  <si>
+    <t>Storage (HDD)</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Laptop Price</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy S25 Ultra</t>
+  </si>
+  <si>
+    <t>Down Payment</t>
+  </si>
+  <si>
+    <t>Tenure</t>
+  </si>
+  <si>
+    <t>EMI</t>
+  </si>
+  <si>
+    <t>YES !</t>
+  </si>
+  <si>
+    <t>$C$7</t>
+  </si>
+  <si>
+    <t>$C$8</t>
+  </si>
+  <si>
+    <t>$C$10</t>
+  </si>
+  <si>
+    <t>$C$11</t>
+  </si>
+  <si>
+    <t>$C$12</t>
+  </si>
+  <si>
+    <t>$C$13</t>
+  </si>
+  <si>
+    <t>$C$14</t>
+  </si>
+  <si>
+    <t>Lower_Prices</t>
+  </si>
+  <si>
+    <t>Created by HP on 09-09-2026</t>
+  </si>
+  <si>
+    <t>Higher_Prices</t>
+  </si>
+  <si>
+    <t>Scenario Summary</t>
+  </si>
+  <si>
+    <t>Changing Cells:</t>
+  </si>
+  <si>
+    <t>Current Values:</t>
+  </si>
+  <si>
+    <t>Result Cells:</t>
+  </si>
+  <si>
+    <t>Notes:  Current Values column represents values of changing cells at</t>
+  </si>
+  <si>
+    <t>time Scenario Summary Report was created.  Changing cells for each</t>
+  </si>
+  <si>
+    <t>scenario are highlighted in gray.</t>
+  </si>
+  <si>
+    <t>RAM</t>
+  </si>
+  <si>
+    <t>Remaining loan amount</t>
+  </si>
+  <si>
+    <t>Total Costing</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>go</t>
   </si>
 </sst>
 </file>
@@ -1457,7 +1646,7 @@
     <numFmt numFmtId="166" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="167" formatCode="dddd"/>
   </numFmts>
-  <fonts count="124" x14ac:knownFonts="1">
+  <fonts count="141" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2358,8 +2547,124 @@
       <name val="Bookman Old Style"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Amasis MT Pro"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF0C0C0C"/>
+      <name val="Amasis MT Pro"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Comic Sans MS"/>
+      <family val="4"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Comic Sans MS"/>
+      <family val="4"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Comic Sans MS"/>
+      <family val="4"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Comic Sans MS"/>
+      <family val="4"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="48">
+  <fills count="56">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2642,8 +2947,56 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE598"/>
+        <bgColor rgb="FFFFE598"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFE598"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="20"/>
+        <bgColor indexed="24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="65">
+  <borders count="70">
     <border>
       <left/>
       <right/>
@@ -3461,8 +3814,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
@@ -3470,8 +3874,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="551">
+  <cellXfs count="624">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4756,6 +5161,213 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="124" fillId="38" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="124" fillId="38" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="38" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="39" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="81" fillId="38" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="38" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="30" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="65" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="125" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="81" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="81" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="125" fillId="0" borderId="46" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="81" fillId="0" borderId="5" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="81" fillId="0" borderId="51" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="48" borderId="43" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="48" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="48" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="39" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="39" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="40" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="41" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="40" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="53" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="53" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="137" fillId="54" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="54" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="54" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="53" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="53" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="40" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="129" fillId="0" borderId="40" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="48" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="48" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="21" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="48" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="49" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="21" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="50" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="40" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="51" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="52" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="20" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="51" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="39" borderId="40" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="51" borderId="67" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="51" borderId="42" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="40" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="48" borderId="43" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="48" borderId="42" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="39" borderId="43" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="47" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="42" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="39" borderId="41" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="39" borderId="48" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="39" borderId="67" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -4813,92 +5425,92 @@
     <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="28" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="28" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5053,17 +5665,378 @@
     <xf numFmtId="0" fontId="118" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="129" fillId="48" borderId="43" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="48" borderId="42" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{5DD338C1-82ED-4982-9BB5-3EF66968FF01}"/>
     <cellStyle name="Normal 2 2" xfId="4" xr:uid="{511AF93F-5767-4AA6-B1ED-4F988213519B}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{2325A7D6-EA30-4F87-9F44-BE1E3356D852}"/>
     <cellStyle name="Normal 3 2" xfId="6" xr:uid="{ED522051-0225-4473-9518-F3E7B0C53EBF}"/>
+    <cellStyle name="Normal 3 3" xfId="7" xr:uid="{09786FEB-E820-4937-8D5F-BA3D20A84460}"/>
     <cellStyle name="Normal 4" xfId="5" xr:uid="{8BD345DC-0D02-476B-B0AB-1D49AAEB3C56}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="46">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Amasis MT Pro"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Amasis MT Pro"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Amasis MT Pro"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Amasis MT Pro"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color rgb="FF0C0C0C"/>
+        <name val="Amasis MT Pro"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Amasis MT Pro"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -6529,39 +7502,56 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2259108E-2AB4-4B88-A8A4-CCC76144E016}" name="Table2" displayName="Table2" ref="H9:I19" totalsRowShown="0">
   <autoFilter ref="H9:I19" xr:uid="{2259108E-2AB4-4B88-A8A4-CCC76144E016}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2464D0A9-6518-4603-B360-B8F9C929E469}" name="Component" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{D8AB9EE0-C195-426B-A0F6-FACE631E5D6C}" name="Description" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{2464D0A9-6518-4603-B360-B8F9C929E469}" name="Component" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{D8AB9EE0-C195-426B-A0F6-FACE631E5D6C}" name="Description" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{03F9B9C3-28DA-4E2C-B136-0D1A0C085413}" name="Table1" displayName="Table1" ref="G2:J18" totalsRowCount="1" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{03F9B9C3-28DA-4E2C-B136-0D1A0C085413}" name="Table1" displayName="Table1" ref="G2:J18" totalsRowCount="1" headerRowDxfId="43" dataDxfId="41" headerRowBorderDxfId="42" tableBorderDxfId="40" headerRowCellStyle="Normal 2">
   <autoFilter ref="G2:J17" xr:uid="{03F9B9C3-28DA-4E2C-B136-0D1A0C085413}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G9:J16">
     <sortCondition ref="H2:H17"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E2E80BDE-6659-40A7-831C-18BEB4289EFE}" name="Items" totalsRowLabel="Average" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8D63A0B8-A74A-4BC1-8ECE-9A7FCCA8433A}" name="Prices" totalsRowFunction="average" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{497FF2B8-473F-4964-887A-86E30924FC41}" name="Dates" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{477D747F-F012-437E-A2E8-D851D8F6632E}" name="Regions" totalsRowFunction="count" dataDxfId="14" totalsRowDxfId="13" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{E2E80BDE-6659-40A7-831C-18BEB4289EFE}" name="Items" totalsRowLabel="Average" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{8D63A0B8-A74A-4BC1-8ECE-9A7FCCA8433A}" name="Prices" totalsRowFunction="average" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{497FF2B8-473F-4964-887A-86E30924FC41}" name="Dates" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{477D747F-F012-437E-A2E8-D851D8F6632E}" name="Regions" totalsRowFunction="count" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark9" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7892D181-4F54-4CC4-9870-0F1B70F0D6ED}" name="Table5" displayName="Table5" ref="H21:K42" totalsRowCount="1" headerRowDxfId="12" dataDxfId="10" totalsRowDxfId="8" headerRowBorderDxfId="11" tableBorderDxfId="9" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7892D181-4F54-4CC4-9870-0F1B70F0D6ED}" name="Table5" displayName="Table5" ref="H21:K42" totalsRowCount="1" headerRowDxfId="31" dataDxfId="29" totalsRowDxfId="27" headerRowBorderDxfId="30" tableBorderDxfId="28" headerRowCellStyle="Normal 2">
   <autoFilter ref="H21:K41" xr:uid="{7892D181-4F54-4CC4-9870-0F1B70F0D6ED}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2AACB5FA-11B1-4C44-9C64-E52CD7AB7730}" name="Items" totalsRowLabel="Total" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{92EF6DDD-DF7B-4C56-A99D-A6DC933F3587}" name="Prices" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{A9F9C94F-4F23-4565-8FE5-2F93B4730101}" name="Dates" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{56FE6152-6975-46D1-8C22-C5DA30B8B866}" name="Regions" totalsRowFunction="count" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{2AACB5FA-11B1-4C44-9C64-E52CD7AB7730}" name="Items" totalsRowLabel="Total" dataDxfId="26" totalsRowDxfId="25" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{92EF6DDD-DF7B-4C56-A99D-A6DC933F3587}" name="Prices" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{A9F9C94F-4F23-4565-8FE5-2F93B4730101}" name="Dates" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{56FE6152-6975-46D1-8C22-C5DA30B8B866}" name="Regions" totalsRowFunction="count" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight17" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1D3D1180-8D86-4200-9176-C36EC0845D94}" name="Table3" displayName="Table3" ref="A1:E36" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14" headerRowCellStyle="Normal 4">
+  <autoFilter ref="A1:E36" xr:uid="{1D3D1180-8D86-4200-9176-C36EC0845D94}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E36">
+    <sortCondition ref="A1:A36"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{DC16FF6B-5D2D-4864-9DD8-943E3F4FE058}" name="Date" dataDxfId="13" dataCellStyle="Normal 4"/>
+    <tableColumn id="2" xr3:uid="{C311610C-E221-4526-B401-063BAE9C320C}" name="Months" dataDxfId="12" dataCellStyle="Normal 4"/>
+    <tableColumn id="3" xr3:uid="{9641B6CB-1C5E-4092-8443-BE42A1D8884A}" name="Items" dataDxfId="11" dataCellStyle="Normal 4"/>
+    <tableColumn id="4" xr3:uid="{B66C3345-EACF-4846-A18D-0BBE92EE3957}" name="Cost Price" dataDxfId="10" dataCellStyle="Normal 4"/>
+    <tableColumn id="5" xr3:uid="{04206549-B7A9-46DC-B90B-534EDDDC7126}" name="Cost Price2" dataDxfId="9" dataCellStyle="Normal 4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -6885,77 +7875,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="452" t="s">
+      <c r="A1" s="523" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="453"/>
-      <c r="C1" s="453"/>
-      <c r="D1" s="453"/>
-      <c r="E1" s="453"/>
-      <c r="F1" s="453"/>
+      <c r="B1" s="524"/>
+      <c r="C1" s="524"/>
+      <c r="D1" s="524"/>
+      <c r="E1" s="524"/>
+      <c r="F1" s="524"/>
     </row>
     <row r="2" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="453"/>
-      <c r="B2" s="453"/>
-      <c r="C2" s="453"/>
-      <c r="D2" s="453"/>
-      <c r="E2" s="453"/>
-      <c r="F2" s="453"/>
+      <c r="A2" s="524"/>
+      <c r="B2" s="524"/>
+      <c r="C2" s="524"/>
+      <c r="D2" s="524"/>
+      <c r="E2" s="524"/>
+      <c r="F2" s="524"/>
     </row>
     <row r="3" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="453"/>
-      <c r="B3" s="453"/>
-      <c r="C3" s="453"/>
-      <c r="D3" s="453"/>
-      <c r="E3" s="453"/>
-      <c r="F3" s="453"/>
-      <c r="G3" s="454" t="s">
+      <c r="A3" s="524"/>
+      <c r="B3" s="524"/>
+      <c r="C3" s="524"/>
+      <c r="D3" s="524"/>
+      <c r="E3" s="524"/>
+      <c r="F3" s="524"/>
+      <c r="G3" s="525" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="454"/>
-      <c r="I3" s="454"/>
-      <c r="J3" s="454"/>
-      <c r="K3" s="454"/>
+      <c r="H3" s="525"/>
+      <c r="I3" s="525"/>
+      <c r="J3" s="525"/>
+      <c r="K3" s="525"/>
     </row>
     <row r="4" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G4" s="454" t="s">
+      <c r="G4" s="525" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="454"/>
-      <c r="I4" s="454"/>
-      <c r="J4" s="454"/>
-      <c r="K4" s="454"/>
+      <c r="H4" s="525"/>
+      <c r="I4" s="525"/>
+      <c r="J4" s="525"/>
+      <c r="K4" s="525"/>
     </row>
     <row r="5" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G5" s="454" t="s">
+      <c r="G5" s="525" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="454"/>
-      <c r="I5" s="454"/>
-      <c r="J5" s="454"/>
-      <c r="K5" s="454"/>
+      <c r="H5" s="525"/>
+      <c r="I5" s="525"/>
+      <c r="J5" s="525"/>
+      <c r="K5" s="525"/>
     </row>
     <row r="6" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G6" s="454" t="s">
+      <c r="G6" s="525" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="454"/>
-      <c r="I6" s="454"/>
-      <c r="J6" s="454"/>
-      <c r="K6" s="454"/>
+      <c r="H6" s="525"/>
+      <c r="I6" s="525"/>
+      <c r="J6" s="525"/>
+      <c r="K6" s="525"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C7" s="8"/>
       <c r="E7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="454" t="s">
+      <c r="G7" s="525" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="454"/>
-      <c r="I7" s="454"/>
-      <c r="J7" s="454"/>
-      <c r="K7" s="454"/>
+      <c r="H7" s="525"/>
+      <c r="I7" s="525"/>
+      <c r="J7" s="525"/>
+      <c r="K7" s="525"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -7276,18 +8266,18 @@
         <f>IF(D3&gt;=180,"Excellent","Good")</f>
         <v>Excellent</v>
       </c>
-      <c r="F3" s="500" t="s">
+      <c r="F3" s="571" t="s">
         <v>305</v>
       </c>
       <c r="G3" s="123"/>
-      <c r="H3" s="503" t="s">
+      <c r="H3" s="574" t="s">
         <v>306</v>
       </c>
       <c r="I3" s="178" t="str" cm="1">
         <f t="array" ref="I3">_xlfn.IFS(D3&lt;130,"Poor",D3&gt;=180,"Good")</f>
         <v>Good</v>
       </c>
-      <c r="J3" s="506" t="s">
+      <c r="J3" s="577" t="s">
         <v>307</v>
       </c>
       <c r="K3" s="139"/>
@@ -7307,14 +8297,14 @@
         <f>IF(D4&gt;=180,"Excellent","Good")</f>
         <v>Excellent</v>
       </c>
-      <c r="F4" s="501"/>
+      <c r="F4" s="572"/>
       <c r="G4" s="123"/>
-      <c r="H4" s="504"/>
+      <c r="H4" s="575"/>
       <c r="I4" s="178" t="str" cm="1">
         <f t="array" ref="I4">_xlfn.IFS(D4&lt;130,"Poor",D4&gt;=180,"Good")</f>
         <v>Good</v>
       </c>
-      <c r="J4" s="507"/>
+      <c r="J4" s="578"/>
       <c r="K4" s="139"/>
       <c r="L4" s="140"/>
     </row>
@@ -7332,14 +8322,14 @@
         <f t="shared" ref="E5:E34" si="0">IF(D5&gt;=180,"Excellent","Good")</f>
         <v>Good</v>
       </c>
-      <c r="F5" s="501"/>
+      <c r="F5" s="572"/>
       <c r="G5" s="123"/>
-      <c r="H5" s="505"/>
+      <c r="H5" s="576"/>
       <c r="I5" s="178" t="str" cm="1">
         <f t="array" ref="I5">_xlfn.IFS(D5&lt;150,"Poor",D5&gt;=150,"Good")</f>
         <v>Poor</v>
       </c>
-      <c r="J5" s="507"/>
+      <c r="J5" s="578"/>
       <c r="K5" s="141"/>
       <c r="L5" s="181" t="s">
         <v>309</v>
@@ -7359,11 +8349,11 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F6" s="501"/>
+      <c r="F6" s="572"/>
       <c r="G6" s="122"/>
       <c r="H6" s="120"/>
       <c r="I6" s="120"/>
-      <c r="J6" s="507"/>
+      <c r="J6" s="578"/>
       <c r="K6" s="141"/>
       <c r="L6" s="117" t="s">
         <v>310</v>
@@ -7383,16 +8373,16 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F7" s="501"/>
+      <c r="F7" s="572"/>
       <c r="G7" s="123"/>
-      <c r="H7" s="509" t="s">
+      <c r="H7" s="580" t="s">
         <v>312</v>
       </c>
       <c r="I7" s="178" t="str" cm="1">
         <f t="array" ref="I7">_xlfn.IFS(D6&lt;100,"very poor",D6&lt;=150,"average",D6&gt;=150,"Goog")</f>
         <v>average</v>
       </c>
-      <c r="J7" s="507"/>
+      <c r="J7" s="578"/>
       <c r="K7" s="141"/>
       <c r="L7" s="120"/>
     </row>
@@ -7410,14 +8400,14 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F8" s="501"/>
+      <c r="F8" s="572"/>
       <c r="G8" s="123"/>
-      <c r="H8" s="510"/>
+      <c r="H8" s="581"/>
       <c r="I8" s="178" t="str" cm="1">
         <f t="array" ref="I8">_xlfn.IFS(D7&lt;100,"very poor",D7&lt;=150,"average",D7&gt;=150,"Goog")</f>
         <v>average</v>
       </c>
-      <c r="J8" s="507"/>
+      <c r="J8" s="578"/>
       <c r="K8" s="139"/>
       <c r="L8" s="139"/>
     </row>
@@ -7435,14 +8425,14 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F9" s="501"/>
+      <c r="F9" s="572"/>
       <c r="G9" s="123"/>
-      <c r="H9" s="511"/>
+      <c r="H9" s="582"/>
       <c r="I9" s="178" t="str" cm="1">
         <f t="array" ref="I9">_xlfn.IFS(D8&lt;100,"very poor",D8&lt;=150,"average",D8&gt;=150,"Good")</f>
         <v>Good</v>
       </c>
-      <c r="J9" s="507"/>
+      <c r="J9" s="578"/>
       <c r="K9" s="139"/>
       <c r="L9" s="139"/>
     </row>
@@ -7460,11 +8450,11 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F10" s="501"/>
+      <c r="F10" s="572"/>
       <c r="G10" s="122"/>
       <c r="H10" s="115"/>
       <c r="I10" s="142"/>
-      <c r="J10" s="507"/>
+      <c r="J10" s="578"/>
       <c r="K10" s="139"/>
       <c r="L10" s="139"/>
     </row>
@@ -7482,16 +8472,16 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F11" s="501"/>
+      <c r="F11" s="572"/>
       <c r="G11" s="123"/>
-      <c r="H11" s="512" t="s">
+      <c r="H11" s="583" t="s">
         <v>317</v>
       </c>
       <c r="I11" s="180" t="str" cm="1">
         <f t="array" ref="I11">_xlfn.IFS(D10&lt;100,"very poor",D10&lt;=100,"poor",D10&lt;=150,"Good",D10&gt;=200,"excellent")</f>
         <v>very poor</v>
       </c>
-      <c r="J11" s="507"/>
+      <c r="J11" s="578"/>
       <c r="K11" s="139"/>
       <c r="L11" s="139"/>
     </row>
@@ -7509,14 +8499,14 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F12" s="501"/>
+      <c r="F12" s="572"/>
       <c r="G12" s="123"/>
-      <c r="H12" s="513"/>
+      <c r="H12" s="584"/>
       <c r="I12" s="180" t="str" cm="1">
         <f t="array" ref="I12">_xlfn.IFS(D11&lt;100,"very poor",D11&lt;=100,"poor",D11&lt;=150,"Good",D11&gt;=200,"excellent")</f>
         <v>Good</v>
       </c>
-      <c r="J12" s="507"/>
+      <c r="J12" s="578"/>
       <c r="K12" s="139"/>
       <c r="L12" s="179"/>
     </row>
@@ -7534,14 +8524,14 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F13" s="501"/>
+      <c r="F13" s="572"/>
       <c r="G13" s="123"/>
-      <c r="H13" s="514"/>
+      <c r="H13" s="585"/>
       <c r="I13" s="180" t="str" cm="1">
         <f t="array" ref="I13">_xlfn.IFS(D12&lt;100,"very poor",D12&lt;=100,"poor",D12&lt;=150,"Good",D12&gt;=200,"excellent")</f>
         <v>excellent</v>
       </c>
-      <c r="J13" s="508"/>
+      <c r="J13" s="579"/>
       <c r="K13" s="139"/>
       <c r="L13" s="139"/>
     </row>
@@ -7559,12 +8549,12 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F14" s="501"/>
+      <c r="F14" s="572"/>
       <c r="G14" s="123"/>
-      <c r="H14" s="515" t="s">
+      <c r="H14" s="586" t="s">
         <v>281</v>
       </c>
-      <c r="I14" s="516"/>
+      <c r="I14" s="587"/>
       <c r="J14" s="122"/>
       <c r="K14" s="139"/>
       <c r="L14" s="139"/>
@@ -7583,7 +8573,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F15" s="501"/>
+      <c r="F15" s="572"/>
       <c r="G15" s="122"/>
       <c r="H15" s="122"/>
       <c r="I15" s="122"/>
@@ -7605,7 +8595,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F16" s="501"/>
+      <c r="F16" s="572"/>
       <c r="G16" s="122"/>
       <c r="H16" s="122"/>
       <c r="I16" s="122"/>
@@ -7627,7 +8617,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F17" s="501"/>
+      <c r="F17" s="572"/>
       <c r="G17" s="122"/>
       <c r="H17" s="122"/>
       <c r="I17" s="122"/>
@@ -7649,7 +8639,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F18" s="501"/>
+      <c r="F18" s="572"/>
       <c r="G18" s="122"/>
       <c r="H18" s="184"/>
       <c r="I18" s="122"/>
@@ -7671,7 +8661,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F19" s="501"/>
+      <c r="F19" s="572"/>
       <c r="G19" s="182"/>
       <c r="H19" s="185"/>
       <c r="I19" s="183" t="s">
@@ -7695,7 +8685,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F20" s="501"/>
+      <c r="F20" s="572"/>
       <c r="G20" s="182"/>
       <c r="H20" s="185"/>
       <c r="I20" s="183"/>
@@ -7717,7 +8707,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F21" s="502"/>
+      <c r="F21" s="573"/>
       <c r="G21" s="122"/>
       <c r="H21" s="186" t="s">
         <v>121</v>
@@ -7753,7 +8743,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F22" s="500" t="s">
+      <c r="F22" s="571" t="s">
         <v>305</v>
       </c>
       <c r="G22" s="122"/>
@@ -7787,7 +8777,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F23" s="501"/>
+      <c r="F23" s="572"/>
       <c r="G23" s="122"/>
       <c r="H23" s="189" t="s">
         <v>127</v>
@@ -7817,7 +8807,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F24" s="501"/>
+      <c r="F24" s="572"/>
       <c r="G24" s="122"/>
       <c r="H24" s="189" t="s">
         <v>129</v>
@@ -7847,7 +8837,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F25" s="501"/>
+      <c r="F25" s="572"/>
       <c r="G25" s="122"/>
       <c r="H25" s="189" t="s">
         <v>130</v>
@@ -7877,7 +8867,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F26" s="501"/>
+      <c r="F26" s="572"/>
       <c r="G26" s="122"/>
       <c r="H26" s="189" t="s">
         <v>131</v>
@@ -7907,7 +8897,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F27" s="501"/>
+      <c r="F27" s="572"/>
       <c r="G27" s="122"/>
       <c r="H27" s="189" t="s">
         <v>133</v>
@@ -7937,7 +8927,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F28" s="501"/>
+      <c r="F28" s="572"/>
       <c r="G28" s="122"/>
       <c r="H28" s="189" t="s">
         <v>129</v>
@@ -7967,7 +8957,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F29" s="501"/>
+      <c r="F29" s="572"/>
       <c r="G29" s="122"/>
       <c r="H29" s="189" t="s">
         <v>135</v>
@@ -7997,7 +8987,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F30" s="501"/>
+      <c r="F30" s="572"/>
       <c r="G30" s="122"/>
       <c r="H30" s="189" t="s">
         <v>136</v>
@@ -8027,7 +9017,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F31" s="501"/>
+      <c r="F31" s="572"/>
       <c r="G31" s="122"/>
       <c r="H31" s="189" t="s">
         <v>137</v>
@@ -8057,7 +9047,7 @@
         <f t="shared" si="0"/>
         <v>Excellent</v>
       </c>
-      <c r="F32" s="501"/>
+      <c r="F32" s="572"/>
       <c r="G32" s="122"/>
       <c r="H32" s="189" t="s">
         <v>138</v>
@@ -8087,7 +9077,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F33" s="501"/>
+      <c r="F33" s="572"/>
       <c r="G33" s="122"/>
       <c r="H33" s="189" t="s">
         <v>139</v>
@@ -8117,7 +9107,7 @@
         <f t="shared" si="0"/>
         <v>Good</v>
       </c>
-      <c r="F34" s="501"/>
+      <c r="F34" s="572"/>
       <c r="G34" s="122"/>
       <c r="H34" s="189" t="s">
         <v>140</v>
@@ -8147,7 +9137,7 @@
         <f>IF(D35&gt;=180,"Excellent","Good")</f>
         <v>Good</v>
       </c>
-      <c r="F35" s="502"/>
+      <c r="F35" s="573"/>
       <c r="G35" s="122"/>
       <c r="H35" s="189" t="s">
         <v>141</v>
@@ -8414,11 +9404,11 @@
       <c r="F6" s="243">
         <v>90</v>
       </c>
-      <c r="I6" s="520" t="s">
+      <c r="I6" s="591" t="s">
         <v>389</v>
       </c>
-      <c r="J6" s="520"/>
-      <c r="K6" s="520"/>
+      <c r="J6" s="591"/>
+      <c r="K6" s="591"/>
       <c r="L6" s="251" t="b">
         <v>1</v>
       </c>
@@ -8448,9 +9438,9 @@
       <c r="F7" s="86">
         <v>40</v>
       </c>
-      <c r="I7" s="520"/>
-      <c r="J7" s="520"/>
-      <c r="K7" s="520"/>
+      <c r="I7" s="591"/>
+      <c r="J7" s="591"/>
+      <c r="K7" s="591"/>
       <c r="L7" s="251" t="b">
         <v>0</v>
       </c>
@@ -8480,9 +9470,9 @@
       <c r="F8" s="86">
         <v>80</v>
       </c>
-      <c r="I8" s="520"/>
-      <c r="J8" s="520"/>
-      <c r="K8" s="520"/>
+      <c r="I8" s="591"/>
+      <c r="J8" s="591"/>
+      <c r="K8" s="591"/>
       <c r="L8" s="251" t="b">
         <v>1</v>
       </c>
@@ -8512,9 +9502,9 @@
       <c r="F9" s="86">
         <v>100</v>
       </c>
-      <c r="I9" s="520"/>
-      <c r="J9" s="520"/>
-      <c r="K9" s="520"/>
+      <c r="I9" s="591"/>
+      <c r="J9" s="591"/>
+      <c r="K9" s="591"/>
       <c r="L9" s="251" t="b">
         <v>0</v>
       </c>
@@ -8568,11 +9558,11 @@
       <c r="F11" s="86">
         <v>35</v>
       </c>
-      <c r="I11" s="521" t="s">
+      <c r="I11" s="592" t="s">
         <v>390</v>
       </c>
-      <c r="J11" s="521"/>
-      <c r="K11" s="521"/>
+      <c r="J11" s="592"/>
+      <c r="K11" s="592"/>
       <c r="L11" s="257" t="b">
         <v>1</v>
       </c>
@@ -8602,9 +9592,9 @@
       <c r="F12" s="86">
         <v>90</v>
       </c>
-      <c r="I12" s="521"/>
-      <c r="J12" s="521"/>
-      <c r="K12" s="521"/>
+      <c r="I12" s="592"/>
+      <c r="J12" s="592"/>
+      <c r="K12" s="592"/>
       <c r="L12" s="257" t="b">
         <v>0</v>
       </c>
@@ -8634,9 +9624,9 @@
       <c r="F13" s="86">
         <v>25</v>
       </c>
-      <c r="I13" s="521"/>
-      <c r="J13" s="521"/>
-      <c r="K13" s="521"/>
+      <c r="I13" s="592"/>
+      <c r="J13" s="592"/>
+      <c r="K13" s="592"/>
       <c r="L13" s="257" t="b">
         <v>1</v>
       </c>
@@ -8666,9 +9656,9 @@
       <c r="F14" s="86">
         <v>85</v>
       </c>
-      <c r="I14" s="521"/>
-      <c r="J14" s="521"/>
-      <c r="K14" s="521"/>
+      <c r="I14" s="592"/>
+      <c r="J14" s="592"/>
+      <c r="K14" s="592"/>
       <c r="L14" s="257" t="b">
         <v>0</v>
       </c>
@@ -8722,11 +9712,11 @@
       <c r="F16" s="86">
         <v>60</v>
       </c>
-      <c r="I16" s="522" t="s">
+      <c r="I16" s="593" t="s">
         <v>391</v>
       </c>
-      <c r="J16" s="522"/>
-      <c r="K16" s="522"/>
+      <c r="J16" s="593"/>
+      <c r="K16" s="593"/>
       <c r="L16" s="261" t="b">
         <v>1</v>
       </c>
@@ -8746,9 +9736,9 @@
       <c r="D17" s="86"/>
       <c r="E17" s="86"/>
       <c r="F17" s="244"/>
-      <c r="I17" s="522"/>
-      <c r="J17" s="522"/>
-      <c r="K17" s="522"/>
+      <c r="I17" s="593"/>
+      <c r="J17" s="593"/>
+      <c r="K17" s="593"/>
       <c r="L17" s="261" t="b">
         <v>1</v>
       </c>
@@ -8763,9 +9753,9 @@
       </c>
     </row>
     <row r="18" spans="2:15" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="I18" s="522"/>
-      <c r="J18" s="522"/>
-      <c r="K18" s="522"/>
+      <c r="I18" s="593"/>
+      <c r="J18" s="593"/>
+      <c r="K18" s="593"/>
       <c r="L18" s="261" t="b">
         <v>0</v>
       </c>
@@ -8780,9 +9770,9 @@
       </c>
     </row>
     <row r="19" spans="2:15" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="I19" s="522"/>
-      <c r="J19" s="522"/>
-      <c r="K19" s="522"/>
+      <c r="I19" s="593"/>
+      <c r="J19" s="593"/>
+      <c r="K19" s="593"/>
       <c r="L19" s="261" t="b">
         <v>0</v>
       </c>
@@ -8797,7 +9787,7 @@
       </c>
     </row>
     <row r="20" spans="2:15" ht="55.8" x14ac:dyDescent="0.3">
-      <c r="B20" s="517" t="s">
+      <c r="B20" s="588" t="s">
         <v>380</v>
       </c>
       <c r="C20" s="247" t="s">
@@ -8807,7 +9797,7 @@
         <f>OR(D3&gt;70,E3&gt;70,F3&gt;70)</f>
         <v>1</v>
       </c>
-      <c r="E20" s="518" t="s">
+      <c r="E20" s="589" t="s">
         <v>382</v>
       </c>
       <c r="F20" s="249" t="b">
@@ -8821,9 +9811,9 @@
         <f>AND(D5&gt;70,E5&gt;70,F5&gt;70)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="522"/>
-      <c r="J20" s="522"/>
-      <c r="K20" s="522"/>
+      <c r="I20" s="593"/>
+      <c r="J20" s="593"/>
+      <c r="K20" s="593"/>
       <c r="L20" s="263" t="s">
         <v>392</v>
       </c>
@@ -8834,7 +9824,7 @@
       <c r="O20" s="262"/>
     </row>
     <row r="21" spans="2:15" ht="18" x14ac:dyDescent="0.3">
-      <c r="B21" s="517"/>
+      <c r="B21" s="588"/>
       <c r="C21" s="246" t="s">
         <v>384</v>
       </c>
@@ -8842,7 +9832,7 @@
         <f>OR(D4&gt;70,E4&gt;70,F4&gt;70)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="519"/>
+      <c r="E21" s="590"/>
       <c r="F21" s="249" t="b">
         <f>AND(D10&gt;70,E10&gt;70,F10&gt;70)</f>
         <v>1</v>
@@ -9031,7 +10021,7 @@
       <c r="F7" s="216">
         <v>35</v>
       </c>
-      <c r="G7" s="524" t="s">
+      <c r="G7" s="595" t="s">
         <v>360</v>
       </c>
       <c r="H7" s="217" t="b">
@@ -9066,7 +10056,7 @@
       <c r="F8" s="216">
         <v>40</v>
       </c>
-      <c r="G8" s="524"/>
+      <c r="G8" s="595"/>
       <c r="H8" s="217" t="b">
         <f>OR(D5&gt;=50,E5&gt;=50,F5&gt;=50)</f>
         <v>1</v>
@@ -9099,7 +10089,7 @@
       <c r="F9" s="216">
         <v>80</v>
       </c>
-      <c r="G9" s="524"/>
+      <c r="G9" s="595"/>
       <c r="H9" s="217" t="b">
         <f>OR(D6&gt;=50,E6&gt;=50,F6&gt;=50)</f>
         <v>0</v>
@@ -9154,7 +10144,7 @@
       <c r="F11" s="221">
         <v>75</v>
       </c>
-      <c r="G11" s="525" t="s">
+      <c r="G11" s="596" t="s">
         <v>361</v>
       </c>
       <c r="H11" s="224" t="b">
@@ -9189,7 +10179,7 @@
       <c r="F12" s="221">
         <v>35</v>
       </c>
-      <c r="G12" s="526"/>
+      <c r="G12" s="597"/>
       <c r="H12" s="224" t="b">
         <f t="shared" ref="H12:H13" si="1">AND(D8&gt;=50,E8&gt;=50,F8&gt;=50)</f>
         <v>0</v>
@@ -9222,7 +10212,7 @@
       <c r="F13" s="227">
         <v>90</v>
       </c>
-      <c r="G13" s="527"/>
+      <c r="G13" s="598"/>
       <c r="H13" s="224" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -9277,7 +10267,7 @@
       <c r="F15" s="227">
         <v>85</v>
       </c>
-      <c r="G15" s="525" t="s">
+      <c r="G15" s="596" t="s">
         <v>362</v>
       </c>
       <c r="H15" s="231" t="b">
@@ -9312,7 +10302,7 @@
       <c r="F16" s="227">
         <v>50</v>
       </c>
-      <c r="G16" s="526"/>
+      <c r="G16" s="597"/>
       <c r="H16" s="231" t="b">
         <f t="shared" ref="H16:H17" si="4">_xlfn.XOR(D11&gt;=50,E11&gt;=50,F11&gt;=50)</f>
         <v>1</v>
@@ -9345,7 +10335,7 @@
       <c r="F17" s="227">
         <v>60</v>
       </c>
-      <c r="G17" s="527"/>
+      <c r="G17" s="598"/>
       <c r="H17" s="231" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -9377,14 +10367,14 @@
       <c r="K18" s="210"/>
     </row>
     <row r="20" spans="2:11" ht="51.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="528" t="s">
+      <c r="B20" s="599" t="s">
         <v>364</v>
       </c>
       <c r="C20" s="234" t="b">
         <f>ISBLANK(G10)</f>
         <v>1</v>
       </c>
-      <c r="D20" s="528" t="s">
+      <c r="D20" s="599" t="s">
         <v>365</v>
       </c>
       <c r="E20" s="234" t="b">
@@ -9406,12 +10396,12 @@
       </c>
     </row>
     <row r="21" spans="2:11" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="529"/>
+      <c r="B21" s="600"/>
       <c r="C21" s="234" t="b">
         <f>ISBLANK(G11)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="529"/>
+      <c r="D21" s="600"/>
       <c r="E21" s="234" t="b">
         <f>IFERROR(H8, 0)</f>
         <v>1</v>
@@ -9434,14 +10424,14 @@
       </c>
     </row>
     <row r="22" spans="2:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B22" s="528" t="s">
+      <c r="B22" s="599" t="s">
         <v>366</v>
       </c>
       <c r="C22" s="234" t="b">
         <f>ISERROR(G10)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="528" t="s">
+      <c r="D22" s="599" t="s">
         <v>367</v>
       </c>
       <c r="E22" s="234" t="b">
@@ -9450,19 +10440,19 @@
       </c>
       <c r="G22" s="210"/>
       <c r="H22" s="210"/>
-      <c r="I22" s="523" t="s">
+      <c r="I22" s="594" t="s">
         <v>373</v>
       </c>
-      <c r="J22" s="523"/>
-      <c r="K22" s="523"/>
+      <c r="J22" s="594"/>
+      <c r="K22" s="594"/>
     </row>
     <row r="23" spans="2:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B23" s="529"/>
+      <c r="B23" s="600"/>
       <c r="C23" s="234" t="b">
         <f>ISERROR(G11)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="529"/>
+      <c r="D23" s="600"/>
       <c r="E23" s="234" t="b">
         <f>_xlfn.IFNA(H12, 0)</f>
         <v>0</v>
@@ -9741,12 +10731,12 @@
         <f>HLOOKUP(B11,$C$5:$P$7,3,FALSE)</f>
         <v>45663</v>
       </c>
-      <c r="F11" s="530" t="s">
+      <c r="F11" s="601" t="s">
         <v>408</v>
       </c>
-      <c r="G11" s="499"/>
-      <c r="H11" s="499"/>
-      <c r="I11" s="499"/>
+      <c r="G11" s="544"/>
+      <c r="H11" s="544"/>
+      <c r="I11" s="544"/>
     </row>
     <row r="12" spans="2:16" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B12" s="278" t="s">
@@ -9760,10 +10750,10 @@
         <f t="shared" ref="D12:D18" si="0">HLOOKUP(B12,$C$5:$P$7,3,FALSE)</f>
         <v>45666</v>
       </c>
-      <c r="F12" s="499"/>
-      <c r="G12" s="499"/>
-      <c r="H12" s="499"/>
-      <c r="I12" s="499"/>
+      <c r="F12" s="544"/>
+      <c r="G12" s="544"/>
+      <c r="H12" s="544"/>
+      <c r="I12" s="544"/>
     </row>
     <row r="13" spans="2:16" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B13" s="278" t="s">
@@ -9777,10 +10767,10 @@
         <f t="shared" si="0"/>
         <v>45676</v>
       </c>
-      <c r="F13" s="499"/>
-      <c r="G13" s="499"/>
-      <c r="H13" s="499"/>
-      <c r="I13" s="499"/>
+      <c r="F13" s="544"/>
+      <c r="G13" s="544"/>
+      <c r="H13" s="544"/>
+      <c r="I13" s="544"/>
     </row>
     <row r="14" spans="2:16" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B14" s="278" t="s">
@@ -9794,10 +10784,10 @@
         <f t="shared" si="0"/>
         <v>45658</v>
       </c>
-      <c r="F14" s="499"/>
-      <c r="G14" s="499"/>
-      <c r="H14" s="499"/>
-      <c r="I14" s="499"/>
+      <c r="F14" s="544"/>
+      <c r="G14" s="544"/>
+      <c r="H14" s="544"/>
+      <c r="I14" s="544"/>
     </row>
     <row r="15" spans="2:16" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B15" s="281" t="s">
@@ -9811,10 +10801,10 @@
         <f t="shared" si="0"/>
         <v>45677</v>
       </c>
-      <c r="F15" s="499"/>
-      <c r="G15" s="499"/>
-      <c r="H15" s="499"/>
-      <c r="I15" s="499"/>
+      <c r="F15" s="544"/>
+      <c r="G15" s="544"/>
+      <c r="H15" s="544"/>
+      <c r="I15" s="544"/>
     </row>
     <row r="16" spans="2:16" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B16" s="281" t="s">
@@ -9828,10 +10818,10 @@
         <f t="shared" si="0"/>
         <v>45667</v>
       </c>
-      <c r="F16" s="499"/>
-      <c r="G16" s="499"/>
-      <c r="H16" s="499"/>
-      <c r="I16" s="499"/>
+      <c r="F16" s="544"/>
+      <c r="G16" s="544"/>
+      <c r="H16" s="544"/>
+      <c r="I16" s="544"/>
     </row>
     <row r="17" spans="2:9" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B17" s="281" t="s">
@@ -9845,10 +10835,10 @@
         <f t="shared" si="0"/>
         <v>45674</v>
       </c>
-      <c r="F17" s="499"/>
-      <c r="G17" s="499"/>
-      <c r="H17" s="499"/>
-      <c r="I17" s="499"/>
+      <c r="F17" s="544"/>
+      <c r="G17" s="544"/>
+      <c r="H17" s="544"/>
+      <c r="I17" s="544"/>
     </row>
     <row r="18" spans="2:9" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B18" s="281" t="s">
@@ -10405,14 +11395,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="499" t="s">
+      <c r="F1" s="544" t="s">
         <v>429</v>
       </c>
-      <c r="G1" s="499"/>
+      <c r="G1" s="544"/>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="F2" s="499"/>
-      <c r="G2" s="499"/>
+      <c r="F2" s="544"/>
+      <c r="G2" s="544"/>
     </row>
     <row r="3" spans="2:8" ht="18" x14ac:dyDescent="0.3">
       <c r="B3" s="367" t="s">
@@ -11418,11 +12408,11 @@
       <c r="U58" s="372" t="s">
         <v>405</v>
       </c>
-      <c r="V58" s="531" t="s">
+      <c r="V58" s="602" t="s">
         <v>435</v>
       </c>
-      <c r="W58" s="531"/>
-      <c r="X58" s="531"/>
+      <c r="W58" s="602"/>
+      <c r="X58" s="602"/>
     </row>
     <row r="59" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H59" s="393"/>
@@ -11444,9 +12434,9 @@
       <c r="S59" s="374"/>
       <c r="T59" s="374"/>
       <c r="U59" s="374"/>
-      <c r="V59" s="531"/>
-      <c r="W59" s="531"/>
-      <c r="X59" s="531"/>
+      <c r="V59" s="602"/>
+      <c r="W59" s="602"/>
+      <c r="X59" s="602"/>
     </row>
     <row r="60" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H60" s="393"/>
@@ -11465,9 +12455,9 @@
       <c r="S60" s="374"/>
       <c r="T60" s="374"/>
       <c r="U60" s="374"/>
-      <c r="V60" s="531"/>
-      <c r="W60" s="531"/>
-      <c r="X60" s="531"/>
+      <c r="V60" s="602"/>
+      <c r="W60" s="602"/>
+      <c r="X60" s="602"/>
     </row>
     <row r="61" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H61" s="393"/>
@@ -11486,9 +12476,9 @@
       <c r="S61" s="381"/>
       <c r="T61" s="381"/>
       <c r="U61" s="381"/>
-      <c r="V61" s="531"/>
-      <c r="W61" s="531"/>
-      <c r="X61" s="531"/>
+      <c r="V61" s="602"/>
+      <c r="W61" s="602"/>
+      <c r="X61" s="602"/>
     </row>
     <row r="62" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H62" s="393"/>
@@ -11507,9 +12497,9 @@
       <c r="S62" s="381"/>
       <c r="T62" s="381"/>
       <c r="U62" s="381"/>
-      <c r="V62" s="531"/>
-      <c r="W62" s="531"/>
-      <c r="X62" s="531"/>
+      <c r="V62" s="602"/>
+      <c r="W62" s="602"/>
+      <c r="X62" s="602"/>
     </row>
     <row r="63" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H63" s="382"/>
@@ -11526,9 +12516,9 @@
       <c r="S63" s="382"/>
       <c r="T63" s="382"/>
       <c r="U63" s="382"/>
-      <c r="V63" s="531"/>
-      <c r="W63" s="531"/>
-      <c r="X63" s="531"/>
+      <c r="V63" s="602"/>
+      <c r="W63" s="602"/>
+      <c r="X63" s="602"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11566,7 +12556,7 @@
       <c r="A1" s="305"/>
     </row>
     <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="A2" s="537">
+      <c r="A2" s="608">
         <v>1</v>
       </c>
       <c r="B2" s="307" t="s">
@@ -11583,7 +12573,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="537"/>
+      <c r="A3" s="608"/>
       <c r="B3" s="309">
         <v>36533</v>
       </c>
@@ -11598,7 +12588,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="537"/>
+      <c r="A4" s="608"/>
       <c r="B4" s="309">
         <v>36540</v>
       </c>
@@ -11614,7 +12604,7 @@
       <c r="F4" s="305"/>
     </row>
     <row r="5" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="537"/>
+      <c r="A5" s="608"/>
       <c r="B5" s="309">
         <v>36526</v>
       </c>
@@ -11630,7 +12620,7 @@
       <c r="F5" s="305"/>
     </row>
     <row r="6" spans="1:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="A6" s="537"/>
+      <c r="A6" s="608"/>
       <c r="B6" s="309">
         <v>36536</v>
       </c>
@@ -11655,12 +12645,12 @@
       <c r="I6" s="324" t="s">
         <v>403</v>
       </c>
-      <c r="J6" s="538" t="s">
+      <c r="J6" s="609" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="537"/>
+      <c r="A7" s="608"/>
       <c r="B7" s="309">
         <v>36528</v>
       </c>
@@ -11685,10 +12675,10 @@
         <f>_xlfn.XLOOKUP(G7,$D$3:$D$19,$E$3:$E$19)</f>
         <v>2000</v>
       </c>
-      <c r="J7" s="539"/>
+      <c r="J7" s="610"/>
     </row>
     <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A8" s="537"/>
+      <c r="A8" s="608"/>
       <c r="B8" s="309">
         <v>36544</v>
       </c>
@@ -11715,10 +12705,10 @@
         <f>_xlfn.XLOOKUP(G8,D2:D19,E2:E19,,,-1)</f>
         <v>28000</v>
       </c>
-      <c r="J8" s="539"/>
+      <c r="J8" s="610"/>
     </row>
     <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A9" s="537"/>
+      <c r="A9" s="608"/>
       <c r="B9" s="309">
         <v>36538</v>
       </c>
@@ -11743,10 +12733,10 @@
         <f t="shared" ref="I9" si="0">_xlfn.XLOOKUP(G9,$D$3:$D$19,$E$3:$E$19)</f>
         <v>30000</v>
       </c>
-      <c r="J9" s="539"/>
+      <c r="J9" s="610"/>
     </row>
     <row r="10" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="537"/>
+      <c r="A10" s="608"/>
       <c r="B10" s="309">
         <v>36532</v>
       </c>
@@ -11771,10 +12761,10 @@
         <f t="shared" ref="I10" si="2">_xlfn.XLOOKUP(G10,D4:D21,E4:E21,,,-1)</f>
         <v>38000</v>
       </c>
-      <c r="J10" s="539"/>
+      <c r="J10" s="610"/>
     </row>
     <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A11" s="537"/>
+      <c r="A11" s="608"/>
       <c r="B11" s="309">
         <v>36531</v>
       </c>
@@ -11801,10 +12791,10 @@
         <f t="shared" ref="I11" si="4">_xlfn.XLOOKUP(G11,$D$3:$D$19,$E$3:$E$19)</f>
         <v>20000</v>
       </c>
-      <c r="J11" s="539"/>
+      <c r="J11" s="610"/>
     </row>
     <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A12" s="537"/>
+      <c r="A12" s="608"/>
       <c r="B12" s="309">
         <v>36538</v>
       </c>
@@ -11829,10 +12819,10 @@
         <f t="shared" ref="I12" si="6">_xlfn.XLOOKUP(G12,D6:D23,E6:E23,,,-1)</f>
         <v>25000</v>
       </c>
-      <c r="J12" s="539"/>
+      <c r="J12" s="610"/>
     </row>
     <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A13" s="537"/>
+      <c r="A13" s="608"/>
       <c r="B13" s="309">
         <v>36542</v>
       </c>
@@ -11859,10 +12849,10 @@
         <f t="shared" ref="I13" si="7">_xlfn.XLOOKUP(G13,$D$3:$D$19,$E$3:$E$19)</f>
         <v>10000</v>
       </c>
-      <c r="J13" s="539"/>
+      <c r="J13" s="610"/>
     </row>
     <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="537"/>
+      <c r="A14" s="608"/>
       <c r="B14" s="313">
         <v>36535</v>
       </c>
@@ -11886,10 +12876,10 @@
         <f t="shared" ref="I14" si="9">_xlfn.XLOOKUP(G14,D8:D25,E8:E25,,,-1)</f>
         <v>42000</v>
       </c>
-      <c r="J14" s="539"/>
+      <c r="J14" s="610"/>
     </row>
     <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A15" s="537"/>
+      <c r="A15" s="608"/>
       <c r="B15" s="316">
         <v>36545</v>
       </c>
@@ -11913,10 +12903,10 @@
         <f t="shared" ref="I15" si="11">_xlfn.XLOOKUP(G15,$D$3:$D$19,$E$3:$E$19)</f>
         <v>20000</v>
       </c>
-      <c r="J15" s="540"/>
+      <c r="J15" s="611"/>
     </row>
     <row r="16" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="537"/>
+      <c r="A16" s="608"/>
       <c r="B16" s="316">
         <v>36529</v>
       </c>
@@ -11931,7 +12921,7 @@
       </c>
     </row>
     <row r="17" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="537"/>
+      <c r="A17" s="608"/>
       <c r="B17" s="316">
         <v>36531</v>
       </c>
@@ -11946,7 +12936,7 @@
       </c>
     </row>
     <row r="18" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="537"/>
+      <c r="A18" s="608"/>
       <c r="B18" s="316">
         <v>36535</v>
       </c>
@@ -11961,7 +12951,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="537"/>
+      <c r="A19" s="608"/>
       <c r="B19" s="316">
         <v>36531</v>
       </c>
@@ -12215,25 +13205,25 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="36" x14ac:dyDescent="0.3">
-      <c r="A25" s="537">
+      <c r="A25" s="608">
         <v>2</v>
       </c>
-      <c r="B25" s="537"/>
-      <c r="C25" s="537"/>
-      <c r="D25" s="537"/>
-      <c r="E25" s="537"/>
-      <c r="F25" s="537"/>
-      <c r="G25" s="537"/>
-      <c r="H25" s="537"/>
-      <c r="I25" s="537"/>
-      <c r="J25" s="537"/>
-      <c r="K25" s="537"/>
-      <c r="L25" s="537"/>
-      <c r="M25" s="537"/>
-      <c r="N25" s="537"/>
-      <c r="O25" s="537"/>
-      <c r="P25" s="537"/>
-      <c r="Q25" s="537"/>
+      <c r="B25" s="608"/>
+      <c r="C25" s="608"/>
+      <c r="D25" s="608"/>
+      <c r="E25" s="608"/>
+      <c r="F25" s="608"/>
+      <c r="G25" s="608"/>
+      <c r="H25" s="608"/>
+      <c r="I25" s="608"/>
+      <c r="J25" s="608"/>
+      <c r="K25" s="608"/>
+      <c r="L25" s="608"/>
+      <c r="M25" s="608"/>
+      <c r="N25" s="608"/>
+      <c r="O25" s="608"/>
+      <c r="P25" s="608"/>
+      <c r="Q25" s="608"/>
       <c r="R25" s="305"/>
       <c r="S25" s="305"/>
     </row>
@@ -12248,7 +13238,7 @@
       <c r="D27" s="338" t="s">
         <v>403</v>
       </c>
-      <c r="E27" s="541" t="s">
+      <c r="E27" s="612" t="s">
         <v>412</v>
       </c>
     </row>
@@ -12265,7 +13255,7 @@
         <f>_xlfn.XLOOKUP(B28,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
         <v>2000</v>
       </c>
-      <c r="E28" s="541"/>
+      <c r="E28" s="612"/>
     </row>
     <row r="29" spans="1:19" ht="36" x14ac:dyDescent="0.3">
       <c r="A29" s="320" t="s">
@@ -12282,7 +13272,7 @@
         <f>_xlfn.XLOOKUP(B29,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
         <v>2000</v>
       </c>
-      <c r="E29" s="541"/>
+      <c r="E29" s="612"/>
     </row>
     <row r="30" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A30" s="305"/>
@@ -12297,7 +13287,7 @@
         <f t="shared" ref="D30" si="13">_xlfn.XLOOKUP(B30,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
         <v>30000</v>
       </c>
-      <c r="E30" s="541"/>
+      <c r="E30" s="612"/>
     </row>
     <row r="31" spans="1:19" ht="36" x14ac:dyDescent="0.3">
       <c r="A31" s="320" t="s">
@@ -12314,7 +13304,7 @@
         <f t="shared" ref="D31" si="15">_xlfn.XLOOKUP(B31,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
         <v>30000</v>
       </c>
-      <c r="E31" s="541"/>
+      <c r="E31" s="612"/>
     </row>
     <row r="32" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A32" s="305"/>
@@ -12329,7 +13319,7 @@
         <f t="shared" ref="D32" si="16">_xlfn.XLOOKUP(B32,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
         <v>20000</v>
       </c>
-      <c r="E32" s="541"/>
+      <c r="E32" s="612"/>
     </row>
     <row r="33" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A33" s="305"/>
@@ -12344,7 +13334,7 @@
         <f t="shared" ref="D33" si="18">_xlfn.XLOOKUP(B33,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
         <v>16000</v>
       </c>
-      <c r="E33" s="541"/>
+      <c r="E33" s="612"/>
     </row>
     <row r="34" spans="1:10" ht="36" x14ac:dyDescent="0.3">
       <c r="A34" s="305"/>
@@ -12359,7 +13349,7 @@
         <f t="shared" ref="D34" si="19">_xlfn.XLOOKUP(B34,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
         <v>Not found in data</v>
       </c>
-      <c r="E34" s="541"/>
+      <c r="E34" s="612"/>
     </row>
     <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A35" s="305"/>
@@ -12374,7 +13364,7 @@
         <f t="shared" ref="D35" si="20">_xlfn.XLOOKUP(B35,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
         <v>Not found in data</v>
       </c>
-      <c r="E35" s="541"/>
+      <c r="E35" s="612"/>
     </row>
     <row r="36" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A36" s="305"/>
@@ -12389,7 +13379,7 @@
         <f t="shared" ref="D36" si="21">_xlfn.XLOOKUP(B36,$A$21:$S$21,$A$24:$S$24,"Not found in data")</f>
         <v>20000</v>
       </c>
-      <c r="E36" s="541"/>
+      <c r="E36" s="612"/>
     </row>
     <row r="37" spans="1:10" ht="36" x14ac:dyDescent="0.3">
       <c r="A37" s="320" t="s">
@@ -12406,10 +13396,10 @@
         <f t="shared" ref="D37" si="23">_xlfn.XLOOKUP(B37,A$21:S$21,$A$24:$S$24,"Not found in data")</f>
         <v>20000</v>
       </c>
-      <c r="E37" s="541"/>
+      <c r="E37" s="612"/>
     </row>
     <row r="42" spans="1:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="A42" s="535">
+      <c r="A42" s="606">
         <v>3</v>
       </c>
       <c r="B42" s="343" t="s">
@@ -12426,7 +13416,7 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A43" s="535"/>
+      <c r="A43" s="606"/>
       <c r="B43" s="345" t="s">
         <v>139</v>
       </c>
@@ -12441,7 +13431,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A44" s="535"/>
+      <c r="A44" s="606"/>
       <c r="B44" s="345" t="s">
         <v>139</v>
       </c>
@@ -12456,7 +13446,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A45" s="535"/>
+      <c r="A45" s="606"/>
       <c r="B45" s="345" t="s">
         <v>399</v>
       </c>
@@ -12471,7 +13461,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="A46" s="535"/>
+      <c r="A46" s="606"/>
       <c r="B46" s="345" t="s">
         <v>399</v>
       </c>
@@ -12494,12 +13484,12 @@
       <c r="I46" s="350" t="s">
         <v>396</v>
       </c>
-      <c r="J46" s="542" t="s">
+      <c r="J46" s="613" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A47" s="535"/>
+      <c r="A47" s="606"/>
       <c r="B47" s="346" t="s">
         <v>415</v>
       </c>
@@ -12524,10 +13514,10 @@
         <f>_xlfn.XLOOKUP(G47,B43:B58,D43:D58,"Not present in data")</f>
         <v>East</v>
       </c>
-      <c r="J47" s="543"/>
+      <c r="J47" s="614"/>
     </row>
     <row r="48" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A48" s="535"/>
+      <c r="A48" s="606"/>
       <c r="B48" s="346" t="s">
         <v>416</v>
       </c>
@@ -12552,10 +13542,10 @@
         <f>_xlfn.XLOOKUP(G48,$B$43:$B$58,$D$43:$D$58,"Not found in data")</f>
         <v>East</v>
       </c>
-      <c r="J48" s="543"/>
+      <c r="J48" s="614"/>
     </row>
     <row r="49" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="535"/>
+      <c r="A49" s="606"/>
       <c r="B49" s="345" t="s">
         <v>405</v>
       </c>
@@ -12582,10 +13572,10 @@
         <f>_xlfn.XLOOKUP("*"&amp;G49&amp;"*",B45:B60,D45:D60,"Not present in data",2)</f>
         <v>North</v>
       </c>
-      <c r="J49" s="543"/>
+      <c r="J49" s="614"/>
     </row>
     <row r="50" spans="1:11" ht="38.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="535"/>
+      <c r="A50" s="606"/>
       <c r="B50" s="345" t="s">
         <v>405</v>
       </c>
@@ -12612,10 +13602,10 @@
         <f>_xlfn.XLOOKUP("*"&amp;G50&amp;"*",B46:B61,D46:D61,"Not present in data",2,-1)</f>
         <v>East</v>
       </c>
-      <c r="J50" s="543"/>
+      <c r="J50" s="614"/>
     </row>
     <row r="51" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="535"/>
+      <c r="A51" s="606"/>
       <c r="B51" s="345" t="s">
         <v>397</v>
       </c>
@@ -12642,10 +13632,10 @@
         <f>_xlfn.XLOOKUP("*"&amp;G51&amp;"*",B47:B62,D47:D62,"Not present in data",2)</f>
         <v>North</v>
       </c>
-      <c r="J51" s="543"/>
+      <c r="J51" s="614"/>
     </row>
     <row r="52" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="535"/>
+      <c r="A52" s="606"/>
       <c r="B52" s="345" t="s">
         <v>406</v>
       </c>
@@ -12672,10 +13662,10 @@
         <f>_xlfn.XLOOKUP("*"&amp;G52&amp;"*",B48:B63,D48:D63,"Not present in data",2,-1)</f>
         <v>West</v>
       </c>
-      <c r="J52" s="544"/>
+      <c r="J52" s="615"/>
     </row>
     <row r="53" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="A53" s="535"/>
+      <c r="A53" s="606"/>
       <c r="B53" s="345" t="s">
         <v>72</v>
       </c>
@@ -12690,7 +13680,7 @@
       </c>
     </row>
     <row r="54" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="A54" s="535"/>
+      <c r="A54" s="606"/>
       <c r="B54" s="345" t="s">
         <v>72</v>
       </c>
@@ -12705,7 +13695,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="21" x14ac:dyDescent="0.3">
-      <c r="A55" s="535"/>
+      <c r="A55" s="606"/>
       <c r="B55" s="346" t="s">
         <v>401</v>
       </c>
@@ -12731,12 +13721,12 @@
       <c r="J55" s="350" t="s">
         <v>403</v>
       </c>
-      <c r="K55" s="545" t="s">
+      <c r="K55" s="616" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="535"/>
+      <c r="A56" s="606"/>
       <c r="B56" s="346" t="s">
         <v>417</v>
       </c>
@@ -12763,10 +13753,10 @@
       <c r="J56" s="355">
         <v>4000</v>
       </c>
-      <c r="K56" s="545"/>
+      <c r="K56" s="616"/>
     </row>
     <row r="57" spans="1:11" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="535"/>
+      <c r="A57" s="606"/>
       <c r="B57" s="348" t="s">
         <v>398</v>
       </c>
@@ -12793,10 +13783,10 @@
       <c r="J57" s="355">
         <v>8000</v>
       </c>
-      <c r="K57" s="545"/>
+      <c r="K57" s="616"/>
     </row>
     <row r="58" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="535"/>
+      <c r="A58" s="606"/>
       <c r="B58" s="349" t="s">
         <v>402</v>
       </c>
@@ -12825,7 +13815,7 @@
       <c r="J58" s="355">
         <v>16000</v>
       </c>
-      <c r="K58" s="545"/>
+      <c r="K58" s="616"/>
     </row>
     <row r="59" spans="1:11" ht="38.4" x14ac:dyDescent="0.3">
       <c r="F59" s="352" t="s">
@@ -12844,7 +13834,7 @@
       <c r="J59" s="355">
         <v>18000</v>
       </c>
-      <c r="K59" s="545"/>
+      <c r="K59" s="616"/>
     </row>
     <row r="60" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
       <c r="F60" s="352" t="s">
@@ -12863,7 +13853,7 @@
       <c r="J60" s="355">
         <v>20000</v>
       </c>
-      <c r="K60" s="545"/>
+      <c r="K60" s="616"/>
     </row>
     <row r="61" spans="1:11" ht="19.2" x14ac:dyDescent="0.3">
       <c r="F61" s="352" t="s">
@@ -12882,16 +13872,16 @@
       <c r="J61" s="355">
         <v>42000</v>
       </c>
-      <c r="K61" s="545"/>
+      <c r="K61" s="616"/>
     </row>
     <row r="67" spans="1:10" ht="21" x14ac:dyDescent="0.3">
       <c r="A67" s="305"/>
       <c r="B67" s="305"/>
-      <c r="C67" s="532" t="s">
+      <c r="C67" s="603" t="s">
         <v>422</v>
       </c>
-      <c r="D67" s="533"/>
-      <c r="E67" s="534"/>
+      <c r="D67" s="604"/>
+      <c r="E67" s="605"/>
       <c r="G67" s="362" t="s">
         <v>425</v>
       </c>
@@ -12901,7 +13891,7 @@
       <c r="I67" s="363" t="s">
         <v>122</v>
       </c>
-      <c r="J67" s="536" t="s">
+      <c r="J67" s="607" t="s">
         <v>427</v>
       </c>
     </row>
@@ -12930,10 +13920,10 @@
         <f t="array" ref="I68">_xlfn.XLOOKUP(G68,$B$68:$B$82,_xlfn.XLOOKUP(H68,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>40000</v>
       </c>
-      <c r="J68" s="536"/>
+      <c r="J68" s="607"/>
     </row>
     <row r="69" spans="1:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="A69" s="535">
+      <c r="A69" s="606">
         <v>4</v>
       </c>
       <c r="B69" s="345" t="s">
@@ -12959,10 +13949,10 @@
         <f t="array" ref="I69">_xlfn.XLOOKUP(G69,$B$68:$B$82,_xlfn.XLOOKUP(H69,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>57000</v>
       </c>
-      <c r="J69" s="536"/>
+      <c r="J69" s="607"/>
     </row>
     <row r="70" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A70" s="535"/>
+      <c r="A70" s="606"/>
       <c r="B70" s="345" t="s">
         <v>139</v>
       </c>
@@ -12986,10 +13976,10 @@
         <f t="array" ref="I70">_xlfn.XLOOKUP(G70,$B$68:$B$82,_xlfn.XLOOKUP(H70,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>8000</v>
       </c>
-      <c r="J70" s="536"/>
+      <c r="J70" s="607"/>
     </row>
     <row r="71" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A71" s="535"/>
+      <c r="A71" s="606"/>
       <c r="B71" s="346" t="s">
         <v>399</v>
       </c>
@@ -13013,10 +14003,10 @@
         <f t="array" ref="I71">_xlfn.XLOOKUP(G71,$B$68:$B$82,_xlfn.XLOOKUP(H71,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>78000</v>
       </c>
-      <c r="J71" s="536"/>
+      <c r="J71" s="607"/>
     </row>
     <row r="72" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A72" s="535"/>
+      <c r="A72" s="606"/>
       <c r="B72" s="346" t="s">
         <v>399</v>
       </c>
@@ -13040,10 +14030,10 @@
         <f t="array" ref="I72">_xlfn.XLOOKUP(G72,$B$68:$B$82,_xlfn.XLOOKUP(H72,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>35000</v>
       </c>
-      <c r="J72" s="536"/>
+      <c r="J72" s="607"/>
     </row>
     <row r="73" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A73" s="535"/>
+      <c r="A73" s="606"/>
       <c r="B73" s="345" t="s">
         <v>423</v>
       </c>
@@ -13067,10 +14057,10 @@
         <f t="array" ref="I73">_xlfn.XLOOKUP(G73,$B$68:$B$82,_xlfn.XLOOKUP(H73,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>42000</v>
       </c>
-      <c r="J73" s="536"/>
+      <c r="J73" s="607"/>
     </row>
     <row r="74" spans="1:10" ht="36" x14ac:dyDescent="0.3">
-      <c r="A74" s="535"/>
+      <c r="A74" s="606"/>
       <c r="B74" s="345" t="s">
         <v>424</v>
       </c>
@@ -13094,10 +14084,10 @@
         <f t="array" ref="I74">_xlfn.XLOOKUP(G74,$B$68:$B$82,_xlfn.XLOOKUP(H74,$C$68:$E$68,$C$68:$E$82,"Not present",,-1))</f>
         <v>80000</v>
       </c>
-      <c r="J74" s="536"/>
+      <c r="J74" s="607"/>
     </row>
     <row r="75" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A75" s="535"/>
+      <c r="A75" s="606"/>
       <c r="B75" s="346" t="s">
         <v>405</v>
       </c>
@@ -13115,7 +14105,7 @@
       <c r="H75" s="360"/>
     </row>
     <row r="76" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A76" s="535"/>
+      <c r="A76" s="606"/>
       <c r="B76" s="346" t="s">
         <v>405</v>
       </c>
@@ -13133,7 +14123,7 @@
       <c r="H76" s="360"/>
     </row>
     <row r="77" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A77" s="535"/>
+      <c r="A77" s="606"/>
       <c r="B77" s="345" t="s">
         <v>397</v>
       </c>
@@ -13151,7 +14141,7 @@
       <c r="H77" s="360"/>
     </row>
     <row r="78" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A78" s="535"/>
+      <c r="A78" s="606"/>
       <c r="B78" s="346" t="s">
         <v>406</v>
       </c>
@@ -13169,7 +14159,7 @@
       <c r="H78" s="360"/>
     </row>
     <row r="79" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A79" s="535"/>
+      <c r="A79" s="606"/>
       <c r="B79" s="346" t="s">
         <v>72</v>
       </c>
@@ -13187,7 +14177,7 @@
       <c r="H79" s="360"/>
     </row>
     <row r="80" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A80" s="535"/>
+      <c r="A80" s="606"/>
       <c r="B80" s="346" t="s">
         <v>72</v>
       </c>
@@ -13205,7 +14195,7 @@
       <c r="H80" s="360"/>
     </row>
     <row r="81" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A81" s="535"/>
+      <c r="A81" s="606"/>
       <c r="B81" s="345" t="s">
         <v>401</v>
       </c>
@@ -13223,7 +14213,7 @@
       <c r="H81" s="360"/>
     </row>
     <row r="82" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A82" s="535"/>
+      <c r="A82" s="606"/>
       <c r="B82" s="345" t="s">
         <v>398</v>
       </c>
@@ -13665,7 +14655,7 @@
         <f>INDEX(C3:C16,MATCH(H2,D3:D15,0))</f>
         <v>East</v>
       </c>
-      <c r="H15" s="546" t="s">
+      <c r="H15" s="617" t="s">
         <v>443</v>
       </c>
       <c r="I15" s="407"/>
@@ -13691,7 +14681,7 @@
         <f>INDEX(C3:C16,MATCH(D6,D3:D16,0))</f>
         <v>East</v>
       </c>
-      <c r="H16" s="547"/>
+      <c r="H16" s="618"/>
       <c r="I16" s="407"/>
       <c r="J16" s="407"/>
       <c r="K16" s="407"/>
@@ -13703,7 +14693,7 @@
         <f>INDEX($C$3:$C$16, MATCH(J2, $D$3:$D$16, 0))</f>
         <v>South</v>
       </c>
-      <c r="H17" s="547"/>
+      <c r="H17" s="618"/>
       <c r="I17" s="422"/>
       <c r="J17" s="422"/>
       <c r="K17" s="422"/>
@@ -13715,7 +14705,7 @@
         <f>INDEX($C$3:$C$16, MATCH(K2, $D$3:$D$16, 0))</f>
         <v>North</v>
       </c>
-      <c r="H18" s="548"/>
+      <c r="H18" s="619"/>
       <c r="I18" s="422"/>
       <c r="J18" s="422"/>
       <c r="K18" s="422"/>
@@ -13768,7 +14758,7 @@
         <v>134</v>
       </c>
       <c r="I1" s="402"/>
-      <c r="J1" s="549" t="s">
+      <c r="J1" s="620" t="s">
         <v>444</v>
       </c>
       <c r="K1" s="403"/>
@@ -13794,7 +14784,7 @@
       <c r="G2" s="443"/>
       <c r="H2" s="423"/>
       <c r="I2" s="402"/>
-      <c r="J2" s="549"/>
+      <c r="J2" s="620"/>
       <c r="K2" s="403"/>
       <c r="L2" s="403"/>
       <c r="M2" s="403"/>
@@ -13822,7 +14812,7 @@
       <c r="I3" s="402" t="s">
         <v>128</v>
       </c>
-      <c r="J3" s="549"/>
+      <c r="J3" s="620"/>
       <c r="K3" s="403"/>
       <c r="L3" s="403"/>
       <c r="M3" s="403"/>
@@ -13846,7 +14836,7 @@
       <c r="G4" s="436"/>
       <c r="H4" s="423"/>
       <c r="I4" s="402"/>
-      <c r="J4" s="549"/>
+      <c r="J4" s="620"/>
       <c r="K4" s="403"/>
       <c r="L4" s="403"/>
       <c r="M4" s="403"/>
@@ -13870,7 +14860,7 @@
         <v>446</v>
       </c>
       <c r="I5" s="402"/>
-      <c r="J5" s="549"/>
+      <c r="J5" s="620"/>
       <c r="K5" s="403"/>
       <c r="L5" s="403"/>
       <c r="M5" s="403"/>
@@ -13935,7 +14925,7 @@
       <c r="G9" s="402"/>
       <c r="H9" s="402"/>
       <c r="I9" s="402"/>
-      <c r="J9" s="550" t="s">
+      <c r="J9" s="621" t="s">
         <v>447</v>
       </c>
       <c r="K9" s="404"/>
@@ -13959,7 +14949,7 @@
       <c r="G10" s="402"/>
       <c r="H10" s="402"/>
       <c r="I10" s="402"/>
-      <c r="J10" s="550"/>
+      <c r="J10" s="621"/>
       <c r="K10" s="404"/>
       <c r="L10" s="405"/>
       <c r="M10" s="401"/>
@@ -13981,7 +14971,7 @@
       <c r="G11" s="402"/>
       <c r="H11" s="402"/>
       <c r="I11" s="402"/>
-      <c r="J11" s="550"/>
+      <c r="J11" s="621"/>
       <c r="K11" s="404"/>
       <c r="L11" s="405"/>
       <c r="M11" s="401"/>
@@ -14003,7 +14993,7 @@
       <c r="G12" s="402"/>
       <c r="H12" s="402"/>
       <c r="I12" s="402"/>
-      <c r="J12" s="550"/>
+      <c r="J12" s="621"/>
       <c r="K12" s="401"/>
       <c r="L12" s="401"/>
       <c r="M12" s="401"/>
@@ -14025,7 +15015,7 @@
       <c r="G13" s="402"/>
       <c r="H13" s="402"/>
       <c r="I13" s="402"/>
-      <c r="J13" s="550"/>
+      <c r="J13" s="621"/>
       <c r="K13" s="401"/>
       <c r="L13" s="401"/>
       <c r="M13" s="401"/>
@@ -15404,16 +16394,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="455" t="s">
+      <c r="A1" s="526" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="454"/>
-      <c r="C1" s="454"/>
+      <c r="B1" s="525"/>
+      <c r="C1" s="525"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="454"/>
-      <c r="B2" s="454"/>
-      <c r="C2" s="454"/>
+      <c r="A2" s="525"/>
+      <c r="B2" s="525"/>
+      <c r="C2" s="525"/>
     </row>
     <row r="3" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="D3" s="29"/>
@@ -15437,11 +16427,11 @@
       <c r="R4" s="5"/>
     </row>
     <row r="5" spans="1:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="C5" s="456" t="s">
+      <c r="C5" s="527" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="456"/>
-      <c r="E5" s="456"/>
+      <c r="D5" s="527"/>
+      <c r="E5" s="527"/>
       <c r="I5" s="30"/>
       <c r="J5" s="30"/>
       <c r="K5" s="30"/>
@@ -15460,13 +16450,13 @@
       <c r="E6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="459" t="s">
+      <c r="H6" s="530" t="s">
         <v>75</v>
       </c>
-      <c r="I6" s="460"/>
-      <c r="J6" s="460"/>
-      <c r="K6" s="460"/>
-      <c r="L6" s="460"/>
+      <c r="I6" s="531"/>
+      <c r="J6" s="531"/>
+      <c r="K6" s="531"/>
+      <c r="L6" s="531"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
@@ -15685,12 +16675,12 @@
       </c>
     </row>
     <row r="17" spans="3:12" ht="15" x14ac:dyDescent="0.35">
-      <c r="C17" s="457" t="s">
+      <c r="C17" s="528" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="458"/>
-      <c r="E17" s="458"/>
-      <c r="F17" s="458"/>
+      <c r="D17" s="529"/>
+      <c r="E17" s="529"/>
+      <c r="F17" s="529"/>
       <c r="H17" s="22">
         <v>109</v>
       </c>
@@ -15875,6 +16865,3851 @@
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="H6:L6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D54A3BC-158A-4976-8A3D-1A5B16E3E1AC}">
+  <dimension ref="A1:O74"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.21875" customWidth="1"/>
+    <col min="2" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" customWidth="1"/>
+    <col min="11" max="13" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="458" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="459" t="s">
+        <v>264</v>
+      </c>
+      <c r="C1" s="459" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="459" t="s">
+        <v>448</v>
+      </c>
+      <c r="E1" s="460" t="s">
+        <v>449</v>
+      </c>
+      <c r="G1" s="455" t="s">
+        <v>448</v>
+      </c>
+      <c r="H1" s="454"/>
+      <c r="I1" s="455" t="s">
+        <v>448</v>
+      </c>
+      <c r="J1" s="454"/>
+      <c r="K1" s="455" t="s">
+        <v>448</v>
+      </c>
+      <c r="L1" s="454"/>
+      <c r="M1" s="455" t="s">
+        <v>448</v>
+      </c>
+      <c r="N1" s="454"/>
+      <c r="O1" s="455" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="461">
+        <v>44930</v>
+      </c>
+      <c r="B2" s="462" t="s">
+        <v>450</v>
+      </c>
+      <c r="C2" s="462" t="s">
+        <v>451</v>
+      </c>
+      <c r="D2" s="463">
+        <v>6600</v>
+      </c>
+      <c r="E2" s="464">
+        <v>7000</v>
+      </c>
+      <c r="G2" s="456">
+        <v>1000</v>
+      </c>
+      <c r="H2" s="454"/>
+      <c r="I2" s="456">
+        <v>1000</v>
+      </c>
+      <c r="J2" s="454"/>
+      <c r="K2" s="456">
+        <v>10000</v>
+      </c>
+      <c r="L2" s="454"/>
+      <c r="M2" s="456">
+        <v>1000</v>
+      </c>
+      <c r="N2" s="454"/>
+      <c r="O2" s="456">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A3" s="461">
+        <v>44930</v>
+      </c>
+      <c r="B3" s="462" t="s">
+        <v>452</v>
+      </c>
+      <c r="C3" s="462" t="s">
+        <v>453</v>
+      </c>
+      <c r="D3" s="463">
+        <v>7000</v>
+      </c>
+      <c r="E3" s="464">
+        <v>7200</v>
+      </c>
+      <c r="G3" s="456">
+        <v>1000</v>
+      </c>
+      <c r="H3" s="454"/>
+      <c r="I3" s="456">
+        <v>1000</v>
+      </c>
+      <c r="J3" s="454"/>
+      <c r="K3" s="456">
+        <v>1000</v>
+      </c>
+      <c r="L3" s="454"/>
+      <c r="M3" s="456">
+        <v>1000</v>
+      </c>
+      <c r="N3" s="454"/>
+      <c r="O3" s="456">
+        <v>8800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A4" s="461">
+        <v>45294</v>
+      </c>
+      <c r="B4" s="462" t="s">
+        <v>454</v>
+      </c>
+      <c r="C4" s="462" t="s">
+        <v>455</v>
+      </c>
+      <c r="D4" s="463">
+        <v>7300</v>
+      </c>
+      <c r="E4" s="464">
+        <v>7300</v>
+      </c>
+      <c r="G4" s="456">
+        <v>1000</v>
+      </c>
+      <c r="H4" s="454"/>
+      <c r="I4" s="456">
+        <v>1000</v>
+      </c>
+      <c r="J4" s="454"/>
+      <c r="K4" s="456">
+        <v>1000</v>
+      </c>
+      <c r="L4" s="454"/>
+      <c r="M4" s="456">
+        <v>1000</v>
+      </c>
+      <c r="N4" s="454"/>
+      <c r="O4" s="456">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="461">
+        <v>45297</v>
+      </c>
+      <c r="B5" s="462" t="s">
+        <v>456</v>
+      </c>
+      <c r="C5" s="462" t="s">
+        <v>457</v>
+      </c>
+      <c r="D5" s="463">
+        <v>7400</v>
+      </c>
+      <c r="E5" s="464">
+        <v>7400</v>
+      </c>
+      <c r="G5" s="456">
+        <v>1000</v>
+      </c>
+      <c r="H5" s="454"/>
+      <c r="I5" s="456">
+        <v>1000</v>
+      </c>
+      <c r="J5" s="454"/>
+      <c r="K5" s="456">
+        <v>1000</v>
+      </c>
+      <c r="L5" s="454"/>
+      <c r="M5" s="456">
+        <v>1000</v>
+      </c>
+      <c r="N5" s="454"/>
+      <c r="O5" s="456">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A6" s="461">
+        <v>45297</v>
+      </c>
+      <c r="B6" s="462" t="s">
+        <v>458</v>
+      </c>
+      <c r="C6" s="462" t="s">
+        <v>459</v>
+      </c>
+      <c r="D6" s="463">
+        <v>7800</v>
+      </c>
+      <c r="E6" s="464">
+        <v>7800</v>
+      </c>
+      <c r="G6" s="456">
+        <v>1500</v>
+      </c>
+      <c r="H6" s="454"/>
+      <c r="I6" s="456">
+        <v>1500</v>
+      </c>
+      <c r="J6" s="454"/>
+      <c r="K6" s="456">
+        <v>1500</v>
+      </c>
+      <c r="L6" s="454"/>
+      <c r="M6" s="456">
+        <v>1500</v>
+      </c>
+      <c r="N6" s="454"/>
+      <c r="O6" s="456">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A7" s="461">
+        <v>45304</v>
+      </c>
+      <c r="B7" s="462" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="462" t="s">
+        <v>460</v>
+      </c>
+      <c r="D7" s="463">
+        <v>8000</v>
+      </c>
+      <c r="E7" s="464">
+        <v>8000</v>
+      </c>
+      <c r="G7" s="456">
+        <v>2000</v>
+      </c>
+      <c r="H7" s="454"/>
+      <c r="I7" s="456">
+        <v>2000</v>
+      </c>
+      <c r="J7" s="454"/>
+      <c r="K7" s="456">
+        <v>2000</v>
+      </c>
+      <c r="L7" s="454"/>
+      <c r="M7" s="456">
+        <v>2000</v>
+      </c>
+      <c r="N7" s="454"/>
+      <c r="O7" s="456">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A8" s="461">
+        <v>45665</v>
+      </c>
+      <c r="B8" s="462" t="s">
+        <v>461</v>
+      </c>
+      <c r="C8" s="462" t="s">
+        <v>462</v>
+      </c>
+      <c r="D8" s="463">
+        <v>8800</v>
+      </c>
+      <c r="E8" s="464">
+        <v>8800</v>
+      </c>
+      <c r="G8" s="456">
+        <v>2200</v>
+      </c>
+      <c r="H8" s="454"/>
+      <c r="I8" s="456">
+        <v>2200</v>
+      </c>
+      <c r="J8" s="454"/>
+      <c r="K8" s="456">
+        <v>2200</v>
+      </c>
+      <c r="L8" s="454"/>
+      <c r="M8" s="456">
+        <v>2300</v>
+      </c>
+      <c r="N8" s="454"/>
+      <c r="O8" s="456">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A9" s="461">
+        <v>45972</v>
+      </c>
+      <c r="B9" s="462" t="s">
+        <v>450</v>
+      </c>
+      <c r="C9" s="462" t="s">
+        <v>451</v>
+      </c>
+      <c r="D9" s="463">
+        <v>8900</v>
+      </c>
+      <c r="E9" s="464">
+        <v>8900</v>
+      </c>
+      <c r="G9" s="456">
+        <v>2300</v>
+      </c>
+      <c r="H9" s="454"/>
+      <c r="I9" s="456">
+        <v>2300</v>
+      </c>
+      <c r="J9" s="454"/>
+      <c r="K9" s="456">
+        <v>2300</v>
+      </c>
+      <c r="L9" s="454"/>
+      <c r="M9" s="456">
+        <v>2800</v>
+      </c>
+      <c r="N9" s="454"/>
+      <c r="O9" s="456">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A10" s="461">
+        <v>46023</v>
+      </c>
+      <c r="B10" s="462" t="s">
+        <v>454</v>
+      </c>
+      <c r="C10" s="462" t="s">
+        <v>455</v>
+      </c>
+      <c r="D10" s="463">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="464">
+        <v>1000</v>
+      </c>
+      <c r="G10" s="456">
+        <v>2800</v>
+      </c>
+      <c r="H10" s="454"/>
+      <c r="I10" s="456">
+        <v>2800</v>
+      </c>
+      <c r="J10" s="454"/>
+      <c r="K10" s="456">
+        <v>2800</v>
+      </c>
+      <c r="L10" s="454"/>
+      <c r="M10" s="456">
+        <v>3300</v>
+      </c>
+      <c r="N10" s="454"/>
+      <c r="O10" s="456">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A11" s="461">
+        <v>46023</v>
+      </c>
+      <c r="B11" s="462" t="s">
+        <v>456</v>
+      </c>
+      <c r="C11" s="462" t="s">
+        <v>457</v>
+      </c>
+      <c r="D11" s="463">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="464">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="456">
+        <v>3000</v>
+      </c>
+      <c r="H11" s="454"/>
+      <c r="I11" s="456">
+        <v>3000</v>
+      </c>
+      <c r="J11" s="454"/>
+      <c r="K11" s="456">
+        <v>3000</v>
+      </c>
+      <c r="L11" s="454"/>
+      <c r="M11" s="456">
+        <v>3330</v>
+      </c>
+      <c r="N11" s="454"/>
+      <c r="O11" s="456">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A12" s="461">
+        <v>46025</v>
+      </c>
+      <c r="B12" s="462" t="s">
+        <v>458</v>
+      </c>
+      <c r="C12" s="462" t="s">
+        <v>459</v>
+      </c>
+      <c r="D12" s="463">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="464">
+        <v>1000</v>
+      </c>
+      <c r="G12" s="456">
+        <v>3330</v>
+      </c>
+      <c r="H12" s="454"/>
+      <c r="I12" s="456">
+        <v>3300</v>
+      </c>
+      <c r="J12" s="454"/>
+      <c r="K12" s="456">
+        <v>3300</v>
+      </c>
+      <c r="L12" s="454"/>
+      <c r="M12" s="456">
+        <v>3700</v>
+      </c>
+      <c r="N12" s="454"/>
+      <c r="O12" s="456">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A13" s="461">
+        <v>46028</v>
+      </c>
+      <c r="B13" s="462" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="462" t="s">
+        <v>460</v>
+      </c>
+      <c r="D13" s="463">
+        <v>1000</v>
+      </c>
+      <c r="E13" s="464">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="456">
+        <v>3700</v>
+      </c>
+      <c r="H13" s="454"/>
+      <c r="I13" s="456">
+        <v>3330</v>
+      </c>
+      <c r="J13" s="454"/>
+      <c r="K13" s="456">
+        <v>7000</v>
+      </c>
+      <c r="L13" s="454"/>
+      <c r="M13" s="456">
+        <v>4000</v>
+      </c>
+      <c r="N13" s="454"/>
+      <c r="O13" s="456">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A14" s="461">
+        <v>46028</v>
+      </c>
+      <c r="B14" s="462" t="s">
+        <v>461</v>
+      </c>
+      <c r="C14" s="462" t="s">
+        <v>462</v>
+      </c>
+      <c r="D14" s="463">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="464">
+        <v>1500</v>
+      </c>
+      <c r="G14" s="456">
+        <v>4000</v>
+      </c>
+      <c r="H14" s="454"/>
+      <c r="I14" s="456">
+        <v>3700</v>
+      </c>
+      <c r="J14" s="454"/>
+      <c r="K14" s="456">
+        <v>3700</v>
+      </c>
+      <c r="L14" s="454"/>
+      <c r="M14" s="456">
+        <v>4000</v>
+      </c>
+      <c r="N14" s="454"/>
+      <c r="O14" s="456">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A15" s="461">
+        <v>46029</v>
+      </c>
+      <c r="B15" s="462" t="s">
+        <v>450</v>
+      </c>
+      <c r="C15" s="462" t="s">
+        <v>451</v>
+      </c>
+      <c r="D15" s="463">
+        <v>1500</v>
+      </c>
+      <c r="E15" s="464">
+        <v>2000</v>
+      </c>
+      <c r="G15" s="456">
+        <v>4000</v>
+      </c>
+      <c r="H15" s="454"/>
+      <c r="I15" s="456">
+        <v>4000</v>
+      </c>
+      <c r="J15" s="454"/>
+      <c r="K15" s="456">
+        <v>4000</v>
+      </c>
+      <c r="L15" s="454"/>
+      <c r="M15" s="456">
+        <v>4000</v>
+      </c>
+      <c r="N15" s="454"/>
+      <c r="O15" s="456">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A16" s="461">
+        <v>46029</v>
+      </c>
+      <c r="B16" s="462" t="s">
+        <v>452</v>
+      </c>
+      <c r="C16" s="462" t="s">
+        <v>453</v>
+      </c>
+      <c r="D16" s="463">
+        <v>2000</v>
+      </c>
+      <c r="E16" s="464">
+        <v>2200</v>
+      </c>
+      <c r="G16" s="456">
+        <v>4200</v>
+      </c>
+      <c r="H16" s="454"/>
+      <c r="I16" s="456">
+        <v>4000</v>
+      </c>
+      <c r="J16" s="454"/>
+      <c r="K16" s="456">
+        <v>4000</v>
+      </c>
+      <c r="L16" s="454"/>
+      <c r="M16" s="456">
+        <v>4200</v>
+      </c>
+      <c r="N16" s="454"/>
+      <c r="O16" s="456">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A17" s="461">
+        <v>46030</v>
+      </c>
+      <c r="B17" s="462" t="s">
+        <v>452</v>
+      </c>
+      <c r="C17" s="462" t="s">
+        <v>453</v>
+      </c>
+      <c r="D17" s="463">
+        <v>2200</v>
+      </c>
+      <c r="E17" s="464">
+        <v>2300</v>
+      </c>
+      <c r="G17" s="456">
+        <v>4500</v>
+      </c>
+      <c r="H17" s="454"/>
+      <c r="I17" s="456">
+        <v>4000</v>
+      </c>
+      <c r="J17" s="454"/>
+      <c r="K17" s="456">
+        <v>4000</v>
+      </c>
+      <c r="L17" s="454"/>
+      <c r="M17" s="456">
+        <v>4500</v>
+      </c>
+      <c r="N17" s="454"/>
+      <c r="O17" s="456">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A18" s="461">
+        <v>46032</v>
+      </c>
+      <c r="B18" s="462" t="s">
+        <v>456</v>
+      </c>
+      <c r="C18" s="462" t="s">
+        <v>457</v>
+      </c>
+      <c r="D18" s="463">
+        <v>2800</v>
+      </c>
+      <c r="E18" s="464">
+        <v>3000</v>
+      </c>
+      <c r="G18" s="456">
+        <v>5000</v>
+      </c>
+      <c r="H18" s="454"/>
+      <c r="I18" s="456">
+        <v>4200</v>
+      </c>
+      <c r="J18" s="454"/>
+      <c r="K18" s="456">
+        <v>4200</v>
+      </c>
+      <c r="L18" s="454"/>
+      <c r="M18" s="456">
+        <v>4700</v>
+      </c>
+      <c r="N18" s="454"/>
+      <c r="O18" s="456">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A19" s="461">
+        <v>46032</v>
+      </c>
+      <c r="B19" s="462" t="s">
+        <v>454</v>
+      </c>
+      <c r="C19" s="462" t="s">
+        <v>455</v>
+      </c>
+      <c r="D19" s="463">
+        <v>6300</v>
+      </c>
+      <c r="E19" s="464">
+        <v>2800</v>
+      </c>
+      <c r="G19" s="456">
+        <v>5100</v>
+      </c>
+      <c r="H19" s="454"/>
+      <c r="I19" s="456">
+        <v>4500</v>
+      </c>
+      <c r="J19" s="454"/>
+      <c r="K19" s="456">
+        <v>4500</v>
+      </c>
+      <c r="L19" s="454"/>
+      <c r="M19" s="456">
+        <v>5000</v>
+      </c>
+      <c r="N19" s="454"/>
+      <c r="O19" s="456">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A20" s="461">
+        <v>46033</v>
+      </c>
+      <c r="B20" s="462" t="s">
+        <v>458</v>
+      </c>
+      <c r="C20" s="462" t="s">
+        <v>459</v>
+      </c>
+      <c r="D20" s="463">
+        <v>3000</v>
+      </c>
+      <c r="E20" s="464">
+        <v>3300</v>
+      </c>
+      <c r="G20" s="456">
+        <v>5200</v>
+      </c>
+      <c r="H20" s="454"/>
+      <c r="I20" s="456">
+        <v>5000</v>
+      </c>
+      <c r="J20" s="454"/>
+      <c r="K20" s="456">
+        <v>4700</v>
+      </c>
+      <c r="L20" s="454"/>
+      <c r="M20" s="456">
+        <v>5200</v>
+      </c>
+      <c r="N20" s="454"/>
+      <c r="O20" s="456">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A21" s="461">
+        <v>46033</v>
+      </c>
+      <c r="B21" s="462" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="462" t="s">
+        <v>460</v>
+      </c>
+      <c r="D21" s="463">
+        <v>3300</v>
+      </c>
+      <c r="E21" s="464">
+        <v>3330</v>
+      </c>
+      <c r="G21" s="456">
+        <v>5300</v>
+      </c>
+      <c r="H21" s="454"/>
+      <c r="I21" s="456">
+        <v>5200</v>
+      </c>
+      <c r="J21" s="454"/>
+      <c r="K21" s="456">
+        <v>5000</v>
+      </c>
+      <c r="L21" s="454"/>
+      <c r="M21" s="456">
+        <v>5300</v>
+      </c>
+      <c r="N21" s="454"/>
+      <c r="O21" s="456">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A22" s="461">
+        <v>46035</v>
+      </c>
+      <c r="B22" s="462" t="s">
+        <v>461</v>
+      </c>
+      <c r="C22" s="462" t="s">
+        <v>462</v>
+      </c>
+      <c r="D22" s="463">
+        <v>3330</v>
+      </c>
+      <c r="E22" s="464">
+        <v>3700</v>
+      </c>
+      <c r="G22" s="456">
+        <v>5500</v>
+      </c>
+      <c r="H22" s="454"/>
+      <c r="I22" s="456">
+        <v>5300</v>
+      </c>
+      <c r="J22" s="454"/>
+      <c r="K22" s="456">
+        <v>5200</v>
+      </c>
+      <c r="L22" s="454"/>
+      <c r="M22" s="456">
+        <v>5500</v>
+      </c>
+      <c r="N22" s="454"/>
+      <c r="O22" s="456">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A23" s="461">
+        <v>46037</v>
+      </c>
+      <c r="B23" s="462" t="s">
+        <v>452</v>
+      </c>
+      <c r="C23" s="462" t="s">
+        <v>453</v>
+      </c>
+      <c r="D23" s="463">
+        <v>3700</v>
+      </c>
+      <c r="E23" s="464">
+        <v>4000</v>
+      </c>
+      <c r="G23" s="456">
+        <v>5700</v>
+      </c>
+      <c r="H23" s="454"/>
+      <c r="I23" s="456">
+        <v>2200</v>
+      </c>
+      <c r="J23" s="454"/>
+      <c r="K23" s="456">
+        <v>5300</v>
+      </c>
+      <c r="L23" s="454"/>
+      <c r="M23" s="456">
+        <v>5700</v>
+      </c>
+      <c r="N23" s="454"/>
+      <c r="O23" s="456">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A24" s="461">
+        <v>46037</v>
+      </c>
+      <c r="B24" s="462" t="s">
+        <v>450</v>
+      </c>
+      <c r="C24" s="462" t="s">
+        <v>451</v>
+      </c>
+      <c r="D24" s="463">
+        <v>7500</v>
+      </c>
+      <c r="E24" s="464">
+        <v>4000</v>
+      </c>
+      <c r="G24" s="456">
+        <v>5900</v>
+      </c>
+      <c r="H24" s="454"/>
+      <c r="I24" s="456">
+        <v>5700</v>
+      </c>
+      <c r="J24" s="454"/>
+      <c r="K24" s="456">
+        <v>5500</v>
+      </c>
+      <c r="L24" s="454"/>
+      <c r="M24" s="456">
+        <v>5900</v>
+      </c>
+      <c r="N24" s="454"/>
+      <c r="O24" s="456">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A25" s="461">
+        <v>46042</v>
+      </c>
+      <c r="B25" s="462" t="s">
+        <v>456</v>
+      </c>
+      <c r="C25" s="462" t="s">
+        <v>457</v>
+      </c>
+      <c r="D25" s="463">
+        <v>4000</v>
+      </c>
+      <c r="E25" s="464">
+        <v>4200</v>
+      </c>
+      <c r="G25" s="456">
+        <v>6000</v>
+      </c>
+      <c r="H25" s="454"/>
+      <c r="I25" s="456">
+        <v>6000</v>
+      </c>
+      <c r="J25" s="454"/>
+      <c r="K25" s="456">
+        <v>5700</v>
+      </c>
+      <c r="L25" s="454"/>
+      <c r="M25" s="456">
+        <v>6000</v>
+      </c>
+      <c r="N25" s="454"/>
+      <c r="O25" s="456">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A26" s="461">
+        <v>46042</v>
+      </c>
+      <c r="B26" s="462" t="s">
+        <v>454</v>
+      </c>
+      <c r="C26" s="462" t="s">
+        <v>455</v>
+      </c>
+      <c r="D26" s="463">
+        <v>9000</v>
+      </c>
+      <c r="E26" s="464">
+        <v>4000</v>
+      </c>
+      <c r="G26" s="456">
+        <v>6000</v>
+      </c>
+      <c r="H26" s="454"/>
+      <c r="I26" s="456">
+        <v>6600</v>
+      </c>
+      <c r="J26" s="454"/>
+      <c r="K26" s="456">
+        <v>5900</v>
+      </c>
+      <c r="L26" s="454"/>
+      <c r="M26" s="456">
+        <v>6600</v>
+      </c>
+      <c r="N26" s="454"/>
+      <c r="O26" s="456">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A27" s="461">
+        <v>46152</v>
+      </c>
+      <c r="B27" s="462" t="s">
+        <v>458</v>
+      </c>
+      <c r="C27" s="462" t="s">
+        <v>459</v>
+      </c>
+      <c r="D27" s="463">
+        <v>4000</v>
+      </c>
+      <c r="E27" s="464">
+        <v>4500</v>
+      </c>
+      <c r="G27" s="456">
+        <v>6600</v>
+      </c>
+      <c r="H27" s="454"/>
+      <c r="I27" s="456">
+        <v>7000</v>
+      </c>
+      <c r="J27" s="454"/>
+      <c r="K27" s="456">
+        <v>6000</v>
+      </c>
+      <c r="L27" s="454"/>
+      <c r="M27" s="456">
+        <v>7000</v>
+      </c>
+      <c r="N27" s="454"/>
+      <c r="O27" s="456">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A28" s="461">
+        <v>46152</v>
+      </c>
+      <c r="B28" s="462" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="462" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" s="463">
+        <v>4200</v>
+      </c>
+      <c r="E28" s="464">
+        <v>4700</v>
+      </c>
+      <c r="G28" s="456">
+        <v>7000</v>
+      </c>
+      <c r="H28" s="454"/>
+      <c r="I28" s="456">
+        <v>7200</v>
+      </c>
+      <c r="J28" s="454"/>
+      <c r="K28" s="456">
+        <v>6600</v>
+      </c>
+      <c r="L28" s="454"/>
+      <c r="M28" s="456">
+        <v>7200</v>
+      </c>
+      <c r="N28" s="454"/>
+      <c r="O28" s="456">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A29" s="461">
+        <v>46159</v>
+      </c>
+      <c r="B29" s="462" t="s">
+        <v>461</v>
+      </c>
+      <c r="C29" s="462" t="s">
+        <v>462</v>
+      </c>
+      <c r="D29" s="463">
+        <v>4500</v>
+      </c>
+      <c r="E29" s="464">
+        <v>5000</v>
+      </c>
+      <c r="G29" s="456">
+        <v>7200</v>
+      </c>
+      <c r="H29" s="454"/>
+      <c r="I29" s="456">
+        <v>7300</v>
+      </c>
+      <c r="J29" s="454"/>
+      <c r="K29" s="456">
+        <v>7000</v>
+      </c>
+      <c r="L29" s="454"/>
+      <c r="M29" s="456">
+        <v>7300</v>
+      </c>
+      <c r="N29" s="454"/>
+      <c r="O29" s="456">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A30" s="461">
+        <v>46159</v>
+      </c>
+      <c r="B30" s="462" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="462" t="s">
+        <v>451</v>
+      </c>
+      <c r="D30" s="463">
+        <v>4700</v>
+      </c>
+      <c r="E30" s="464">
+        <v>5200</v>
+      </c>
+      <c r="G30" s="456">
+        <v>7300</v>
+      </c>
+      <c r="H30" s="454"/>
+      <c r="I30" s="456">
+        <v>7400</v>
+      </c>
+      <c r="J30" s="454"/>
+      <c r="K30" s="456">
+        <v>7200</v>
+      </c>
+      <c r="L30" s="454"/>
+      <c r="M30" s="456">
+        <v>7400</v>
+      </c>
+      <c r="N30" s="454"/>
+      <c r="O30" s="456">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A31" s="461">
+        <v>46222</v>
+      </c>
+      <c r="B31" s="462" t="s">
+        <v>452</v>
+      </c>
+      <c r="C31" s="462" t="s">
+        <v>453</v>
+      </c>
+      <c r="D31" s="463">
+        <v>5000</v>
+      </c>
+      <c r="E31" s="464">
+        <v>5300</v>
+      </c>
+      <c r="G31" s="456">
+        <v>7400</v>
+      </c>
+      <c r="H31" s="454"/>
+      <c r="I31" s="456">
+        <v>7700</v>
+      </c>
+      <c r="J31" s="454"/>
+      <c r="K31" s="456">
+        <v>7300</v>
+      </c>
+      <c r="L31" s="454"/>
+      <c r="M31" s="456">
+        <v>7800</v>
+      </c>
+      <c r="N31" s="454"/>
+      <c r="O31" s="456">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A32" s="461">
+        <v>46222</v>
+      </c>
+      <c r="B32" s="462" t="s">
+        <v>454</v>
+      </c>
+      <c r="C32" s="462" t="s">
+        <v>455</v>
+      </c>
+      <c r="D32" s="463">
+        <v>5200</v>
+      </c>
+      <c r="E32" s="464">
+        <v>5500</v>
+      </c>
+      <c r="G32" s="456">
+        <v>7800</v>
+      </c>
+      <c r="H32" s="454"/>
+      <c r="I32" s="456">
+        <v>7800</v>
+      </c>
+      <c r="J32" s="454"/>
+      <c r="K32" s="456">
+        <v>3000</v>
+      </c>
+      <c r="L32" s="454"/>
+      <c r="M32" s="456">
+        <v>8000</v>
+      </c>
+      <c r="N32" s="454"/>
+      <c r="O32" s="456">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A33" s="461">
+        <v>46247</v>
+      </c>
+      <c r="B33" s="462" t="s">
+        <v>456</v>
+      </c>
+      <c r="C33" s="462" t="s">
+        <v>457</v>
+      </c>
+      <c r="D33" s="463">
+        <v>5300</v>
+      </c>
+      <c r="E33" s="464">
+        <v>5700</v>
+      </c>
+      <c r="G33" s="456">
+        <v>8000</v>
+      </c>
+      <c r="H33" s="454"/>
+      <c r="I33" s="456">
+        <v>8000</v>
+      </c>
+      <c r="J33" s="454"/>
+      <c r="K33" s="456">
+        <v>7800</v>
+      </c>
+      <c r="L33" s="454"/>
+      <c r="M33" s="456">
+        <v>8000</v>
+      </c>
+      <c r="N33" s="454"/>
+      <c r="O33" s="456">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A34" s="461">
+        <v>46247</v>
+      </c>
+      <c r="B34" s="462" t="s">
+        <v>458</v>
+      </c>
+      <c r="C34" s="462" t="s">
+        <v>459</v>
+      </c>
+      <c r="D34" s="463">
+        <v>5700</v>
+      </c>
+      <c r="E34" s="464">
+        <v>5900</v>
+      </c>
+      <c r="G34" s="456">
+        <v>8300</v>
+      </c>
+      <c r="H34" s="454"/>
+      <c r="I34" s="456">
+        <v>4500</v>
+      </c>
+      <c r="J34" s="454"/>
+      <c r="K34" s="456">
+        <v>8000</v>
+      </c>
+      <c r="L34" s="454"/>
+      <c r="M34" s="456">
+        <v>8800</v>
+      </c>
+      <c r="N34" s="454"/>
+      <c r="O34" s="456">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="461">
+        <v>46334</v>
+      </c>
+      <c r="B35" s="462" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="462" t="s">
+        <v>460</v>
+      </c>
+      <c r="D35" s="463">
+        <v>5900</v>
+      </c>
+      <c r="E35" s="464">
+        <v>6000</v>
+      </c>
+      <c r="G35" s="456">
+        <v>8800</v>
+      </c>
+      <c r="H35" s="454"/>
+      <c r="I35" s="456">
+        <v>8900</v>
+      </c>
+      <c r="J35" s="454"/>
+      <c r="K35" s="456">
+        <v>8800</v>
+      </c>
+      <c r="L35" s="454"/>
+      <c r="M35" s="456">
+        <v>8900</v>
+      </c>
+      <c r="N35" s="454"/>
+      <c r="O35" s="456">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="465">
+        <v>46341</v>
+      </c>
+      <c r="B36" s="466" t="s">
+        <v>461</v>
+      </c>
+      <c r="C36" s="466" t="s">
+        <v>462</v>
+      </c>
+      <c r="D36" s="467">
+        <v>6000</v>
+      </c>
+      <c r="E36" s="468">
+        <v>6600</v>
+      </c>
+      <c r="G36" s="456">
+        <v>8900</v>
+      </c>
+      <c r="H36" s="454"/>
+      <c r="I36" s="456">
+        <v>10000</v>
+      </c>
+      <c r="J36" s="454"/>
+      <c r="K36" s="456">
+        <v>8900</v>
+      </c>
+      <c r="L36" s="454"/>
+      <c r="M36" s="456">
+        <v>9200</v>
+      </c>
+      <c r="N36" s="454"/>
+      <c r="O36" s="456">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="18" x14ac:dyDescent="0.3">
+      <c r="A37" s="452"/>
+      <c r="B37" s="452"/>
+      <c r="C37" s="452"/>
+      <c r="D37" s="452"/>
+      <c r="E37" s="453"/>
+    </row>
+    <row r="39" spans="1:15" ht="18" x14ac:dyDescent="0.3">
+      <c r="B39" s="455" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="454"/>
+      <c r="D39" s="455" t="s">
+        <v>448</v>
+      </c>
+      <c r="E39" s="454"/>
+      <c r="F39" s="455" t="s">
+        <v>448</v>
+      </c>
+      <c r="G39" s="454"/>
+      <c r="H39" s="455" t="s">
+        <v>448</v>
+      </c>
+      <c r="I39" s="454"/>
+      <c r="J39" s="455" t="s">
+        <v>448</v>
+      </c>
+      <c r="K39" s="454"/>
+      <c r="L39" s="455" t="s">
+        <v>448</v>
+      </c>
+      <c r="M39" s="454"/>
+    </row>
+    <row r="40" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B40" s="457" t="s">
+        <v>455</v>
+      </c>
+      <c r="C40" s="454"/>
+      <c r="D40" s="456">
+        <v>8900</v>
+      </c>
+      <c r="E40" s="454"/>
+      <c r="F40" s="456">
+        <v>1000</v>
+      </c>
+      <c r="G40" s="454"/>
+      <c r="H40" s="456">
+        <v>1000</v>
+      </c>
+      <c r="I40" s="454"/>
+      <c r="J40" s="456">
+        <v>1000</v>
+      </c>
+      <c r="K40" s="454"/>
+      <c r="L40" s="456">
+        <v>5900</v>
+      </c>
+      <c r="M40" s="454"/>
+    </row>
+    <row r="41" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B41" s="457" t="s">
+        <v>457</v>
+      </c>
+      <c r="C41" s="454"/>
+      <c r="D41" s="456">
+        <v>8800</v>
+      </c>
+      <c r="E41" s="454"/>
+      <c r="F41" s="456">
+        <v>1000</v>
+      </c>
+      <c r="G41" s="454"/>
+      <c r="H41" s="456">
+        <v>1000</v>
+      </c>
+      <c r="I41" s="454"/>
+      <c r="J41" s="456">
+        <v>1000</v>
+      </c>
+      <c r="K41" s="454"/>
+      <c r="L41" s="456">
+        <v>1000</v>
+      </c>
+      <c r="M41" s="454"/>
+    </row>
+    <row r="42" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B42" s="457" t="s">
+        <v>459</v>
+      </c>
+      <c r="C42" s="454"/>
+      <c r="D42" s="456">
+        <v>8300</v>
+      </c>
+      <c r="E42" s="454"/>
+      <c r="F42" s="456">
+        <v>1000</v>
+      </c>
+      <c r="G42" s="454"/>
+      <c r="H42" s="456">
+        <v>1500</v>
+      </c>
+      <c r="I42" s="454"/>
+      <c r="J42" s="456">
+        <v>1000</v>
+      </c>
+      <c r="K42" s="454"/>
+      <c r="L42" s="456">
+        <v>6000</v>
+      </c>
+      <c r="M42" s="454"/>
+    </row>
+    <row r="43" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B43" s="457" t="s">
+        <v>460</v>
+      </c>
+      <c r="C43" s="454"/>
+      <c r="D43" s="456">
+        <v>8000</v>
+      </c>
+      <c r="E43" s="454"/>
+      <c r="F43" s="456">
+        <v>1000</v>
+      </c>
+      <c r="G43" s="454"/>
+      <c r="H43" s="456">
+        <v>2000</v>
+      </c>
+      <c r="I43" s="454"/>
+      <c r="J43" s="456">
+        <v>1000</v>
+      </c>
+      <c r="K43" s="454"/>
+      <c r="L43" s="456">
+        <v>1000</v>
+      </c>
+      <c r="M43" s="454"/>
+    </row>
+    <row r="44" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B44" s="457" t="s">
+        <v>462</v>
+      </c>
+      <c r="C44" s="454"/>
+      <c r="D44" s="456">
+        <v>7800</v>
+      </c>
+      <c r="E44" s="454"/>
+      <c r="F44" s="456">
+        <v>1500</v>
+      </c>
+      <c r="G44" s="454"/>
+      <c r="H44" s="456">
+        <v>2200</v>
+      </c>
+      <c r="I44" s="454"/>
+      <c r="J44" s="456">
+        <v>1500</v>
+      </c>
+      <c r="K44" s="454"/>
+      <c r="L44" s="456">
+        <v>1000</v>
+      </c>
+      <c r="M44" s="454"/>
+    </row>
+    <row r="45" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B45" s="457" t="s">
+        <v>451</v>
+      </c>
+      <c r="C45" s="454"/>
+      <c r="D45" s="456">
+        <v>7400</v>
+      </c>
+      <c r="E45" s="454"/>
+      <c r="F45" s="456">
+        <v>2000</v>
+      </c>
+      <c r="G45" s="454"/>
+      <c r="H45" s="456">
+        <v>2300</v>
+      </c>
+      <c r="I45" s="454"/>
+      <c r="J45" s="456">
+        <v>2000</v>
+      </c>
+      <c r="K45" s="454"/>
+      <c r="L45" s="456">
+        <v>3000</v>
+      </c>
+      <c r="M45" s="454"/>
+    </row>
+    <row r="46" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B46" s="457" t="s">
+        <v>453</v>
+      </c>
+      <c r="C46" s="454"/>
+      <c r="D46" s="456">
+        <v>7300</v>
+      </c>
+      <c r="E46" s="454"/>
+      <c r="F46" s="456">
+        <v>2200</v>
+      </c>
+      <c r="G46" s="454"/>
+      <c r="H46" s="456">
+        <v>2500</v>
+      </c>
+      <c r="I46" s="454"/>
+      <c r="J46" s="456">
+        <v>2200</v>
+      </c>
+      <c r="K46" s="454"/>
+      <c r="L46" s="456">
+        <v>1500</v>
+      </c>
+      <c r="M46" s="454"/>
+    </row>
+    <row r="47" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B47" s="457" t="s">
+        <v>453</v>
+      </c>
+      <c r="C47" s="454"/>
+      <c r="D47" s="456">
+        <v>7200</v>
+      </c>
+      <c r="E47" s="454"/>
+      <c r="F47" s="456">
+        <v>2300</v>
+      </c>
+      <c r="G47" s="454"/>
+      <c r="H47" s="456">
+        <v>2800</v>
+      </c>
+      <c r="I47" s="454"/>
+      <c r="J47" s="456">
+        <v>2300</v>
+      </c>
+      <c r="K47" s="454"/>
+      <c r="L47" s="456">
+        <v>2000</v>
+      </c>
+      <c r="M47" s="454"/>
+    </row>
+    <row r="48" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B48" s="457" t="s">
+        <v>455</v>
+      </c>
+      <c r="C48" s="454"/>
+      <c r="D48" s="456">
+        <v>7000</v>
+      </c>
+      <c r="E48" s="454"/>
+      <c r="F48" s="456">
+        <v>2800</v>
+      </c>
+      <c r="G48" s="454"/>
+      <c r="H48" s="456">
+        <v>3000</v>
+      </c>
+      <c r="I48" s="454"/>
+      <c r="J48" s="456">
+        <v>2800</v>
+      </c>
+      <c r="K48" s="454"/>
+      <c r="L48" s="456">
+        <v>2200</v>
+      </c>
+      <c r="M48" s="454"/>
+    </row>
+    <row r="49" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B49" s="457" t="s">
+        <v>457</v>
+      </c>
+      <c r="C49" s="454"/>
+      <c r="D49" s="456">
+        <v>6600</v>
+      </c>
+      <c r="E49" s="454"/>
+      <c r="F49" s="456">
+        <v>3000</v>
+      </c>
+      <c r="G49" s="454"/>
+      <c r="H49" s="456">
+        <v>3000</v>
+      </c>
+      <c r="I49" s="454"/>
+      <c r="J49" s="456">
+        <v>3000</v>
+      </c>
+      <c r="K49" s="454"/>
+      <c r="L49" s="456">
+        <v>2300</v>
+      </c>
+      <c r="M49" s="454"/>
+    </row>
+    <row r="50" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B50" s="457" t="s">
+        <v>459</v>
+      </c>
+      <c r="C50" s="454"/>
+      <c r="D50" s="456">
+        <v>6000</v>
+      </c>
+      <c r="E50" s="454"/>
+      <c r="F50" s="456">
+        <v>3330</v>
+      </c>
+      <c r="G50" s="454"/>
+      <c r="H50" s="456">
+        <v>3330</v>
+      </c>
+      <c r="I50" s="454"/>
+      <c r="J50" s="456">
+        <v>3330</v>
+      </c>
+      <c r="K50" s="454"/>
+      <c r="L50" s="456">
+        <v>2800</v>
+      </c>
+      <c r="M50" s="454"/>
+    </row>
+    <row r="51" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B51" s="457" t="s">
+        <v>460</v>
+      </c>
+      <c r="C51" s="454"/>
+      <c r="D51" s="456">
+        <v>6000</v>
+      </c>
+      <c r="E51" s="454"/>
+      <c r="F51" s="456">
+        <v>3700</v>
+      </c>
+      <c r="G51" s="454"/>
+      <c r="H51" s="456">
+        <v>3700</v>
+      </c>
+      <c r="I51" s="454"/>
+      <c r="J51" s="456">
+        <v>3700</v>
+      </c>
+      <c r="K51" s="454"/>
+      <c r="L51" s="456">
+        <v>3000</v>
+      </c>
+      <c r="M51" s="454"/>
+    </row>
+    <row r="52" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B52" s="457" t="s">
+        <v>462</v>
+      </c>
+      <c r="C52" s="454"/>
+      <c r="D52" s="456">
+        <v>5900</v>
+      </c>
+      <c r="E52" s="454"/>
+      <c r="F52" s="456">
+        <v>4000</v>
+      </c>
+      <c r="G52" s="454"/>
+      <c r="H52" s="456">
+        <v>4000</v>
+      </c>
+      <c r="I52" s="454"/>
+      <c r="J52" s="456">
+        <v>4000</v>
+      </c>
+      <c r="K52" s="454"/>
+      <c r="L52" s="456">
+        <v>8300</v>
+      </c>
+      <c r="M52" s="454"/>
+    </row>
+    <row r="53" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B53" s="457" t="s">
+        <v>451</v>
+      </c>
+      <c r="C53" s="454"/>
+      <c r="D53" s="456">
+        <v>5700</v>
+      </c>
+      <c r="E53" s="454"/>
+      <c r="F53" s="456">
+        <v>4000</v>
+      </c>
+      <c r="G53" s="454"/>
+      <c r="H53" s="456">
+        <v>4000</v>
+      </c>
+      <c r="I53" s="454"/>
+      <c r="J53" s="456">
+        <v>4000</v>
+      </c>
+      <c r="K53" s="454"/>
+      <c r="L53" s="456">
+        <v>3330</v>
+      </c>
+      <c r="M53" s="454"/>
+    </row>
+    <row r="54" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B54" s="457" t="s">
+        <v>453</v>
+      </c>
+      <c r="C54" s="454"/>
+      <c r="D54" s="456">
+        <v>5500</v>
+      </c>
+      <c r="E54" s="454"/>
+      <c r="F54" s="456">
+        <v>4200</v>
+      </c>
+      <c r="G54" s="454"/>
+      <c r="H54" s="456">
+        <v>4200</v>
+      </c>
+      <c r="I54" s="454"/>
+      <c r="J54" s="456">
+        <v>4200</v>
+      </c>
+      <c r="K54" s="454"/>
+      <c r="L54" s="456">
+        <v>5500</v>
+      </c>
+      <c r="M54" s="454"/>
+    </row>
+    <row r="55" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B55" s="457" t="s">
+        <v>455</v>
+      </c>
+      <c r="C55" s="454"/>
+      <c r="D55" s="456">
+        <v>5300</v>
+      </c>
+      <c r="E55" s="454"/>
+      <c r="F55" s="456">
+        <v>4500</v>
+      </c>
+      <c r="G55" s="454"/>
+      <c r="H55" s="456">
+        <v>4500</v>
+      </c>
+      <c r="I55" s="454"/>
+      <c r="J55" s="456">
+        <v>4500</v>
+      </c>
+      <c r="K55" s="454"/>
+      <c r="L55" s="456">
+        <v>3700</v>
+      </c>
+      <c r="M55" s="454"/>
+    </row>
+    <row r="56" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B56" s="457" t="s">
+        <v>457</v>
+      </c>
+      <c r="C56" s="454"/>
+      <c r="D56" s="456">
+        <v>5200</v>
+      </c>
+      <c r="E56" s="454"/>
+      <c r="F56" s="456">
+        <v>5000</v>
+      </c>
+      <c r="G56" s="454"/>
+      <c r="H56" s="456">
+        <v>5000</v>
+      </c>
+      <c r="I56" s="454"/>
+      <c r="J56" s="456">
+        <v>5000</v>
+      </c>
+      <c r="K56" s="454"/>
+      <c r="L56" s="456">
+        <v>4000</v>
+      </c>
+      <c r="M56" s="454"/>
+    </row>
+    <row r="57" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B57" s="457" t="s">
+        <v>459</v>
+      </c>
+      <c r="C57" s="454"/>
+      <c r="D57" s="456">
+        <v>5100</v>
+      </c>
+      <c r="E57" s="454"/>
+      <c r="F57" s="456">
+        <v>5100</v>
+      </c>
+      <c r="G57" s="454"/>
+      <c r="H57" s="456">
+        <v>5100</v>
+      </c>
+      <c r="I57" s="454"/>
+      <c r="J57" s="456">
+        <v>5100</v>
+      </c>
+      <c r="K57" s="454"/>
+      <c r="L57" s="456">
+        <v>4000</v>
+      </c>
+      <c r="M57" s="454"/>
+    </row>
+    <row r="58" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B58" s="457" t="s">
+        <v>460</v>
+      </c>
+      <c r="C58" s="454"/>
+      <c r="D58" s="456">
+        <v>5000</v>
+      </c>
+      <c r="E58" s="454"/>
+      <c r="F58" s="456">
+        <v>5200</v>
+      </c>
+      <c r="G58" s="454"/>
+      <c r="H58" s="456">
+        <v>5200</v>
+      </c>
+      <c r="I58" s="454"/>
+      <c r="J58" s="456">
+        <v>5200</v>
+      </c>
+      <c r="K58" s="454"/>
+      <c r="L58" s="456">
+        <v>5100</v>
+      </c>
+      <c r="M58" s="454"/>
+    </row>
+    <row r="59" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B59" s="457" t="s">
+        <v>462</v>
+      </c>
+      <c r="C59" s="454"/>
+      <c r="D59" s="456">
+        <v>4500</v>
+      </c>
+      <c r="E59" s="454"/>
+      <c r="F59" s="456">
+        <v>5300</v>
+      </c>
+      <c r="G59" s="454"/>
+      <c r="H59" s="456">
+        <v>5300</v>
+      </c>
+      <c r="I59" s="454"/>
+      <c r="J59" s="456">
+        <v>5300</v>
+      </c>
+      <c r="K59" s="454"/>
+      <c r="L59" s="456">
+        <v>4200</v>
+      </c>
+      <c r="M59" s="454"/>
+    </row>
+    <row r="60" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B60" s="457" t="s">
+        <v>451</v>
+      </c>
+      <c r="C60" s="454"/>
+      <c r="D60" s="456">
+        <v>4200</v>
+      </c>
+      <c r="E60" s="454"/>
+      <c r="F60" s="456">
+        <v>5500</v>
+      </c>
+      <c r="G60" s="454"/>
+      <c r="H60" s="456">
+        <v>5500</v>
+      </c>
+      <c r="I60" s="454"/>
+      <c r="J60" s="456">
+        <v>5500</v>
+      </c>
+      <c r="K60" s="454"/>
+      <c r="L60" s="456">
+        <v>4500</v>
+      </c>
+      <c r="M60" s="454"/>
+    </row>
+    <row r="61" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B61" s="457" t="s">
+        <v>453</v>
+      </c>
+      <c r="C61" s="454"/>
+      <c r="D61" s="456">
+        <v>4000</v>
+      </c>
+      <c r="E61" s="454"/>
+      <c r="F61" s="456">
+        <v>5700</v>
+      </c>
+      <c r="G61" s="454"/>
+      <c r="H61" s="456">
+        <v>5700</v>
+      </c>
+      <c r="I61" s="454"/>
+      <c r="J61" s="456">
+        <v>5700</v>
+      </c>
+      <c r="K61" s="454"/>
+      <c r="L61" s="456">
+        <v>6000</v>
+      </c>
+      <c r="M61" s="454"/>
+    </row>
+    <row r="62" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B62" s="457" t="s">
+        <v>455</v>
+      </c>
+      <c r="C62" s="454"/>
+      <c r="D62" s="456">
+        <v>4000</v>
+      </c>
+      <c r="E62" s="454"/>
+      <c r="F62" s="456">
+        <v>5900</v>
+      </c>
+      <c r="G62" s="454"/>
+      <c r="H62" s="456">
+        <v>5900</v>
+      </c>
+      <c r="I62" s="454"/>
+      <c r="J62" s="456">
+        <v>5900</v>
+      </c>
+      <c r="K62" s="454"/>
+      <c r="L62" s="456">
+        <v>5000</v>
+      </c>
+      <c r="M62" s="454"/>
+    </row>
+    <row r="63" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B63" s="457" t="s">
+        <v>457</v>
+      </c>
+      <c r="C63" s="454"/>
+      <c r="D63" s="456">
+        <v>3700</v>
+      </c>
+      <c r="E63" s="454"/>
+      <c r="F63" s="456">
+        <v>6000</v>
+      </c>
+      <c r="G63" s="454"/>
+      <c r="H63" s="456">
+        <v>6000</v>
+      </c>
+      <c r="I63" s="454"/>
+      <c r="J63" s="456">
+        <v>6000</v>
+      </c>
+      <c r="K63" s="454"/>
+      <c r="L63" s="456">
+        <v>5200</v>
+      </c>
+      <c r="M63" s="454"/>
+    </row>
+    <row r="64" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B64" s="457" t="s">
+        <v>459</v>
+      </c>
+      <c r="C64" s="454"/>
+      <c r="D64" s="456">
+        <v>3330</v>
+      </c>
+      <c r="E64" s="454"/>
+      <c r="F64" s="456">
+        <v>6000</v>
+      </c>
+      <c r="G64" s="454"/>
+      <c r="H64" s="456">
+        <v>6000</v>
+      </c>
+      <c r="I64" s="454"/>
+      <c r="J64" s="456">
+        <v>6000</v>
+      </c>
+      <c r="K64" s="454"/>
+      <c r="L64" s="456">
+        <v>5300</v>
+      </c>
+      <c r="M64" s="454"/>
+    </row>
+    <row r="65" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B65" s="457" t="s">
+        <v>460</v>
+      </c>
+      <c r="C65" s="454"/>
+      <c r="D65" s="456">
+        <v>3000</v>
+      </c>
+      <c r="E65" s="454"/>
+      <c r="F65" s="456">
+        <v>6600</v>
+      </c>
+      <c r="G65" s="454"/>
+      <c r="H65" s="456">
+        <v>6600</v>
+      </c>
+      <c r="I65" s="454"/>
+      <c r="J65" s="456">
+        <v>6600</v>
+      </c>
+      <c r="K65" s="454"/>
+      <c r="L65" s="456">
+        <v>5700</v>
+      </c>
+      <c r="M65" s="454"/>
+    </row>
+    <row r="66" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B66" s="457" t="s">
+        <v>462</v>
+      </c>
+      <c r="C66" s="454"/>
+      <c r="D66" s="456">
+        <v>2800</v>
+      </c>
+      <c r="E66" s="454"/>
+      <c r="F66" s="456">
+        <v>7000</v>
+      </c>
+      <c r="G66" s="454"/>
+      <c r="H66" s="456">
+        <v>7000</v>
+      </c>
+      <c r="I66" s="454"/>
+      <c r="J66" s="456">
+        <v>7000</v>
+      </c>
+      <c r="K66" s="454"/>
+      <c r="L66" s="456">
+        <v>6000</v>
+      </c>
+      <c r="M66" s="454"/>
+    </row>
+    <row r="67" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B67" s="457" t="s">
+        <v>451</v>
+      </c>
+      <c r="C67" s="454"/>
+      <c r="D67" s="456">
+        <v>2300</v>
+      </c>
+      <c r="E67" s="454"/>
+      <c r="F67" s="456">
+        <v>7200</v>
+      </c>
+      <c r="G67" s="454"/>
+      <c r="H67" s="456">
+        <v>7200</v>
+      </c>
+      <c r="I67" s="454"/>
+      <c r="J67" s="456">
+        <v>7200</v>
+      </c>
+      <c r="K67" s="454"/>
+      <c r="L67" s="456">
+        <v>6600</v>
+      </c>
+      <c r="M67" s="454"/>
+    </row>
+    <row r="68" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B68" s="457" t="s">
+        <v>453</v>
+      </c>
+      <c r="C68" s="454"/>
+      <c r="D68" s="456">
+        <v>2200</v>
+      </c>
+      <c r="E68" s="454"/>
+      <c r="F68" s="456">
+        <v>7300</v>
+      </c>
+      <c r="G68" s="454"/>
+      <c r="H68" s="456">
+        <v>7300</v>
+      </c>
+      <c r="I68" s="454"/>
+      <c r="J68" s="456">
+        <v>7300</v>
+      </c>
+      <c r="K68" s="454"/>
+      <c r="L68" s="456">
+        <v>7000</v>
+      </c>
+      <c r="M68" s="454"/>
+    </row>
+    <row r="69" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B69" s="457" t="s">
+        <v>455</v>
+      </c>
+      <c r="C69" s="454"/>
+      <c r="D69" s="456">
+        <v>2000</v>
+      </c>
+      <c r="E69" s="454"/>
+      <c r="F69" s="456">
+        <v>7400</v>
+      </c>
+      <c r="G69" s="454"/>
+      <c r="H69" s="456">
+        <v>7400</v>
+      </c>
+      <c r="I69" s="454"/>
+      <c r="J69" s="456">
+        <v>7400</v>
+      </c>
+      <c r="K69" s="454"/>
+      <c r="L69" s="456">
+        <v>7300</v>
+      </c>
+      <c r="M69" s="454"/>
+    </row>
+    <row r="70" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B70" s="457" t="s">
+        <v>457</v>
+      </c>
+      <c r="C70" s="454"/>
+      <c r="D70" s="456">
+        <v>1500</v>
+      </c>
+      <c r="E70" s="454"/>
+      <c r="F70" s="456">
+        <v>7800</v>
+      </c>
+      <c r="G70" s="454"/>
+      <c r="H70" s="456">
+        <v>7800</v>
+      </c>
+      <c r="I70" s="454"/>
+      <c r="J70" s="456">
+        <v>7800</v>
+      </c>
+      <c r="K70" s="454"/>
+      <c r="L70" s="456">
+        <v>7400</v>
+      </c>
+      <c r="M70" s="454"/>
+    </row>
+    <row r="71" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B71" s="457" t="s">
+        <v>459</v>
+      </c>
+      <c r="C71" s="454"/>
+      <c r="D71" s="456">
+        <v>1000</v>
+      </c>
+      <c r="E71" s="454"/>
+      <c r="F71" s="456">
+        <v>8000</v>
+      </c>
+      <c r="G71" s="454"/>
+      <c r="H71" s="456">
+        <v>8000</v>
+      </c>
+      <c r="I71" s="454"/>
+      <c r="J71" s="456">
+        <v>8000</v>
+      </c>
+      <c r="K71" s="454"/>
+      <c r="L71" s="456">
+        <v>7800</v>
+      </c>
+      <c r="M71" s="454"/>
+    </row>
+    <row r="72" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B72" s="457" t="s">
+        <v>460</v>
+      </c>
+      <c r="C72" s="454"/>
+      <c r="D72" s="456">
+        <v>1000</v>
+      </c>
+      <c r="E72" s="454"/>
+      <c r="F72" s="456">
+        <v>8300</v>
+      </c>
+      <c r="G72" s="454"/>
+      <c r="H72" s="456">
+        <v>8300</v>
+      </c>
+      <c r="I72" s="454"/>
+      <c r="J72" s="456">
+        <v>8300</v>
+      </c>
+      <c r="K72" s="454"/>
+      <c r="L72" s="456">
+        <v>8000</v>
+      </c>
+      <c r="M72" s="454"/>
+    </row>
+    <row r="73" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B73" s="457" t="s">
+        <v>462</v>
+      </c>
+      <c r="C73" s="454"/>
+      <c r="D73" s="456">
+        <v>1000</v>
+      </c>
+      <c r="E73" s="454"/>
+      <c r="F73" s="456">
+        <v>8800</v>
+      </c>
+      <c r="G73" s="454"/>
+      <c r="H73" s="456">
+        <v>8800</v>
+      </c>
+      <c r="I73" s="454"/>
+      <c r="J73" s="456">
+        <v>8800</v>
+      </c>
+      <c r="K73" s="454"/>
+      <c r="L73" s="456">
+        <v>8800</v>
+      </c>
+      <c r="M73" s="454"/>
+    </row>
+    <row r="74" spans="2:13" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B74" s="457" t="s">
+        <v>451</v>
+      </c>
+      <c r="C74" s="454"/>
+      <c r="D74" s="456">
+        <v>1000</v>
+      </c>
+      <c r="E74" s="454"/>
+      <c r="F74" s="456">
+        <v>8900</v>
+      </c>
+      <c r="G74" s="454"/>
+      <c r="H74" s="456">
+        <v>8900</v>
+      </c>
+      <c r="I74" s="454"/>
+      <c r="J74" s="456">
+        <v>8900</v>
+      </c>
+      <c r="K74" s="454"/>
+      <c r="L74" s="456">
+        <v>8900</v>
+      </c>
+      <c r="M74" s="454"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:A36">
+    <cfRule type="timePeriod" dxfId="8" priority="15" timePeriod="nextWeek">
+      <formula>AND(ROUNDDOWN(A2,0)-TODAY()&gt;(7-WEEKDAY(TODAY())),ROUNDDOWN(A2,0)-TODAY()&lt;(15-WEEKDAY(TODAY())))</formula>
+    </cfRule>
+    <cfRule type="timePeriod" dxfId="7" priority="17" timePeriod="yesterday">
+      <formula>FLOOR(A2,1)=TODAY()-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B36">
+    <cfRule type="containsText" dxfId="6" priority="18" operator="containsText" text="ma">
+      <formula>NOT(ISERROR(SEARCH("ma",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40:B74">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C36">
+    <cfRule type="containsText" dxfId="5" priority="19" operator="containsText" text="Pen">
+      <formula>NOT(ISERROR(SEARCH("Pen",C2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D36">
+    <cfRule type="cellIs" dxfId="4" priority="21" operator="greaterThan">
+      <formula>4000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D40:D74">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E36">
+    <cfRule type="cellIs" dxfId="3" priority="20" operator="between">
+      <formula>4000</formula>
+      <formula>7000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F40:F74">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF7030A0"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF00B050"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF0070C0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G36">
+    <cfRule type="top10" dxfId="2" priority="14" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H40:H74">
+    <cfRule type="iconSet" priority="2">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I36">
+    <cfRule type="aboveAverage" dxfId="1" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J40:J74">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="4Rating">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K36">
+    <cfRule type="aboveAverage" dxfId="0" priority="12" aboveAverage="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M36">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{16AAE4A7-3295-498C-9D27-0E430618114E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O36">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{80DF8A68-B068-4EF5-825F-D1F924FB8F81}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{16AAE4A7-3295-498C-9D27-0E430618114E}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>M2:M36</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{80DF8A68-B068-4EF5-825F-D1F924FB8F81}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>O2:O36</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D25E27EC-A975-49DE-8B5D-3044EF766351}">
+  <dimension ref="B2:C16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="37.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B2" s="622" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2" s="623"/>
+    </row>
+    <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B3" s="472" t="s">
+        <v>464</v>
+      </c>
+      <c r="C3" s="472" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B4" s="473" t="s">
+        <v>466</v>
+      </c>
+      <c r="C4" s="473">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B5" s="473" t="s">
+        <v>467</v>
+      </c>
+      <c r="C5" s="473">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B6" s="473" t="s">
+        <v>468</v>
+      </c>
+      <c r="C6" s="473">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B7" s="473" t="s">
+        <v>469</v>
+      </c>
+      <c r="C7" s="473">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B8" s="473" t="s">
+        <v>470</v>
+      </c>
+      <c r="C8" s="473">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B9" s="473" t="s">
+        <v>471</v>
+      </c>
+      <c r="C9" s="473">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B10" s="473" t="s">
+        <v>472</v>
+      </c>
+      <c r="C10" s="473">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B11" s="473" t="s">
+        <v>473</v>
+      </c>
+      <c r="C11" s="473">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B12" s="473" t="s">
+        <v>474</v>
+      </c>
+      <c r="C12" s="473">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B13" s="473" t="s">
+        <v>475</v>
+      </c>
+      <c r="C13" s="473">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B14" s="474" t="s">
+        <v>356</v>
+      </c>
+      <c r="C14" s="474">
+        <f>SUM(C4:C13)</f>
+        <v>50900</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="B15" s="475"/>
+      <c r="C15" s="471"/>
+    </row>
+    <row r="16" spans="2:3" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B16" s="476" t="s">
+        <v>476</v>
+      </c>
+      <c r="C16" s="477">
+        <v>65000</v>
+      </c>
+    </row>
+  </sheetData>
+  <scenarios current="0" show="0" sqref="C14">
+    <scenario name="Lower_Prices" locked="1" count="10" user="HP" comment="Created by HP on 09-09-2026">
+      <inputCells r="C4" val="6000"/>
+      <inputCells r="C5" val="5000"/>
+      <inputCells r="C6" val="300"/>
+      <inputCells r="C7" val="2500"/>
+      <inputCells r="C8" val="700"/>
+      <inputCells r="C9" val="20000"/>
+      <inputCells r="C10" val="4500"/>
+      <inputCells r="C11" val="10000"/>
+      <inputCells r="C12" val="1500"/>
+      <inputCells r="C13" val="400"/>
+    </scenario>
+    <scenario name="Higher_Prices" locked="1" count="10" user="HP" comment="Created by HP on 09-09-2026">
+      <inputCells r="C4" val="9000"/>
+      <inputCells r="C5" val="6500"/>
+      <inputCells r="C6" val="4000"/>
+      <inputCells r="C7" val="2500"/>
+      <inputCells r="C8" val="700"/>
+      <inputCells r="C9" val="20000"/>
+      <inputCells r="C10" val="4500"/>
+      <inputCells r="C11" val="12000"/>
+      <inputCells r="C12" val="2000"/>
+      <inputCells r="C13" val="400"/>
+    </scenario>
+  </scenarios>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D94B23-9B84-4375-8336-7789FFC1D9E3}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="B1:F20"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="13.109375" bestFit="1" customWidth="1" outlineLevel="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="485" t="s">
+        <v>493</v>
+      </c>
+      <c r="C2" s="485"/>
+      <c r="D2" s="490"/>
+      <c r="E2" s="490"/>
+      <c r="F2" s="490"/>
+    </row>
+    <row r="3" spans="2:6" ht="15.6" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="484"/>
+      <c r="C3" s="484"/>
+      <c r="D3" s="491" t="s">
+        <v>495</v>
+      </c>
+      <c r="E3" s="491" t="s">
+        <v>490</v>
+      </c>
+      <c r="F3" s="491" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="20.399999999999999" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="487"/>
+      <c r="C4" s="487"/>
+      <c r="E4" s="493" t="s">
+        <v>491</v>
+      </c>
+      <c r="F4" s="493" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="488" t="s">
+        <v>494</v>
+      </c>
+      <c r="C5" s="488"/>
+      <c r="D5" s="486"/>
+      <c r="E5" s="486"/>
+      <c r="F5" s="486"/>
+    </row>
+    <row r="6" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="487"/>
+      <c r="C6" s="487" t="s">
+        <v>466</v>
+      </c>
+      <c r="D6">
+        <v>6000</v>
+      </c>
+      <c r="E6" s="492">
+        <v>6000</v>
+      </c>
+      <c r="F6" s="492">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="487"/>
+      <c r="C7" s="487" t="s">
+        <v>500</v>
+      </c>
+      <c r="D7">
+        <v>5000</v>
+      </c>
+      <c r="E7" s="492">
+        <v>5000</v>
+      </c>
+      <c r="F7" s="492">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="487"/>
+      <c r="C8" s="487" t="s">
+        <v>468</v>
+      </c>
+      <c r="D8">
+        <v>300</v>
+      </c>
+      <c r="E8" s="492">
+        <v>300</v>
+      </c>
+      <c r="F8" s="492">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="487"/>
+      <c r="C9" s="487" t="s">
+        <v>483</v>
+      </c>
+      <c r="D9">
+        <v>2500</v>
+      </c>
+      <c r="E9" s="492">
+        <v>2500</v>
+      </c>
+      <c r="F9" s="492">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="487"/>
+      <c r="C10" s="487" t="s">
+        <v>484</v>
+      </c>
+      <c r="D10">
+        <v>700</v>
+      </c>
+      <c r="E10" s="492">
+        <v>700</v>
+      </c>
+      <c r="F10" s="492">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="487"/>
+      <c r="C11" s="487" t="s">
+        <v>471</v>
+      </c>
+      <c r="D11">
+        <v>20000</v>
+      </c>
+      <c r="E11" s="492">
+        <v>20000</v>
+      </c>
+      <c r="F11" s="492">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="487"/>
+      <c r="C12" s="487" t="s">
+        <v>485</v>
+      </c>
+      <c r="D12">
+        <v>4500</v>
+      </c>
+      <c r="E12" s="492">
+        <v>4500</v>
+      </c>
+      <c r="F12" s="492">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="487"/>
+      <c r="C13" s="487" t="s">
+        <v>486</v>
+      </c>
+      <c r="D13">
+        <v>10000</v>
+      </c>
+      <c r="E13" s="492">
+        <v>10000</v>
+      </c>
+      <c r="F13" s="492">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="487"/>
+      <c r="C14" s="487" t="s">
+        <v>487</v>
+      </c>
+      <c r="D14">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="492">
+        <v>1500</v>
+      </c>
+      <c r="F14" s="492">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="487"/>
+      <c r="C15" s="487" t="s">
+        <v>488</v>
+      </c>
+      <c r="D15">
+        <v>400</v>
+      </c>
+      <c r="E15" s="492">
+        <v>400</v>
+      </c>
+      <c r="F15" s="492">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="488" t="s">
+        <v>496</v>
+      </c>
+      <c r="C16" s="488"/>
+      <c r="D16" s="486"/>
+      <c r="E16" s="486"/>
+      <c r="F16" s="486"/>
+    </row>
+    <row r="17" spans="2:6" ht="15" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="489"/>
+      <c r="C17" s="489" t="s">
+        <v>489</v>
+      </c>
+      <c r="D17" s="470">
+        <v>50900</v>
+      </c>
+      <c r="E17" s="470">
+        <v>50900</v>
+      </c>
+      <c r="F17" s="470">
+        <v>61600</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>499</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8991A535-0463-4C84-876B-F5A837C543B4}">
+  <dimension ref="B2:C16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B2" s="622" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2" s="623"/>
+    </row>
+    <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B3" s="472" t="s">
+        <v>464</v>
+      </c>
+      <c r="C3" s="472" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B4" s="473" t="s">
+        <v>466</v>
+      </c>
+      <c r="C4" s="473">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B5" s="473" t="s">
+        <v>467</v>
+      </c>
+      <c r="C5" s="473">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B6" s="473" t="s">
+        <v>468</v>
+      </c>
+      <c r="C6" s="473">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B7" s="473" t="s">
+        <v>469</v>
+      </c>
+      <c r="C7" s="473">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B8" s="473" t="s">
+        <v>470</v>
+      </c>
+      <c r="C8" s="473">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B9" s="473" t="s">
+        <v>471</v>
+      </c>
+      <c r="C9" s="494">
+        <v>16400.000000000007</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B10" s="473" t="s">
+        <v>472</v>
+      </c>
+      <c r="C10" s="473">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B11" s="473" t="s">
+        <v>473</v>
+      </c>
+      <c r="C11" s="473">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B12" s="473" t="s">
+        <v>474</v>
+      </c>
+      <c r="C12" s="473">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B13" s="473" t="s">
+        <v>475</v>
+      </c>
+      <c r="C13" s="473">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B14" s="474" t="s">
+        <v>356</v>
+      </c>
+      <c r="C14" s="474" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="B15" s="475"/>
+      <c r="C15" s="471"/>
+    </row>
+    <row r="16" spans="2:3" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B16" s="476" t="s">
+        <v>476</v>
+      </c>
+      <c r="C16" s="477"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D54137-86E8-456B-AB56-D0A4EBA89623}">
+  <dimension ref="C2:I16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="32.88671875" customWidth="1"/>
+    <col min="4" max="4" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="C2" s="472" t="s">
+        <v>477</v>
+      </c>
+      <c r="D2" s="479" t="s">
+        <v>478</v>
+      </c>
+      <c r="E2" s="478"/>
+      <c r="G2" s="472" t="s">
+        <v>477</v>
+      </c>
+      <c r="H2" s="479" t="s">
+        <v>478</v>
+      </c>
+      <c r="I2" s="478"/>
+    </row>
+    <row r="3" spans="3:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="C3" s="472" t="s">
+        <v>403</v>
+      </c>
+      <c r="D3" s="480">
+        <v>150000</v>
+      </c>
+      <c r="E3" s="478"/>
+      <c r="G3" s="472" t="s">
+        <v>403</v>
+      </c>
+      <c r="H3" s="480">
+        <v>150000</v>
+      </c>
+      <c r="I3" s="478"/>
+    </row>
+    <row r="4" spans="3:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="C4" s="472" t="s">
+        <v>479</v>
+      </c>
+      <c r="D4" s="480">
+        <v>50000</v>
+      </c>
+      <c r="E4" s="478"/>
+      <c r="G4" s="472" t="s">
+        <v>479</v>
+      </c>
+      <c r="H4" s="480">
+        <v>50000</v>
+      </c>
+      <c r="I4" s="478"/>
+    </row>
+    <row r="5" spans="3:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="C5" s="472" t="s">
+        <v>480</v>
+      </c>
+      <c r="D5" s="495">
+        <v>24.999999480308954</v>
+      </c>
+      <c r="E5" s="478"/>
+      <c r="G5" s="472" t="s">
+        <v>480</v>
+      </c>
+      <c r="H5" s="480">
+        <v>36</v>
+      </c>
+      <c r="I5" s="478"/>
+    </row>
+    <row r="6" spans="3:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="C6" s="496" t="s">
+        <v>501</v>
+      </c>
+      <c r="D6" s="481">
+        <v>100000</v>
+      </c>
+      <c r="E6" s="478"/>
+      <c r="H6" s="481">
+        <v>100000</v>
+      </c>
+      <c r="I6" s="478"/>
+    </row>
+    <row r="7" spans="3:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="C7" s="469" t="s">
+        <v>481</v>
+      </c>
+      <c r="D7" s="482">
+        <f>D6/D5</f>
+        <v>4000.000083150569</v>
+      </c>
+      <c r="E7" s="483" t="s">
+        <v>482</v>
+      </c>
+      <c r="G7" s="469" t="s">
+        <v>481</v>
+      </c>
+      <c r="H7" s="482"/>
+      <c r="I7" s="483" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="C11" s="472" t="s">
+        <v>477</v>
+      </c>
+      <c r="D11" s="479" t="s">
+        <v>478</v>
+      </c>
+      <c r="E11" s="478"/>
+    </row>
+    <row r="12" spans="3:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="C12" s="472" t="s">
+        <v>403</v>
+      </c>
+      <c r="D12" s="480">
+        <v>150000</v>
+      </c>
+      <c r="E12" s="478"/>
+    </row>
+    <row r="13" spans="3:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="C13" s="472" t="s">
+        <v>479</v>
+      </c>
+      <c r="D13" s="480">
+        <v>50000</v>
+      </c>
+      <c r="E13" s="478"/>
+    </row>
+    <row r="14" spans="3:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="C14" s="472" t="s">
+        <v>480</v>
+      </c>
+      <c r="D14" s="480">
+        <f>D15/D16</f>
+        <v>31.000004361916073</v>
+      </c>
+      <c r="E14" s="478"/>
+    </row>
+    <row r="15" spans="3:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="C15" s="496" t="s">
+        <v>501</v>
+      </c>
+      <c r="D15" s="481">
+        <v>100000</v>
+      </c>
+      <c r="E15" s="478"/>
+    </row>
+    <row r="16" spans="3:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="C16" s="469" t="s">
+        <v>481</v>
+      </c>
+      <c r="D16" s="482">
+        <v>3225.8059977195153</v>
+      </c>
+      <c r="E16" s="483" t="s">
+        <v>482</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC5E2DD-AD85-4170-B39C-1979BA1B640F}">
+  <dimension ref="B2:L48"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="39.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" customWidth="1"/>
+    <col min="11" max="11" width="22.109375" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.3">
+      <c r="B2" s="515" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2" s="516"/>
+      <c r="F2" s="501" t="s">
+        <v>468</v>
+      </c>
+      <c r="G2" s="501" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B3" s="497" t="s">
+        <v>464</v>
+      </c>
+      <c r="C3" s="497" t="s">
+        <v>465</v>
+      </c>
+      <c r="F3" s="502"/>
+      <c r="G3" s="503">
+        <f>C14</f>
+        <v>57100</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B4" s="498" t="s">
+        <v>466</v>
+      </c>
+      <c r="C4" s="498">
+        <v>8000</v>
+      </c>
+      <c r="F4" s="504">
+        <v>2000</v>
+      </c>
+      <c r="G4" s="504">
+        <f t="dataTable" ref="G4:G8" dt2D="0" dtr="0" r1="C6"/>
+        <v>56100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B5" s="498" t="s">
+        <v>467</v>
+      </c>
+      <c r="C5" s="498">
+        <v>6000</v>
+      </c>
+      <c r="F5" s="504">
+        <v>3500</v>
+      </c>
+      <c r="G5" s="504">
+        <v>57600</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B6" s="499" t="s">
+        <v>468</v>
+      </c>
+      <c r="C6" s="499">
+        <v>3000</v>
+      </c>
+      <c r="F6" s="504">
+        <v>4000</v>
+      </c>
+      <c r="G6" s="504">
+        <v>58100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B7" s="498" t="s">
+        <v>469</v>
+      </c>
+      <c r="C7" s="498">
+        <v>2500</v>
+      </c>
+      <c r="F7" s="504">
+        <v>5000</v>
+      </c>
+      <c r="G7" s="504">
+        <v>59100</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B8" s="498" t="s">
+        <v>470</v>
+      </c>
+      <c r="C8" s="498">
+        <v>700</v>
+      </c>
+      <c r="F8" s="504">
+        <v>6000</v>
+      </c>
+      <c r="G8" s="504">
+        <v>60100</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B9" s="498" t="s">
+        <v>471</v>
+      </c>
+      <c r="C9" s="498">
+        <v>20000</v>
+      </c>
+      <c r="F9" s="504"/>
+      <c r="G9" s="504"/>
+    </row>
+    <row r="10" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B10" s="498" t="s">
+        <v>472</v>
+      </c>
+      <c r="C10" s="498">
+        <v>4500</v>
+      </c>
+      <c r="F10" s="504"/>
+      <c r="G10" s="504"/>
+    </row>
+    <row r="11" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B11" s="498" t="s">
+        <v>473</v>
+      </c>
+      <c r="C11" s="498">
+        <v>10000</v>
+      </c>
+      <c r="F11" s="504"/>
+      <c r="G11" s="504"/>
+    </row>
+    <row r="12" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B12" s="498" t="s">
+        <v>474</v>
+      </c>
+      <c r="C12" s="498">
+        <v>2000</v>
+      </c>
+      <c r="F12" s="504"/>
+      <c r="G12" s="504"/>
+    </row>
+    <row r="13" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B13" s="498" t="s">
+        <v>475</v>
+      </c>
+      <c r="C13" s="498">
+        <v>400</v>
+      </c>
+      <c r="F13" s="504"/>
+      <c r="G13" s="504"/>
+    </row>
+    <row r="14" spans="2:7" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B14" s="500" t="s">
+        <v>356</v>
+      </c>
+      <c r="C14" s="500">
+        <f>SUM(C4:C13)</f>
+        <v>57100</v>
+      </c>
+      <c r="F14" s="504"/>
+      <c r="G14" s="504"/>
+    </row>
+    <row r="22" spans="2:12" ht="21" x14ac:dyDescent="0.3">
+      <c r="B22" s="506" t="s">
+        <v>503</v>
+      </c>
+      <c r="C22" s="506">
+        <v>1000</v>
+      </c>
+      <c r="D22" s="505"/>
+      <c r="E22" s="505"/>
+      <c r="F22" s="507" t="s">
+        <v>504</v>
+      </c>
+      <c r="G22" s="507" t="s">
+        <v>505</v>
+      </c>
+      <c r="H22" s="505"/>
+      <c r="I22" s="505"/>
+      <c r="J22" s="505"/>
+      <c r="K22" s="505"/>
+      <c r="L22" s="505"/>
+    </row>
+    <row r="23" spans="2:12" ht="21" x14ac:dyDescent="0.3">
+      <c r="B23" s="506" t="s">
+        <v>504</v>
+      </c>
+      <c r="C23" s="506">
+        <v>20</v>
+      </c>
+      <c r="D23" s="505"/>
+      <c r="E23" s="505"/>
+      <c r="F23" s="508"/>
+      <c r="G23" s="508">
+        <f>C26</f>
+        <v>20000</v>
+      </c>
+      <c r="H23" s="505"/>
+      <c r="I23" s="505"/>
+      <c r="J23" s="505"/>
+      <c r="K23" s="505"/>
+      <c r="L23" s="505"/>
+    </row>
+    <row r="24" spans="2:12" ht="21" x14ac:dyDescent="0.3">
+      <c r="B24" s="506" t="s">
+        <v>277</v>
+      </c>
+      <c r="C24" s="506">
+        <v>2</v>
+      </c>
+      <c r="D24" s="505"/>
+      <c r="E24" s="505"/>
+      <c r="F24" s="509">
+        <v>10</v>
+      </c>
+      <c r="G24" s="509">
+        <f t="dataTable" ref="G24:G30" dt2D="0" dtr="0" r1="C23"/>
+        <v>10000</v>
+      </c>
+      <c r="H24" s="505"/>
+      <c r="I24" s="505"/>
+      <c r="J24" s="505"/>
+      <c r="K24" s="505"/>
+      <c r="L24" s="505"/>
+    </row>
+    <row r="25" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B25" s="510"/>
+      <c r="C25" s="510"/>
+      <c r="D25" s="505"/>
+      <c r="E25" s="505"/>
+      <c r="F25" s="509">
+        <v>10</v>
+      </c>
+      <c r="G25" s="509">
+        <v>10000</v>
+      </c>
+      <c r="H25" s="505"/>
+      <c r="I25" s="505"/>
+      <c r="J25" s="505"/>
+      <c r="K25" s="505"/>
+      <c r="L25" s="505"/>
+    </row>
+    <row r="26" spans="2:12" ht="21" x14ac:dyDescent="0.3">
+      <c r="B26" s="506" t="s">
+        <v>505</v>
+      </c>
+      <c r="C26" s="506">
+        <f>C22*C23</f>
+        <v>20000</v>
+      </c>
+      <c r="D26" s="505"/>
+      <c r="E26" s="505"/>
+      <c r="F26" s="509">
+        <v>25</v>
+      </c>
+      <c r="G26" s="509">
+        <v>25000</v>
+      </c>
+      <c r="H26" s="505"/>
+      <c r="I26" s="505"/>
+      <c r="J26" s="505"/>
+      <c r="K26" s="505"/>
+      <c r="L26" s="505"/>
+    </row>
+    <row r="27" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B27" s="505"/>
+      <c r="C27" s="505"/>
+      <c r="D27" s="505"/>
+      <c r="E27" s="505"/>
+      <c r="F27" s="509">
+        <v>35</v>
+      </c>
+      <c r="G27" s="509">
+        <v>35000</v>
+      </c>
+      <c r="H27" s="505"/>
+      <c r="I27" s="505"/>
+      <c r="J27" s="505"/>
+      <c r="K27" s="505"/>
+      <c r="L27" s="505"/>
+    </row>
+    <row r="28" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B28" s="505"/>
+      <c r="C28" s="505"/>
+      <c r="D28" s="505"/>
+      <c r="E28" s="505"/>
+      <c r="F28" s="509">
+        <v>40</v>
+      </c>
+      <c r="G28" s="509">
+        <v>40000</v>
+      </c>
+      <c r="H28" s="505"/>
+      <c r="I28" s="505"/>
+      <c r="J28" s="505"/>
+      <c r="K28" s="505"/>
+      <c r="L28" s="505"/>
+    </row>
+    <row r="29" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B29" s="505"/>
+      <c r="C29" s="505"/>
+      <c r="D29" s="505"/>
+      <c r="E29" s="505"/>
+      <c r="F29" s="509">
+        <v>45</v>
+      </c>
+      <c r="G29" s="509">
+        <v>45000</v>
+      </c>
+      <c r="H29" s="505"/>
+      <c r="I29" s="505"/>
+      <c r="J29" s="505"/>
+      <c r="K29" s="505"/>
+      <c r="L29" s="505"/>
+    </row>
+    <row r="30" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B30" s="505"/>
+      <c r="C30" s="505"/>
+      <c r="D30" s="505"/>
+      <c r="E30" s="505"/>
+      <c r="F30" s="509">
+        <v>50</v>
+      </c>
+      <c r="G30" s="509">
+        <v>50000</v>
+      </c>
+      <c r="H30" s="505"/>
+      <c r="I30" s="505"/>
+      <c r="J30" s="505"/>
+      <c r="K30" s="505"/>
+      <c r="L30" s="505"/>
+    </row>
+    <row r="31" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B31" s="505"/>
+      <c r="C31" s="505"/>
+      <c r="D31" s="505"/>
+      <c r="E31" s="505"/>
+      <c r="F31" s="509"/>
+      <c r="G31" s="509"/>
+      <c r="H31" s="505"/>
+      <c r="I31" s="505"/>
+      <c r="J31" s="505"/>
+      <c r="K31" s="505"/>
+      <c r="L31" s="505"/>
+    </row>
+    <row r="32" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B32" s="505"/>
+      <c r="C32" s="505"/>
+      <c r="D32" s="505"/>
+      <c r="E32" s="505"/>
+      <c r="F32" s="509"/>
+      <c r="G32" s="509"/>
+      <c r="H32" s="505"/>
+      <c r="I32" s="505"/>
+      <c r="J32" s="505"/>
+      <c r="K32" s="505"/>
+      <c r="L32" s="505"/>
+    </row>
+    <row r="33" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B33" s="505"/>
+      <c r="C33" s="505"/>
+      <c r="D33" s="505"/>
+      <c r="E33" s="505"/>
+      <c r="F33" s="509"/>
+      <c r="G33" s="509"/>
+      <c r="H33" s="505"/>
+      <c r="I33" s="505"/>
+      <c r="J33" s="505"/>
+      <c r="K33" s="505"/>
+      <c r="L33" s="505"/>
+    </row>
+    <row r="34" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B34" s="505"/>
+      <c r="C34" s="505"/>
+      <c r="D34" s="505"/>
+      <c r="E34" s="505"/>
+      <c r="F34" s="509"/>
+      <c r="G34" s="509"/>
+      <c r="H34" s="505"/>
+      <c r="I34" s="505"/>
+      <c r="J34" s="505"/>
+      <c r="K34" s="505"/>
+      <c r="L34" s="505"/>
+    </row>
+    <row r="35" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B35" s="505"/>
+      <c r="C35" s="505"/>
+      <c r="D35" s="505"/>
+      <c r="E35" s="505"/>
+      <c r="F35" s="509"/>
+      <c r="G35" s="509"/>
+      <c r="H35" s="505"/>
+      <c r="I35" s="505"/>
+      <c r="J35" s="505"/>
+      <c r="K35" s="505"/>
+      <c r="L35" s="505"/>
+    </row>
+    <row r="36" spans="2:12" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="B36" s="505"/>
+      <c r="J36" s="505"/>
+      <c r="K36" s="505"/>
+      <c r="L36" s="505"/>
+    </row>
+    <row r="37" spans="2:12" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="B37" s="505"/>
+      <c r="J37" s="505"/>
+      <c r="K37" s="505"/>
+      <c r="L37" s="505"/>
+    </row>
+    <row r="38" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B38" s="505"/>
+      <c r="C38" s="505"/>
+      <c r="D38" s="511" t="s">
+        <v>505</v>
+      </c>
+      <c r="E38" s="517" t="s">
+        <v>277</v>
+      </c>
+      <c r="F38" s="518"/>
+      <c r="G38" s="518"/>
+      <c r="H38" s="518"/>
+      <c r="I38" s="519"/>
+      <c r="J38" s="505"/>
+      <c r="K38" s="505"/>
+      <c r="L38" s="505"/>
+    </row>
+    <row r="39" spans="2:12" ht="21" x14ac:dyDescent="0.3">
+      <c r="B39" s="505"/>
+      <c r="C39" s="505"/>
+      <c r="D39" s="512">
+        <f>L43</f>
+        <v>20000</v>
+      </c>
+      <c r="E39" s="512">
+        <v>2</v>
+      </c>
+      <c r="F39" s="512">
+        <v>3</v>
+      </c>
+      <c r="G39" s="512">
+        <v>4</v>
+      </c>
+      <c r="H39" s="512">
+        <v>5</v>
+      </c>
+      <c r="I39" s="512">
+        <v>6</v>
+      </c>
+      <c r="J39" s="505"/>
+      <c r="K39" s="506" t="s">
+        <v>503</v>
+      </c>
+      <c r="L39" s="506">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" ht="21" x14ac:dyDescent="0.3">
+      <c r="B40" s="505"/>
+      <c r="C40" s="520" t="s">
+        <v>504</v>
+      </c>
+      <c r="D40" s="513">
+        <v>10</v>
+      </c>
+      <c r="E40" s="514">
+        <f t="dataTable" ref="E40:I48" dt2D="1" dtr="1" r1="L41" r2="L40"/>
+        <v>10000</v>
+      </c>
+      <c r="F40" s="514">
+        <v>10000</v>
+      </c>
+      <c r="G40" s="514">
+        <v>10000</v>
+      </c>
+      <c r="H40" s="514">
+        <v>10000</v>
+      </c>
+      <c r="I40" s="514">
+        <v>10000</v>
+      </c>
+      <c r="J40" s="505"/>
+      <c r="K40" s="506" t="s">
+        <v>504</v>
+      </c>
+      <c r="L40" s="506">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" ht="21" x14ac:dyDescent="0.3">
+      <c r="B41" s="505"/>
+      <c r="C41" s="521"/>
+      <c r="D41" s="513">
+        <v>30</v>
+      </c>
+      <c r="E41" s="514">
+        <v>30000</v>
+      </c>
+      <c r="F41" s="514">
+        <v>30000</v>
+      </c>
+      <c r="G41" s="514">
+        <v>30000</v>
+      </c>
+      <c r="H41" s="514">
+        <v>30000</v>
+      </c>
+      <c r="I41" s="514">
+        <v>30000</v>
+      </c>
+      <c r="J41" s="505"/>
+      <c r="K41" s="506" t="s">
+        <v>277</v>
+      </c>
+      <c r="L41" s="506">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B42" s="505"/>
+      <c r="C42" s="521"/>
+      <c r="D42" s="513">
+        <v>40</v>
+      </c>
+      <c r="E42" s="514">
+        <v>40000</v>
+      </c>
+      <c r="F42" s="514">
+        <v>40000</v>
+      </c>
+      <c r="G42" s="514">
+        <v>40000</v>
+      </c>
+      <c r="H42" s="514">
+        <v>40000</v>
+      </c>
+      <c r="I42" s="514">
+        <v>40000</v>
+      </c>
+      <c r="J42" s="505"/>
+      <c r="K42" s="510"/>
+      <c r="L42" s="510"/>
+    </row>
+    <row r="43" spans="2:12" ht="21" x14ac:dyDescent="0.3">
+      <c r="B43" s="505"/>
+      <c r="C43" s="521"/>
+      <c r="D43" s="513">
+        <v>50</v>
+      </c>
+      <c r="E43" s="514">
+        <v>50000</v>
+      </c>
+      <c r="F43" s="514">
+        <v>50000</v>
+      </c>
+      <c r="G43" s="514">
+        <v>50000</v>
+      </c>
+      <c r="H43" s="514">
+        <v>50000</v>
+      </c>
+      <c r="I43" s="514">
+        <v>50000</v>
+      </c>
+      <c r="J43" s="505"/>
+      <c r="K43" s="506" t="s">
+        <v>505</v>
+      </c>
+      <c r="L43" s="506">
+        <f>L39*L40</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B44" s="505"/>
+      <c r="C44" s="521"/>
+      <c r="D44" s="513">
+        <v>60</v>
+      </c>
+      <c r="E44" s="514">
+        <v>60000</v>
+      </c>
+      <c r="F44" s="514">
+        <v>60000</v>
+      </c>
+      <c r="G44" s="514">
+        <v>60000</v>
+      </c>
+      <c r="H44" s="514">
+        <v>60000</v>
+      </c>
+      <c r="I44" s="514">
+        <v>60000</v>
+      </c>
+      <c r="J44" s="505"/>
+      <c r="K44" s="505"/>
+      <c r="L44" s="505"/>
+    </row>
+    <row r="45" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B45" s="505"/>
+      <c r="C45" s="521"/>
+      <c r="D45" s="513">
+        <v>70</v>
+      </c>
+      <c r="E45" s="514">
+        <v>70000</v>
+      </c>
+      <c r="F45" s="514">
+        <v>70000</v>
+      </c>
+      <c r="G45" s="514">
+        <v>70000</v>
+      </c>
+      <c r="H45" s="514">
+        <v>70000</v>
+      </c>
+      <c r="I45" s="514">
+        <v>70000</v>
+      </c>
+      <c r="J45" s="505"/>
+      <c r="K45" s="505"/>
+      <c r="L45" s="505"/>
+    </row>
+    <row r="46" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B46" s="505"/>
+      <c r="C46" s="521"/>
+      <c r="D46" s="513">
+        <v>80</v>
+      </c>
+      <c r="E46" s="514">
+        <v>80000</v>
+      </c>
+      <c r="F46" s="514">
+        <v>80000</v>
+      </c>
+      <c r="G46" s="514">
+        <v>80000</v>
+      </c>
+      <c r="H46" s="514">
+        <v>80000</v>
+      </c>
+      <c r="I46" s="514">
+        <v>80000</v>
+      </c>
+      <c r="J46" s="505"/>
+      <c r="K46" s="505"/>
+      <c r="L46" s="505"/>
+    </row>
+    <row r="47" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B47" s="505"/>
+      <c r="C47" s="521"/>
+      <c r="D47" s="513">
+        <v>90</v>
+      </c>
+      <c r="E47" s="514">
+        <v>90000</v>
+      </c>
+      <c r="F47" s="514">
+        <v>90000</v>
+      </c>
+      <c r="G47" s="514">
+        <v>90000</v>
+      </c>
+      <c r="H47" s="514">
+        <v>90000</v>
+      </c>
+      <c r="I47" s="514">
+        <v>90000</v>
+      </c>
+      <c r="J47" s="505"/>
+      <c r="K47" s="505"/>
+      <c r="L47" s="505"/>
+    </row>
+    <row r="48" spans="2:12" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="B48" s="505"/>
+      <c r="C48" s="522"/>
+      <c r="D48" s="513">
+        <v>100</v>
+      </c>
+      <c r="E48" s="514">
+        <v>100000</v>
+      </c>
+      <c r="F48" s="514">
+        <v>100000</v>
+      </c>
+      <c r="G48" s="514">
+        <v>100000</v>
+      </c>
+      <c r="H48" s="514">
+        <v>100000</v>
+      </c>
+      <c r="I48" s="514">
+        <v>100000</v>
+      </c>
+      <c r="J48" s="505"/>
+      <c r="K48" s="505"/>
+      <c r="L48" s="505"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E38:I38"/>
+    <mergeCell ref="C40:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15890,17 +20725,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="461" t="s">
+      <c r="A1" s="532" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="462"/>
-      <c r="C1" s="462"/>
-      <c r="D1" s="462"/>
-      <c r="E1" s="462"/>
-      <c r="F1" s="462"/>
-      <c r="G1" s="462"/>
-      <c r="H1" s="462"/>
-      <c r="I1" s="462"/>
+      <c r="B1" s="533"/>
+      <c r="C1" s="533"/>
+      <c r="D1" s="533"/>
+      <c r="E1" s="533"/>
+      <c r="F1" s="533"/>
+      <c r="G1" s="533"/>
+      <c r="H1" s="533"/>
+      <c r="I1" s="533"/>
     </row>
     <row r="2" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="31">
@@ -16254,7 +21089,7 @@
       <c r="C3" s="33">
         <v>46221</v>
       </c>
-      <c r="D3" s="466" t="s">
+      <c r="D3" s="537" t="s">
         <v>120</v>
       </c>
     </row>
@@ -16262,30 +21097,30 @@
       <c r="C4" s="33">
         <v>46220</v>
       </c>
-      <c r="D4" s="466"/>
+      <c r="D4" s="537"/>
     </row>
     <row r="5" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="40"/>
       <c r="C5" s="33">
         <v>46219</v>
       </c>
-      <c r="D5" s="466"/>
+      <c r="D5" s="537"/>
       <c r="E5" s="35">
         <v>600</v>
       </c>
-      <c r="F5" s="465" t="s">
+      <c r="F5" s="536" t="s">
         <v>120</v>
       </c>
       <c r="G5" s="39">
         <v>0.1</v>
       </c>
-      <c r="H5" s="463" t="s">
+      <c r="H5" s="534" t="s">
         <v>119</v>
       </c>
       <c r="I5" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="J5" s="464" t="s">
+      <c r="J5" s="535" t="s">
         <v>119</v>
       </c>
     </row>
@@ -16294,175 +21129,175 @@
       <c r="C6" s="33">
         <v>46218</v>
       </c>
-      <c r="D6" s="466"/>
+      <c r="D6" s="537"/>
       <c r="E6" s="35">
         <v>432</v>
       </c>
-      <c r="F6" s="465"/>
+      <c r="F6" s="536"/>
       <c r="G6" s="38">
         <v>0.3</v>
       </c>
-      <c r="H6" s="463"/>
+      <c r="H6" s="534"/>
       <c r="I6" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="J6" s="464"/>
+      <c r="J6" s="535"/>
     </row>
     <row r="7" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="40"/>
       <c r="C7" s="33">
         <v>46217</v>
       </c>
-      <c r="D7" s="466"/>
+      <c r="D7" s="537"/>
       <c r="E7" s="35">
         <v>400</v>
       </c>
-      <c r="F7" s="465"/>
+      <c r="F7" s="536"/>
       <c r="G7" s="38">
         <v>0.34</v>
       </c>
-      <c r="H7" s="463"/>
+      <c r="H7" s="534"/>
       <c r="I7" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="J7" s="464"/>
+      <c r="J7" s="535"/>
     </row>
     <row r="8" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="40"/>
       <c r="C8" s="33">
         <v>46216</v>
       </c>
-      <c r="D8" s="466"/>
+      <c r="D8" s="537"/>
       <c r="E8" s="35">
         <v>360</v>
       </c>
-      <c r="F8" s="465"/>
+      <c r="F8" s="536"/>
       <c r="G8" s="38">
         <v>0.43</v>
       </c>
-      <c r="H8" s="463"/>
+      <c r="H8" s="534"/>
       <c r="I8" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="J8" s="464"/>
+      <c r="J8" s="535"/>
     </row>
     <row r="9" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="40"/>
       <c r="C9" s="33">
         <v>46215</v>
       </c>
-      <c r="D9" s="466"/>
+      <c r="D9" s="537"/>
       <c r="E9" s="35">
         <v>350</v>
       </c>
-      <c r="F9" s="465"/>
+      <c r="F9" s="536"/>
       <c r="G9" s="38">
         <v>0.45</v>
       </c>
-      <c r="H9" s="463"/>
+      <c r="H9" s="534"/>
       <c r="I9" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="J9" s="464"/>
+      <c r="J9" s="535"/>
     </row>
     <row r="10" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="40"/>
       <c r="C10" s="33">
         <v>46214</v>
       </c>
-      <c r="D10" s="466"/>
+      <c r="D10" s="537"/>
       <c r="E10" s="35">
         <v>300</v>
       </c>
-      <c r="F10" s="465"/>
+      <c r="F10" s="536"/>
       <c r="G10" s="38">
         <v>0.5</v>
       </c>
-      <c r="H10" s="463"/>
+      <c r="H10" s="534"/>
     </row>
     <row r="11" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="40"/>
       <c r="C11" s="33">
         <v>46213</v>
       </c>
-      <c r="D11" s="466"/>
+      <c r="D11" s="537"/>
       <c r="E11" s="35">
         <v>300</v>
       </c>
-      <c r="F11" s="465"/>
+      <c r="F11" s="536"/>
       <c r="G11" s="38">
         <v>0.6</v>
       </c>
-      <c r="H11" s="463"/>
+      <c r="H11" s="534"/>
     </row>
     <row r="12" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="40"/>
       <c r="C12" s="33">
         <v>46212</v>
       </c>
-      <c r="D12" s="466"/>
+      <c r="D12" s="537"/>
       <c r="E12" s="35">
         <v>230</v>
       </c>
-      <c r="F12" s="465"/>
+      <c r="F12" s="536"/>
       <c r="G12" s="38">
         <v>0.9</v>
       </c>
-      <c r="H12" s="463"/>
+      <c r="H12" s="534"/>
     </row>
     <row r="13" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="40"/>
       <c r="C13" s="33">
         <v>46211</v>
       </c>
-      <c r="D13" s="466"/>
+      <c r="D13" s="537"/>
       <c r="E13" s="35">
         <v>150</v>
       </c>
-      <c r="F13" s="465"/>
+      <c r="F13" s="536"/>
     </row>
     <row r="14" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="40"/>
       <c r="C14" s="33">
         <v>46210</v>
       </c>
-      <c r="D14" s="466"/>
+      <c r="D14" s="537"/>
       <c r="E14" s="35">
         <v>100</v>
       </c>
-      <c r="F14" s="465"/>
+      <c r="F14" s="536"/>
     </row>
     <row r="15" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="40"/>
       <c r="C15" s="33">
         <v>46209</v>
       </c>
-      <c r="D15" s="466"/>
+      <c r="D15" s="537"/>
     </row>
     <row r="16" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="40"/>
       <c r="C16" s="33">
         <v>46208</v>
       </c>
-      <c r="D16" s="466"/>
+      <c r="D16" s="537"/>
     </row>
     <row r="17" spans="3:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C17" s="33">
         <v>46207</v>
       </c>
-      <c r="D17" s="466"/>
+      <c r="D17" s="537"/>
     </row>
     <row r="18" spans="3:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C18" s="33">
         <v>46206</v>
       </c>
-      <c r="D18" s="466"/>
+      <c r="D18" s="537"/>
     </row>
     <row r="19" spans="3:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="33">
         <v>46205</v>
       </c>
-      <c r="D19" s="466"/>
+      <c r="D19" s="537"/>
     </row>
     <row r="20" spans="3:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C20" s="33">
@@ -16548,7 +21383,7 @@
         <f>SUM(C4:C10)</f>
         <v>55000</v>
       </c>
-      <c r="J5" s="467" t="s">
+      <c r="J5" s="538" t="s">
         <v>147</v>
       </c>
     </row>
@@ -16569,7 +21404,7 @@
         <f>C4+C5+C6+C7+C8+C9+C10</f>
         <v>55000</v>
       </c>
-      <c r="J6" s="468"/>
+      <c r="J6" s="539"/>
     </row>
     <row r="7" spans="2:10" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="57" t="s">
@@ -16924,7 +21759,7 @@
       <c r="D29" s="79" t="s">
         <v>157</v>
       </c>
-      <c r="E29" s="469" t="s">
+      <c r="E29" s="540" t="s">
         <v>159</v>
       </c>
     </row>
@@ -16939,7 +21774,7 @@
       <c r="D30" s="80" t="s">
         <v>158</v>
       </c>
-      <c r="E30" s="469"/>
+      <c r="E30" s="540"/>
       <c r="I30" s="81" t="s">
         <v>163</v>
       </c>
@@ -16955,7 +21790,7 @@
       <c r="D31" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="E31" s="469"/>
+      <c r="E31" s="540"/>
       <c r="I31" s="81" t="s">
         <v>164</v>
       </c>
@@ -16971,7 +21806,7 @@
       <c r="D32" s="79" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="469"/>
+      <c r="E32" s="540"/>
       <c r="I32" s="81" t="s">
         <v>165</v>
       </c>
@@ -16987,7 +21822,7 @@
       <c r="D33" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="E33" s="469"/>
+      <c r="E33" s="540"/>
       <c r="I33" s="82" t="s">
         <v>166</v>
       </c>
@@ -18598,18 +23433,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="D1" s="470" t="s">
+      <c r="D1" s="541" t="s">
         <v>340</v>
       </c>
-      <c r="E1" s="470"/>
-      <c r="F1" s="470"/>
-      <c r="G1" s="470"/>
-      <c r="H1" s="470"/>
-      <c r="I1" s="470"/>
-      <c r="J1" s="470"/>
-      <c r="K1" s="470"/>
-      <c r="L1" s="470"/>
-      <c r="M1" s="470"/>
+      <c r="E1" s="541"/>
+      <c r="F1" s="541"/>
+      <c r="G1" s="541"/>
+      <c r="H1" s="541"/>
+      <c r="I1" s="541"/>
+      <c r="J1" s="541"/>
+      <c r="K1" s="541"/>
+      <c r="L1" s="541"/>
+      <c r="M1" s="541"/>
     </row>
     <row r="2" spans="2:13" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="42" t="s">
@@ -19210,11 +24045,11 @@
       </c>
       <c r="G4" s="156">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46274</v>
       </c>
       <c r="H4" s="155">
         <f ca="1">NOW()</f>
-        <v>46266.485833217594</v>
+        <v>46274.620353009261</v>
       </c>
       <c r="I4" s="156">
         <f>DATE(C2,C3,C4)</f>
@@ -19388,13 +24223,13 @@
         <f>F11+H11</f>
         <v>45242</v>
       </c>
-      <c r="K11" s="499" t="s">
+      <c r="K11" s="544" t="s">
         <v>348</v>
       </c>
-      <c r="L11" s="499"/>
-      <c r="M11" s="499"/>
-      <c r="N11" s="499"/>
-      <c r="O11" s="499"/>
+      <c r="L11" s="544"/>
+      <c r="M11" s="544"/>
+      <c r="N11" s="544"/>
+      <c r="O11" s="544"/>
     </row>
     <row r="12" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="116" t="s">
@@ -19418,13 +24253,13 @@
         <f>F12+H12</f>
         <v>44913</v>
       </c>
-      <c r="K12" s="499" t="s">
+      <c r="K12" s="544" t="s">
         <v>349</v>
       </c>
-      <c r="L12" s="499"/>
-      <c r="M12" s="499"/>
-      <c r="N12" s="499"/>
-      <c r="O12" s="499"/>
+      <c r="L12" s="544"/>
+      <c r="M12" s="544"/>
+      <c r="N12" s="544"/>
+      <c r="O12" s="544"/>
     </row>
     <row r="13" spans="2:18" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="116" t="s">
@@ -19448,13 +24283,13 @@
         <f>F13+H13</f>
         <v>42293</v>
       </c>
-      <c r="K13" s="499" t="s">
+      <c r="K13" s="544" t="s">
         <v>350</v>
       </c>
-      <c r="L13" s="499"/>
-      <c r="M13" s="499"/>
-      <c r="N13" s="499"/>
-      <c r="O13" s="499"/>
+      <c r="L13" s="544"/>
+      <c r="M13" s="544"/>
+      <c r="N13" s="544"/>
+      <c r="O13" s="544"/>
     </row>
     <row r="14" spans="2:18" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="116" t="s">
@@ -19478,13 +24313,13 @@
         <f>E14+H14</f>
         <v>45770</v>
       </c>
-      <c r="K14" s="499" t="s">
+      <c r="K14" s="544" t="s">
         <v>353</v>
       </c>
-      <c r="L14" s="499"/>
-      <c r="M14" s="499"/>
-      <c r="N14" s="499"/>
-      <c r="O14" s="499"/>
+      <c r="L14" s="544"/>
+      <c r="M14" s="544"/>
+      <c r="N14" s="544"/>
+      <c r="O14" s="544"/>
     </row>
     <row r="15" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="116" t="s">
@@ -19497,11 +24332,11 @@
       <c r="G15" s="122"/>
       <c r="H15" s="122"/>
       <c r="I15" s="122"/>
-      <c r="K15" s="499"/>
-      <c r="L15" s="499"/>
-      <c r="M15" s="499"/>
-      <c r="N15" s="499"/>
-      <c r="O15" s="499"/>
+      <c r="K15" s="544"/>
+      <c r="L15" s="544"/>
+      <c r="M15" s="544"/>
+      <c r="N15" s="544"/>
+      <c r="O15" s="544"/>
     </row>
     <row r="16" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="116" t="s">
@@ -19514,32 +24349,32 @@
       <c r="G16" s="122"/>
       <c r="H16" s="122"/>
       <c r="I16" s="122"/>
-      <c r="K16" s="499"/>
-      <c r="L16" s="499"/>
-      <c r="M16" s="499"/>
-      <c r="N16" s="499"/>
-      <c r="O16" s="499"/>
+      <c r="K16" s="544"/>
+      <c r="L16" s="544"/>
+      <c r="M16" s="544"/>
+      <c r="N16" s="544"/>
+      <c r="O16" s="544"/>
     </row>
     <row r="17" spans="2:15" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="116" t="s">
         <v>262</v>
       </c>
       <c r="C17" s="122"/>
-      <c r="D17" s="497" t="s">
+      <c r="D17" s="542" t="s">
         <v>347</v>
       </c>
-      <c r="E17" s="498"/>
+      <c r="E17" s="543"/>
       <c r="F17" s="122"/>
       <c r="G17" s="122"/>
       <c r="H17" s="163" t="s">
         <v>352</v>
       </c>
       <c r="I17" s="122"/>
-      <c r="K17" s="499"/>
-      <c r="L17" s="499"/>
-      <c r="M17" s="499"/>
-      <c r="N17" s="499"/>
-      <c r="O17" s="499"/>
+      <c r="K17" s="544"/>
+      <c r="L17" s="544"/>
+      <c r="M17" s="544"/>
+      <c r="N17" s="544"/>
+      <c r="O17" s="544"/>
     </row>
     <row r="18" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="116" t="s">
@@ -19552,11 +24387,11 @@
       <c r="G18" s="115"/>
       <c r="H18" s="115"/>
       <c r="I18" s="115"/>
-      <c r="K18" s="496"/>
-      <c r="L18" s="496"/>
-      <c r="M18" s="496"/>
-      <c r="N18" s="496"/>
-      <c r="O18" s="496"/>
+      <c r="K18" s="545"/>
+      <c r="L18" s="545"/>
+      <c r="M18" s="545"/>
+      <c r="N18" s="545"/>
+      <c r="O18" s="545"/>
     </row>
     <row r="19" spans="2:15" ht="33" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="122"/>
@@ -19579,7 +24414,7 @@
     <row r="20" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="122"/>
       <c r="C20" s="123"/>
-      <c r="D20" s="474" t="s">
+      <c r="D20" s="546" t="s">
         <v>267</v>
       </c>
       <c r="E20" s="124">
@@ -19595,14 +24430,14 @@
       <c r="H20" s="162">
         <v>44988</v>
       </c>
-      <c r="I20" s="474" t="s">
+      <c r="I20" s="546" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="122"/>
       <c r="C21" s="123"/>
-      <c r="D21" s="475"/>
+      <c r="D21" s="547"/>
       <c r="E21" s="124">
         <v>45512</v>
       </c>
@@ -19616,12 +24451,12 @@
       <c r="H21" s="162">
         <v>45665</v>
       </c>
-      <c r="I21" s="475"/>
+      <c r="I21" s="547"/>
     </row>
     <row r="22" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="122"/>
       <c r="C22" s="123"/>
-      <c r="D22" s="475"/>
+      <c r="D22" s="547"/>
       <c r="E22" s="124">
         <v>42252</v>
       </c>
@@ -19635,12 +24470,12 @@
       <c r="H22" s="162">
         <v>42099</v>
       </c>
-      <c r="I22" s="475"/>
+      <c r="I22" s="547"/>
     </row>
     <row r="23" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="122"/>
       <c r="C23" s="123"/>
-      <c r="D23" s="476"/>
+      <c r="D23" s="548"/>
       <c r="E23" s="124">
         <v>45770</v>
       </c>
@@ -19654,7 +24489,7 @@
       <c r="H23" s="162">
         <v>45405</v>
       </c>
-      <c r="I23" s="476"/>
+      <c r="I23" s="548"/>
     </row>
     <row r="24" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="122"/>
@@ -19668,10 +24503,10 @@
     </row>
     <row r="25" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="123"/>
-      <c r="C25" s="471" t="s">
+      <c r="C25" s="549" t="s">
         <v>269</v>
       </c>
-      <c r="D25" s="474" t="s">
+      <c r="D25" s="546" t="s">
         <v>270</v>
       </c>
       <c r="E25" s="156">
@@ -19685,8 +24520,8 @@
     </row>
     <row r="26" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="123"/>
-      <c r="C26" s="472"/>
-      <c r="D26" s="475"/>
+      <c r="C26" s="550"/>
+      <c r="D26" s="547"/>
       <c r="E26" s="156">
         <f>EOMONTH(G21,G12)</f>
         <v>45838</v>
@@ -19700,8 +24535,8 @@
     </row>
     <row r="27" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="123"/>
-      <c r="C27" s="472"/>
-      <c r="D27" s="475"/>
+      <c r="C27" s="550"/>
+      <c r="D27" s="547"/>
       <c r="E27" s="156">
         <f>EOMONTH(G22,G13)</f>
         <v>41973</v>
@@ -19713,8 +24548,8 @@
     </row>
     <row r="28" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="123"/>
-      <c r="C28" s="473"/>
-      <c r="D28" s="476"/>
+      <c r="C28" s="551"/>
+      <c r="D28" s="548"/>
       <c r="E28" s="156">
         <f>EOMONTH(G23,G14)</f>
         <v>45046</v>
@@ -19736,10 +24571,10 @@
     </row>
     <row r="30" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="123"/>
-      <c r="C30" s="471" t="s">
+      <c r="C30" s="549" t="s">
         <v>271</v>
       </c>
-      <c r="D30" s="474" t="s">
+      <c r="D30" s="546" t="s">
         <v>257</v>
       </c>
       <c r="E30" s="164">
@@ -19757,8 +24592,8 @@
     </row>
     <row r="31" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="123"/>
-      <c r="C31" s="472"/>
-      <c r="D31" s="475"/>
+      <c r="C31" s="550"/>
+      <c r="D31" s="547"/>
       <c r="E31" s="164">
         <f t="shared" ref="E31:E33" si="1">WEEKDAY(F31,2)</f>
         <v>3</v>
@@ -19774,8 +24609,8 @@
     </row>
     <row r="32" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="123"/>
-      <c r="C32" s="472"/>
-      <c r="D32" s="475"/>
+      <c r="C32" s="550"/>
+      <c r="D32" s="547"/>
       <c r="E32" s="164">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -19791,8 +24626,8 @@
     </row>
     <row r="33" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="123"/>
-      <c r="C33" s="473"/>
-      <c r="D33" s="476"/>
+      <c r="C33" s="551"/>
+      <c r="D33" s="548"/>
       <c r="E33" s="164">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -19818,10 +24653,10 @@
     </row>
     <row r="35" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="123"/>
-      <c r="C35" s="471" t="s">
+      <c r="C35" s="549" t="s">
         <v>272</v>
       </c>
-      <c r="D35" s="474" t="s">
+      <c r="D35" s="546" t="s">
         <v>258</v>
       </c>
       <c r="E35" s="164">
@@ -19837,8 +24672,8 @@
     </row>
     <row r="36" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="123"/>
-      <c r="C36" s="472"/>
-      <c r="D36" s="475"/>
+      <c r="C36" s="550"/>
+      <c r="D36" s="547"/>
       <c r="E36" s="164">
         <f t="shared" ref="E36:E38" si="2">WEEKNUM(F36,11)</f>
         <v>2</v>
@@ -19852,8 +24687,8 @@
     </row>
     <row r="37" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="123"/>
-      <c r="C37" s="472"/>
-      <c r="D37" s="475"/>
+      <c r="C37" s="550"/>
+      <c r="D37" s="547"/>
       <c r="E37" s="164">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -19867,8 +24702,8 @@
     </row>
     <row r="38" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="123"/>
-      <c r="C38" s="473"/>
-      <c r="D38" s="476"/>
+      <c r="C38" s="551"/>
+      <c r="D38" s="548"/>
       <c r="E38" s="164">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -19913,7 +24748,7 @@
     <row r="41" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="122"/>
       <c r="C41" s="123"/>
-      <c r="D41" s="474" t="s">
+      <c r="D41" s="546" t="s">
         <v>255</v>
       </c>
       <c r="E41" s="164">
@@ -19938,7 +24773,7 @@
     <row r="42" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="122"/>
       <c r="C42" s="123"/>
-      <c r="D42" s="475"/>
+      <c r="D42" s="547"/>
       <c r="E42" s="164">
         <f>DATEDIF(F42,G42,"M")</f>
         <v>28</v>
@@ -19961,7 +24796,7 @@
     <row r="43" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="122"/>
       <c r="C43" s="123"/>
-      <c r="D43" s="475"/>
+      <c r="D43" s="547"/>
       <c r="E43" s="164">
         <f>DATEDIF(F43,G43,"M")</f>
         <v>10</v>
@@ -19984,7 +24819,7 @@
     <row r="44" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="122"/>
       <c r="C44" s="123"/>
-      <c r="D44" s="476"/>
+      <c r="D44" s="548"/>
       <c r="E44" s="164">
         <f>DATEDIF(F44,G44,"M")</f>
         <v>44</v>
@@ -20027,7 +24862,7 @@
         <f>DATEDIF($D$47,$I$47,"Y")</f>
         <v>20</v>
       </c>
-      <c r="G46" s="474" t="s">
+      <c r="G46" s="546" t="s">
         <v>278</v>
       </c>
       <c r="H46" s="115"/>
@@ -20046,7 +24881,7 @@
         <f>DATEDIF($D$47,$I$47,"M")</f>
         <v>244</v>
       </c>
-      <c r="G47" s="475"/>
+      <c r="G47" s="547"/>
       <c r="H47" s="119" t="s">
         <v>279</v>
       </c>
@@ -20065,7 +24900,7 @@
         <f>DATEDIF($D$47,$I$47,"D")</f>
         <v>7434</v>
       </c>
-      <c r="G48" s="476"/>
+      <c r="G48" s="548"/>
       <c r="H48" s="122"/>
       <c r="I48" s="122"/>
     </row>
@@ -20090,16 +24925,16 @@
       <c r="I50" s="115"/>
     </row>
     <row r="51" spans="2:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="487" t="s">
+      <c r="B51" s="562" t="s">
         <v>280</v>
       </c>
-      <c r="C51" s="488"/>
-      <c r="D51" s="488"/>
-      <c r="E51" s="488"/>
-      <c r="F51" s="488"/>
-      <c r="G51" s="488"/>
-      <c r="H51" s="489"/>
-      <c r="I51" s="490" t="s">
+      <c r="C51" s="563"/>
+      <c r="D51" s="563"/>
+      <c r="E51" s="563"/>
+      <c r="F51" s="563"/>
+      <c r="G51" s="563"/>
+      <c r="H51" s="564"/>
+      <c r="I51" s="565" t="s">
         <v>281</v>
       </c>
     </row>
@@ -20125,7 +24960,7 @@
       <c r="H52" s="124">
         <v>43862</v>
       </c>
-      <c r="I52" s="491"/>
+      <c r="I52" s="566"/>
     </row>
     <row r="53" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="128" t="s">
@@ -20149,7 +24984,7 @@
       <c r="H53" s="124">
         <v>44208</v>
       </c>
-      <c r="I53" s="491"/>
+      <c r="I53" s="566"/>
     </row>
     <row r="54" spans="2:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="128" t="s">
@@ -20173,7 +25008,7 @@
       <c r="H54" s="118" t="s">
         <v>285</v>
       </c>
-      <c r="I54" s="491"/>
+      <c r="I54" s="566"/>
     </row>
     <row r="55" spans="2:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="129" t="s">
@@ -20203,7 +25038,7 @@
         <f>DATEDIF(H52,H53,"YD")</f>
         <v>346</v>
       </c>
-      <c r="I55" s="492"/>
+      <c r="I55" s="567"/>
     </row>
     <row r="56" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="115"/>
@@ -20273,7 +25108,7 @@
         <f>NETWORKDAYS(E59,F59,D66:D68)</f>
         <v>257</v>
       </c>
-      <c r="I59" s="477" t="s">
+      <c r="I59" s="552" t="s">
         <v>262</v>
       </c>
     </row>
@@ -20299,7 +25134,7 @@
         <f>NETWORKDAYS(E60,F60,D69:D71)</f>
         <v>259</v>
       </c>
-      <c r="I60" s="478"/>
+      <c r="I60" s="553"/>
     </row>
     <row r="61" spans="2:9" ht="49.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="130" t="s">
@@ -20323,7 +25158,7 @@
         <f>NETWORKDAYS.INTL(E61,F61,1,D72:D74)</f>
         <v>259</v>
       </c>
-      <c r="I61" s="479" t="s">
+      <c r="I61" s="554" t="s">
         <v>354</v>
       </c>
     </row>
@@ -20349,7 +25184,7 @@
         <f>NETWORKDAYS.INTL(E62,F62,1,G69:G71)</f>
         <v>258</v>
       </c>
-      <c r="I62" s="480"/>
+      <c r="I62" s="555"/>
     </row>
     <row r="63" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="122"/>
@@ -20383,7 +25218,7 @@
     </row>
     <row r="66" spans="2:9" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="135"/>
-      <c r="C66" s="493" t="s">
+      <c r="C66" s="568" t="s">
         <v>298</v>
       </c>
       <c r="D66" s="134">
@@ -20392,7 +25227,7 @@
       <c r="E66" s="136" t="s">
         <v>295</v>
       </c>
-      <c r="F66" s="481" t="s">
+      <c r="F66" s="556" t="s">
         <v>296</v>
       </c>
       <c r="G66" s="137">
@@ -20401,56 +25236,56 @@
       <c r="H66" s="138" t="s">
         <v>297</v>
       </c>
-      <c r="I66" s="484" t="s">
+      <c r="I66" s="559" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="67" spans="2:9" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="135"/>
-      <c r="C67" s="494"/>
+      <c r="C67" s="569"/>
       <c r="D67" s="124">
         <v>45153</v>
       </c>
       <c r="E67" s="125" t="s">
         <v>299</v>
       </c>
-      <c r="F67" s="482"/>
+      <c r="F67" s="557"/>
       <c r="G67" s="137">
         <v>42189</v>
       </c>
       <c r="H67" s="138" t="s">
         <v>299</v>
       </c>
-      <c r="I67" s="485"/>
+      <c r="I67" s="560"/>
     </row>
     <row r="68" spans="2:9" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="135"/>
-      <c r="C68" s="494"/>
+      <c r="C68" s="569"/>
       <c r="D68" s="134">
         <v>45201</v>
       </c>
       <c r="E68" s="136" t="s">
         <v>300</v>
       </c>
-      <c r="F68" s="482"/>
+      <c r="F68" s="557"/>
       <c r="G68" s="137">
         <v>42248</v>
       </c>
       <c r="H68" s="138" t="s">
         <v>301</v>
       </c>
-      <c r="I68" s="486"/>
+      <c r="I68" s="561"/>
     </row>
     <row r="69" spans="2:9" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B69" s="122"/>
-      <c r="C69" s="494"/>
+      <c r="C69" s="569"/>
       <c r="D69" s="134">
         <v>45317</v>
       </c>
       <c r="E69" s="136" t="s">
         <v>295</v>
       </c>
-      <c r="F69" s="482"/>
+      <c r="F69" s="557"/>
       <c r="G69" s="137">
         <v>45705</v>
       </c>
@@ -20461,14 +25296,14 @@
     </row>
     <row r="70" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B70" s="122"/>
-      <c r="C70" s="494"/>
+      <c r="C70" s="569"/>
       <c r="D70" s="124">
         <v>45519</v>
       </c>
       <c r="E70" s="125" t="s">
         <v>299</v>
       </c>
-      <c r="F70" s="482"/>
+      <c r="F70" s="557"/>
       <c r="G70" s="137">
         <v>45842</v>
       </c>
@@ -20479,14 +25314,14 @@
     </row>
     <row r="71" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="122"/>
-      <c r="C71" s="494"/>
+      <c r="C71" s="569"/>
       <c r="D71" s="134">
         <v>45567</v>
       </c>
       <c r="E71" s="136" t="s">
         <v>300</v>
       </c>
-      <c r="F71" s="482"/>
+      <c r="F71" s="557"/>
       <c r="G71" s="137">
         <v>45901</v>
       </c>
@@ -20497,61 +25332,48 @@
     </row>
     <row r="72" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B72" s="122"/>
-      <c r="C72" s="494"/>
+      <c r="C72" s="569"/>
       <c r="D72" s="134">
         <v>42030</v>
       </c>
       <c r="E72" s="136" t="s">
         <v>295</v>
       </c>
-      <c r="F72" s="482"/>
+      <c r="F72" s="557"/>
       <c r="G72" s="122"/>
       <c r="H72" s="122"/>
       <c r="I72" s="122"/>
     </row>
     <row r="73" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B73" s="122"/>
-      <c r="C73" s="494"/>
+      <c r="C73" s="569"/>
       <c r="D73" s="124">
         <v>42231</v>
       </c>
       <c r="E73" s="125" t="s">
         <v>299</v>
       </c>
-      <c r="F73" s="482"/>
+      <c r="F73" s="557"/>
       <c r="G73" s="122"/>
       <c r="H73" s="122"/>
       <c r="I73" s="122"/>
     </row>
     <row r="74" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="122"/>
-      <c r="C74" s="495"/>
+      <c r="C74" s="570"/>
       <c r="D74" s="134">
         <v>42279</v>
       </c>
       <c r="E74" s="136" t="s">
         <v>300</v>
       </c>
-      <c r="F74" s="483"/>
+      <c r="F74" s="558"/>
       <c r="G74" s="122"/>
       <c r="H74" s="122"/>
       <c r="I74" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="K11:O11"/>
-    <mergeCell ref="K12:O12"/>
-    <mergeCell ref="K13:O13"/>
-    <mergeCell ref="K14:O14"/>
-    <mergeCell ref="K15:O15"/>
-    <mergeCell ref="K16:O16"/>
-    <mergeCell ref="K17:O17"/>
-    <mergeCell ref="K18:O18"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="I20:I23"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="D25:D28"/>
     <mergeCell ref="C30:C33"/>
     <mergeCell ref="D30:D33"/>
     <mergeCell ref="I59:I60"/>
@@ -20565,6 +25387,19 @@
     <mergeCell ref="B51:H51"/>
     <mergeCell ref="I51:I55"/>
     <mergeCell ref="C66:C74"/>
+    <mergeCell ref="K18:O18"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="I20:I23"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="K11:O11"/>
+    <mergeCell ref="K12:O12"/>
+    <mergeCell ref="K13:O13"/>
+    <mergeCell ref="K14:O14"/>
+    <mergeCell ref="K15:O15"/>
+    <mergeCell ref="K16:O16"/>
+    <mergeCell ref="K17:O17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
